--- a/reports/HEDGEFUND_TERMINAL.xlsx
+++ b/reports/HEDGEFUND_TERMINAL.xlsx
@@ -491,7 +491,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>28 February 2026</t>
+          <t>01 March 2026</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
         <v>0.17468001</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>2.503</v>
+        <v>0.264</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>0.25638</v>
@@ -6029,7 +6029,7 @@
         <v>10.537379</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>1.8201014</v>
+        <v>1.8180939</v>
       </c>
       <c r="J5" s="11" t="n">
         <v>0</v>

--- a/reports/HEDGEFUND_TERMINAL.xlsx
+++ b/reports/HEDGEFUND_TERMINAL.xlsx
@@ -491,7 +491,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01 March 2026</t>
+          <t>04 March 2026</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7"/>
@@ -572,7 +572,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-5.5M</t>
+          <t>-2.9M</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>745400</t>
+          <t>-21.6M</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -625,7 +625,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.2M</t>
+          <t>745400</t>
         </is>
       </c>
     </row>
@@ -637,12 +637,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>115.0M</t>
+          <t>115.7M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -650,7 +650,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.9M</t>
+          <t>-5.5M</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -675,7 +675,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.9M</t>
+          <t>56.6M</t>
         </is>
       </c>
     </row>
@@ -723,75 +723,75 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1. Consumer Cyclical</t>
+          <t>1. Basic Materials</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>297.8M</t>
+          <t>-165.8M</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2. Basic Materials</t>
+          <t>2. Energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>60.9</v>
+        <v>60.4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-165.8M</t>
+          <t>-494.1M</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3. Healthcare</t>
+          <t>3. Consumer Cyclical</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>59</v>
+        <v>52.7</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-34.5M</t>
+          <t>297.8M</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4. Industrials</t>
+          <t>4. Healthcare</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>54.3</v>
+        <v>52.5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-102.8M</t>
+          <t>-34.5M</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5. Energy</t>
+          <t>5. Financial Services</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>54.2</v>
+        <v>51.8</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-494.1M</t>
+          <t>115.7M</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -902,7 +902,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -910,36 +910,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1502-1578</t>
+          <t>2909-3091</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1427.5</v>
+        <v>2726.785714285714</v>
       </c>
       <c r="F2" t="n">
-        <v>1681.964285714286</v>
+        <v>3341.785714285714</v>
       </c>
       <c r="G2" t="n">
-        <v>1850.160714285714</v>
+        <v>3675.964285714286</v>
       </c>
       <c r="H2" t="n">
-        <v>1925.714285714286</v>
+        <v>3926.785714285714</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>18.56%</t>
+          <t>25.36%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>90.95</v>
+        <v>26.27</v>
       </c>
       <c r="L2" t="n">
-        <v>-5503000</v>
+        <v>-2895500</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -961,40 +961,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7714-8086</t>
+          <t>840-910</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7342.857142857143</v>
+        <v>770.5357142857143</v>
       </c>
       <c r="F3" t="n">
-        <v>8575.892857142857</v>
+        <v>1011.607142857143</v>
       </c>
       <c r="G3" t="n">
-        <v>9066.071428571428</v>
+        <v>1112.767857142857</v>
       </c>
       <c r="H3" t="n">
-        <v>9719.642857142857</v>
+        <v>1249.107142857143</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.81%</t>
+          <t>28.45%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>784.42</v>
+        <v>10812872355.39</v>
       </c>
       <c r="L3" t="n">
-        <v>745400</v>
+        <v>-21636100</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1012,36 +1012,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2354-2426</t>
+          <t>6238-6712</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2282.857142857143</v>
+        <v>5765.178571428572</v>
       </c>
       <c r="F4" t="n">
-        <v>2531.785714285714</v>
+        <v>7338.392857142857</v>
       </c>
       <c r="G4" t="n">
-        <v>2637.857142857143</v>
+        <v>8072.232142857143</v>
       </c>
       <c r="H4" t="n">
-        <v>2779.285714285714</v>
+        <v>8800.892857142857</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.70%</t>
+          <t>28.58%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>441.56</v>
+        <v>691.24</v>
       </c>
       <c r="L4" t="n">
-        <v>10200200</v>
+        <v>745400</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1063,36 +1063,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11305-11895</t>
+          <t>1280-1370</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10716.07142857143</v>
+        <v>1190</v>
       </c>
       <c r="F5" t="n">
-        <v>12767.85714285714</v>
+        <v>1495.892857142857</v>
       </c>
       <c r="G5" t="n">
-        <v>14044.64285714286</v>
+        <v>1645.482142857143</v>
       </c>
       <c r="H5" t="n">
-        <v>14805.35714285714</v>
+        <v>1789.642857142857</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.27%</t>
+          <t>17.78%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6.21</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-1912500</v>
+        <v>-5503000</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1114,40 +1114,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3149-3331</t>
+          <t>2037-2243</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2965.714285714286</v>
+        <v>1831.964285714286</v>
       </c>
       <c r="F6" t="n">
-        <v>3593.928571428572</v>
+        <v>2537.321428571428</v>
       </c>
       <c r="G6" t="n">
-        <v>3856.428571428572</v>
+        <v>2791.053571428572</v>
       </c>
       <c r="H6" t="n">
-        <v>4206.428571428572</v>
+        <v>3224.821428571428</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>26.44%</t>
+          <t>4.49%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>28.74</v>
+        <v>1.56</v>
       </c>
       <c r="L6" t="n">
-        <v>-2895500</v>
+        <v>56554200</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1157,48 +1157,48 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>823-877</t>
+          <t>2298-2382</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>768.5714285714286</v>
+        <v>2213.571428571428</v>
       </c>
       <c r="F7" t="n">
-        <v>958.5714285714286</v>
+        <v>2507.5</v>
       </c>
       <c r="G7" t="n">
-        <v>1040</v>
+        <v>2758.25</v>
       </c>
       <c r="H7" t="n">
-        <v>1148.571428571428</v>
+        <v>2800</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>23.94%</t>
+          <t>10.52%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>195.78</v>
+        <v>454.82</v>
       </c>
       <c r="L7" t="n">
-        <v>-21636100</v>
+        <v>10200200</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1216,36 +1216,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>277-311</t>
+          <t>1952-2068</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>243.3214285714286</v>
+        <v>1835.892857142857</v>
       </c>
       <c r="F8" t="n">
-        <v>360.3928571428572</v>
+        <v>2240.535714285714</v>
       </c>
       <c r="G8" t="n">
-        <v>396.4321428571429</v>
+        <v>2464.589285714286</v>
       </c>
       <c r="H8" t="n">
-        <v>475.8928571428572</v>
+        <v>2643.035714285714</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>61.35%</t>
+          <t>20.15%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>13.48</v>
+        <v>17.58</v>
       </c>
       <c r="L8" t="n">
-        <v>-104512900</v>
+        <v>-25253200</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1267,36 +1267,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>402-442</t>
+          <t>10055-10545</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>361.7857142857143</v>
+        <v>9566.071428571429</v>
       </c>
       <c r="F9" t="n">
-        <v>501.6428571428571</v>
+        <v>11225</v>
       </c>
       <c r="G9" t="n">
-        <v>551.8071428571428</v>
+        <v>12347.5</v>
       </c>
       <c r="H9" t="n">
-        <v>640.6428571428571</v>
+        <v>12812.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>38.27%</t>
+          <t>12.86%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>29.52</v>
+        <v>45.48</v>
       </c>
       <c r="L9" t="n">
-        <v>-2360900</v>
+        <v>-4000</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1318,20 +1318,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12161-12539</t>
+          <t>2823-2897</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>11782.14285714286</v>
+        <v>2749.642857142857</v>
       </c>
       <c r="F10" t="n">
-        <v>13104.46428571428</v>
+        <v>2998.571428571428</v>
       </c>
       <c r="G10" t="n">
-        <v>13669.64285714286</v>
+        <v>3236.071428571428</v>
       </c>
       <c r="H10" t="n">
-        <v>14423.21428571428</v>
+        <v>3298.428571428572</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1340,14 +1340,14 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18.33%</t>
+          <t>7.42%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7332136191.1</v>
+        <v>2818040467.88</v>
       </c>
       <c r="L10" t="n">
-        <v>328500</v>
+        <v>1793800</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1369,40 +1369,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1682-1838</t>
+          <t>2356-2444</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1527.5</v>
+        <v>2268.214285714286</v>
       </c>
       <c r="F11" t="n">
-        <v>2067.321428571428</v>
+        <v>2572.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2297.142857142857</v>
+        <v>2829.75</v>
       </c>
       <c r="H11" t="n">
-        <v>2603.571428571428</v>
+        <v>2872.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.19%</t>
+          <t>15.68%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1.55</v>
+        <v>56.96</v>
       </c>
       <c r="L11" t="n">
-        <v>56554200</v>
+        <v>-2979900</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BULL.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1420,40 +1420,40 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>474-526</t>
+          <t>4907-5053</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>420.9285714285714</v>
+        <v>4760.892857142857</v>
       </c>
       <c r="F12" t="n">
-        <v>602.1071428571429</v>
+        <v>5256.071428571429</v>
       </c>
       <c r="G12" t="n">
-        <v>662.3178571428572</v>
+        <v>5729.821428571429</v>
       </c>
       <c r="H12" t="n">
-        <v>778.8571428571429</v>
+        <v>5781.678571428572</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24.31%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>3.96</v>
+        <v>3.44</v>
       </c>
       <c r="L12" t="n">
-        <v>-2075700</v>
+        <v>33741800</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1463,48 +1463,48 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>594-646</t>
+          <t>3942-4158</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>541.25</v>
+        <v>3726.428571428572</v>
       </c>
       <c r="F13" t="n">
-        <v>723.3928571428571</v>
+        <v>4451.428571428572</v>
       </c>
       <c r="G13" t="n">
-        <v>795.7321428571429</v>
+        <v>4896.571428571429</v>
       </c>
       <c r="H13" t="n">
-        <v>903.3928571428571</v>
+        <v>5136.428571428572</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>17.80%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1.42</v>
+        <v>42.83</v>
       </c>
       <c r="L13" t="n">
-        <v>4580900</v>
+        <v>-30506300</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1514,44 +1514,44 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5209-5341</t>
+          <t>3325-3535</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5075.714285714285</v>
+        <v>3116.071428571428</v>
       </c>
       <c r="F14" t="n">
-        <v>5538.035714285715</v>
+        <v>3834.642857142857</v>
       </c>
       <c r="G14" t="n">
-        <v>5996.785714285715</v>
+        <v>4218.107142857143</v>
       </c>
       <c r="H14" t="n">
-        <v>6091.839285714286</v>
+        <v>4534.642857142857</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>23.35%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>3.48</v>
+        <v>8873218352.25</v>
       </c>
       <c r="L14" t="n">
-        <v>33741800</v>
+        <v>6595200</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1565,48 +1565,48 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>157-169</t>
+          <t>3755-4045</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>145.5357142857143</v>
+        <v>3465</v>
       </c>
       <c r="F15" t="n">
-        <v>185.9642857142857</v>
+        <v>4474.642857142857</v>
       </c>
       <c r="G15" t="n">
-        <v>203.1071428571429</v>
+        <v>4922.107142857143</v>
       </c>
       <c r="H15" t="n">
-        <v>225.9642857142857</v>
+        <v>5477.142857142857</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>39.51%</t>
+          <t>34.49%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>22.96</v>
+        <v>545.65</v>
       </c>
       <c r="L15" t="n">
-        <v>316433400</v>
+        <v>-1117600</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1616,44 +1616,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3652-3848</t>
+          <t>1759-1881</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3455.357142857143</v>
+        <v>1637.857142857143</v>
       </c>
       <c r="F16" t="n">
-        <v>4124.642857142857</v>
+        <v>2058.571428571428</v>
       </c>
       <c r="G16" t="n">
-        <v>4537.107142857143</v>
+        <v>2264.428571428572</v>
       </c>
       <c r="H16" t="n">
-        <v>4769.642857142857</v>
+        <v>2473.571428571428</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>21.28%</t>
+          <t>12.55%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>667.77</v>
+        <v>62.1</v>
       </c>
       <c r="L16" t="n">
-        <v>6595200</v>
+        <v>766200</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1667,44 +1667,44 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EMAS.JK</t>
+          <t>ARCI.JK</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8062-8588</t>
+          <t>1723-1817</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7537.5</v>
+        <v>1628.571428571428</v>
       </c>
       <c r="F17" t="n">
-        <v>9334.821428571429</v>
+        <v>1940.892857142857</v>
       </c>
       <c r="G17" t="n">
-        <v>10268.30357142857</v>
+        <v>2134.982142857143</v>
       </c>
       <c r="H17" t="n">
-        <v>11078.57142857143</v>
+        <v>2229.642857142857</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>28.33%</t>
+          <t>8.02%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>11331586348.94</v>
+        <v>3.86</v>
       </c>
       <c r="L17" t="n">
-        <v>-658500</v>
+        <v>-11431200</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1718,44 +1718,44 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>INKP.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3551-3789</t>
+          <t>9370-10080</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3312.142857142857</v>
+        <v>8658.928571428572</v>
       </c>
       <c r="F18" t="n">
-        <v>4145</v>
+        <v>11098.21428571429</v>
       </c>
       <c r="G18" t="n">
-        <v>4559.5</v>
+        <v>12208.03571428572</v>
       </c>
       <c r="H18" t="n">
-        <v>4975</v>
+        <v>13473.21428571429</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>33.12%</t>
+          <t>10.95%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>551.55</v>
+        <v>7.11</v>
       </c>
       <c r="L18" t="n">
-        <v>-1117600</v>
+        <v>-1912500</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1769,48 +1769,48 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>MBMA.JK</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1677-1773</t>
+          <t>674-746</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1580.892857142857</v>
+        <v>602.8571428571429</v>
       </c>
       <c r="F19" t="n">
-        <v>1917.142857142857</v>
+        <v>847.5</v>
       </c>
       <c r="G19" t="n">
-        <v>2108.857142857143</v>
+        <v>945</v>
       </c>
       <c r="H19" t="n">
-        <v>2253.392857142857</v>
+        <v>1085</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10.75%</t>
+          <t>18.78%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>56.06</v>
+        <v>26.51</v>
       </c>
       <c r="L19" t="n">
-        <v>766200</v>
+        <v>-73678300</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1828,36 +1828,36 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9066-9434</t>
+          <t>721-759</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8698.214285714286</v>
+        <v>682.1428571428571</v>
       </c>
       <c r="F20" t="n">
-        <v>9969.642857142857</v>
+        <v>814.4642857142858</v>
       </c>
       <c r="G20" t="n">
-        <v>10966.60714285714</v>
+        <v>895.9107142857144</v>
       </c>
       <c r="H20" t="n">
-        <v>11219.64285714286</v>
+        <v>943.2142857142858</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8.91%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>9.31</v>
+        <v>1.59</v>
       </c>
       <c r="L20" t="n">
-        <v>-4000</v>
+        <v>-4702400</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1871,44 +1871,44 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2576-2624</t>
+          <t>158-168</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2528.214285714286</v>
+        <v>148.2142857142857</v>
       </c>
       <c r="F21" t="n">
-        <v>2694.642857142857</v>
+        <v>182.3928571428571</v>
       </c>
       <c r="G21" t="n">
-        <v>2859.642857142857</v>
+        <v>196.8571428571428</v>
       </c>
       <c r="H21" t="n">
-        <v>2964.107142857143</v>
+        <v>216.1428571428571</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>47.29%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>32.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1793800</v>
+        <v>316433400</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2387,1555 +2387,1555 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>101.4</v>
+        <v>80.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-7.7%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>98</v>
       </c>
       <c r="C3" t="n">
-        <v>98.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>97</v>
       </c>
       <c r="C4" t="n">
-        <v>96.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-18.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>96</v>
       </c>
       <c r="C5" t="n">
-        <v>93</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-14.2%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>95</v>
       </c>
       <c r="C6" t="n">
-        <v>85.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-2.7%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>84.59999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-4.5%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>84</v>
+        <v>74.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>93</v>
       </c>
       <c r="C9" t="n">
-        <v>84</v>
+        <v>74.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-2.6%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>93</v>
       </c>
       <c r="C10" t="n">
-        <v>84</v>
+        <v>74.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-2.1%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>90</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-2.8%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BULL.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>89</v>
       </c>
       <c r="C12" t="n">
-        <v>81.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-7.3%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" t="n">
-        <v>79.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-14.9%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" t="n">
-        <v>75.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-12.9%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-8.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-8.8%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EMAS.JK</t>
+          <t>ARCI.JK</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>62.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-12.8%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>INKP.JK</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C18" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-19.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>MBMA.JK</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C19" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-21.5%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>69.8</v>
+        <v>56</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-1.3%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21" t="n">
-        <v>69.8</v>
+        <v>55</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MBMA.JK</t>
+          <t>BULL.JK</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>78</v>
       </c>
       <c r="C22" t="n">
-        <v>69</v>
+        <v>54.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-30.8%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>EMAS.JK</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C23" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-6.9%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C24" t="n">
-        <v>64.8</v>
+        <v>52</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-18.2%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>UNTR.JK</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C25" t="n">
-        <v>63.6</v>
+        <v>49.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-9.6%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AMMN.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-18.2%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LPKR.JK</t>
+          <t>HRUM.JK</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C27" t="n">
-        <v>59.8</v>
+        <v>49</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-14.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C28" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-5.9%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>70</v>
       </c>
       <c r="C29" t="n">
-        <v>56.2</v>
+        <v>48</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-15.4%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BRIS.JK</t>
+          <t>PSAB.JK</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>69</v>
       </c>
       <c r="C30" t="n">
-        <v>50.8</v>
+        <v>46.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-19.1%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HRUM.JK</t>
+          <t>SUPA.JK</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>68</v>
       </c>
       <c r="C31" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-28.0%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>45.6</v>
+        <v>40.6</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-7.1%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ARCI.JK</t>
+          <t>VKTR.JK</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C33" t="n">
-        <v>44.6</v>
+        <v>38.8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-39.8%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C34" t="n">
-        <v>43</v>
+        <v>35.4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-49.7%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C35" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-10.4%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C36" t="n">
-        <v>35.8</v>
+        <v>34</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-10.8%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>UNTR.JK</t>
+          <t>AMMN.JK</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C37" t="n">
-        <v>34.8</v>
+        <v>32</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-25.2%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>GTSI.JK</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>34.8</v>
+        <v>31.8</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-42.9%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>VKTR.JK</t>
+          <t>CPRO.JK</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C39" t="n">
-        <v>33.8</v>
+        <v>31</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-33.7%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>JPFA.JK</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C40" t="n">
-        <v>33.4</v>
+        <v>28.2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-22.2%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>HUMI.JK</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C41" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-39.3%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>TOBA.JK</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>56</v>
       </c>
       <c r="C42" t="n">
-        <v>28</v>
+        <v>26.8</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-34.4%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TOBA.JK</t>
+          <t>TPIA.JK</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C43" t="n">
-        <v>26.8</v>
+        <v>24.6</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-29.8%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>LPKR.JK</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C44" t="n">
-        <v>26.4</v>
+        <v>23.6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-28.1%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C45" t="n">
-        <v>25.4</v>
+        <v>23.4</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-63.3%</t>
+          <t>-45.4%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HUMI.JK</t>
+          <t>BBCA.JK</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C46" t="n">
-        <v>25</v>
+        <v>22.8</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-17.2%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TRIN.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>51</v>
       </c>
       <c r="C47" t="n">
-        <v>25</v>
+        <v>21.6</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-41.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>BRIS.JK</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C48" t="n">
-        <v>25</v>
+        <v>20.8</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TPIA.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C49" t="n">
-        <v>24.6</v>
+        <v>20.4</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-38.9%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GTSI.JK</t>
+          <t>AMRT.JK</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C50" t="n">
-        <v>21.8</v>
+        <v>19.8</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-22.5%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>DADA.JK</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C51" t="n">
-        <v>21.6</v>
+        <v>18.6</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-20.6%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RATU.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C52" t="n">
-        <v>20.4</v>
+        <v>18</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-16.9%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EXCL.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C53" t="n">
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-14.9%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AMRT.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C54" t="n">
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-20.0%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C55" t="n">
-        <v>19</v>
+        <v>17.4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-49.9%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>BBYB.JK</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C56" t="n">
-        <v>18</v>
+        <v>17.4</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-46.8%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BBCA.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C57" t="n">
-        <v>17.8</v>
+        <v>16.8</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-18.8%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BBYB.JK</t>
+          <t>GOTO.JK</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C58" t="n">
-        <v>17.4</v>
+        <v>16.8</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-36.9%</t>
+          <t>-19.7%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GOTO.JK</t>
+          <t>EMTK.JK</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C59" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-46.9%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EMTK.JK</t>
+          <t>BUMI.JK</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C60" t="n">
-        <v>16.2</v>
+        <v>15</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-39.5%</t>
+          <t>-49.6%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>ICBP.JK</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C61" t="n">
         <v>15</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-12.8%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C62" t="n">
-        <v>11.8</v>
+        <v>15</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-38.8%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NICL.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C63" t="n">
-        <v>10.8</v>
+        <v>13.2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-41.2%</t>
+          <t>-44.2%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DADA.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C64" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-32.8%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>NICL.JK</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C65" t="n">
-        <v>8.4</v>
+        <v>10.8</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-40.1%</t>
+          <t>-47.9%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>COIN.JK</t>
+          <t>DEWA.JK</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C66" t="n">
-        <v>7.8</v>
+        <v>10.6</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-64.8%</t>
+          <t>-42.8%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PBSA.JK</t>
+          <t>BBKP.JK</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C67" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-51.5%</t>
+          <t>-30.9%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C68" t="n">
-        <v>7.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-41.6%</t>
+          <t>-11.7%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C69" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-46.5%</t>
+          <t>-54.0%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PNLF.JK</t>
+          <t>COIN.JK</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-70.5%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CPRO.JK</t>
+          <t>PBSA.JK</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-54.3%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C72" t="n">
-        <v>5.399999999999999</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-52.5%</t>
+          <t>-50.4%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>23</v>
       </c>
       <c r="C73" t="n">
-        <v>5.399999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-55.9%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>IRSX.JK</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>23</v>
       </c>
       <c r="C74" t="n">
-        <v>5.399999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-59.6%</t>
+          <t>-40.4%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>PNLF.JK</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C75" t="n">
-        <v>5.399999999999999</v>
+        <v>6</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-25.1%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C76" t="n">
         <v>5.399999999999999</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-58.9%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C77" t="n">
         <v>5.399999999999999</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-35.1%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C78" t="n">
         <v>5.399999999999999</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-67.7%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>WIFI.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C79" t="n">
-        <v>4.8</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-39.5%</t>
+          <t>-54.2%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DEWA.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C80" t="n">
-        <v>3.6</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-54.3%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-24.2%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TRUE.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-58.5%</t>
+          <t>-62.2%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>WIFI.JK</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C83" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-44.4%</t>
+          <t>-49.2%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DSSA.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C84" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-30.1%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PSAB.JK</t>
+          <t>SSIA.JK</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C85" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-39.7%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BUMI.JK</t>
+          <t>DSSA.JK</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-44.4%</t>
+          <t>-35.5%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>RMKE.JK</t>
+          <t>EXCL.JK</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-55.6%</t>
+          <t>-37.2%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ICBP.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3946,14 +3946,14 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-51.2%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BBKP.JK</t>
+          <t>RMKE.JK</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -3964,61 +3964,97 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-62.9%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BKSL.JK</t>
+          <t>TRUE.JK</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C90" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-66.0%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>BKSL.JK</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C91" t="n">
-        <v>-3</v>
+        <v>-1.2</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-36.6%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SSIA.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C92" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-47.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>OASA.JK</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>3</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>-38.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TRIN.JK</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>3</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>-51.4%</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4085,7 +4121,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4093,7 +4129,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -4101,17 +4137,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1502-1578</t>
+          <t>2909-3091</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5503000</t>
+          <t>-2895500</t>
         </is>
       </c>
     </row>
@@ -4122,25 +4158,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7714-8086</t>
+          <t>158-168</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>197</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>745400</t>
+          <t>316433400</t>
         </is>
       </c>
     </row>
@@ -4151,25 +4187,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>VKTR.JK</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11305-11895</t>
+          <t>728-832</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1912500</t>
+          <t>-2430100</t>
         </is>
       </c>
     </row>
@@ -4180,25 +4216,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3652-3848</t>
+          <t>224-268</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>380</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6595200</t>
+          <t>7483200</t>
         </is>
       </c>
     </row>
@@ -4209,32 +4245,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EMAS.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8062-8588</t>
+          <t>268-316</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>450</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-658500</t>
+          <t>-4347200</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4242,25 +4278,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2354-2426</t>
+          <t>840-910</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10200200</t>
+          <t>-21636100</t>
         </is>
       </c>
     </row>
@@ -4271,25 +4307,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>402-442</t>
+          <t>2037-2243</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2360900</t>
+          <t>56554200</t>
         </is>
       </c>
     </row>
@@ -4300,25 +4336,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1014-1086</t>
+          <t>10055-10545</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-7662000</t>
+          <t>-4000</t>
         </is>
       </c>
     </row>
@@ -4329,25 +4365,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8070-8380</t>
+          <t>2823-2897</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-65600</t>
+          <t>1793800</t>
         </is>
       </c>
     </row>
@@ -4358,32 +4394,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1068-1102</t>
+          <t>2356-2444</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2798000</t>
+          <t>-2979900</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4391,25 +4427,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3149-3331</t>
+          <t>6238-6712</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2895500</t>
+          <t>745400</t>
         </is>
       </c>
     </row>
@@ -4420,25 +4456,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>157-169</t>
+          <t>1280-1370</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>316433400</t>
+          <t>-5503000</t>
         </is>
       </c>
     </row>
@@ -4449,25 +4485,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>262-302</t>
+          <t>1952-2068</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7483200</t>
+          <t>-25253200</t>
         </is>
       </c>
     </row>
@@ -4478,25 +4514,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>365-411</t>
+          <t>3942-4158</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>4897</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-4347200</t>
+          <t>-30506300</t>
         </is>
       </c>
     </row>
@@ -4507,32 +4543,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VKTR.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>896-994</t>
+          <t>3325-3535</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2430100</t>
+          <t>6595200</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -4540,25 +4576,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>823-877</t>
+          <t>2298-2382</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-21636100</t>
+          <t>10200200</t>
         </is>
       </c>
     </row>
@@ -4569,25 +4605,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1682-1838</t>
+          <t>1022-1058</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2297</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>56554200</t>
+          <t>-2798000</t>
         </is>
       </c>
     </row>
@@ -4598,25 +4634,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3551-3789</t>
+          <t>3851-4269</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1117600</t>
+          <t>-128900</t>
         </is>
       </c>
     </row>
@@ -4627,25 +4663,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1677-1773</t>
+          <t>860-930</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>766200</t>
+          <t>-7662000</t>
         </is>
       </c>
     </row>
@@ -4656,32 +4692,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>9066-9434</t>
+          <t>7246-7604</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-4000</t>
+          <t>-65600</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -4689,25 +4725,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>277-311</t>
+          <t>4907-5053</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-104512900</t>
+          <t>33741800</t>
         </is>
       </c>
     </row>
@@ -4718,25 +4754,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12161-12539</t>
+          <t>1598-1692</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>328500</t>
+          <t>-1514600</t>
         </is>
       </c>
     </row>
@@ -4747,25 +4783,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BULL.JK</t>
+          <t>SUPA.JK</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>474-526</t>
+          <t>854-916</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2075700</t>
+          <t>724900</t>
         </is>
       </c>
     </row>
@@ -4776,25 +4812,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6588-6762</t>
+          <t>3653-3727</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6227500</t>
+          <t>105416300</t>
         </is>
       </c>
     </row>
@@ -4805,32 +4841,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HUMI.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>222-246</t>
+          <t>4112-4188</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-571700</t>
+          <t>8426900</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -4838,25 +4874,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>BULL.JK</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>594-646</t>
+          <t>446-502</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>639</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4580900</t>
+          <t>-2075700</t>
         </is>
       </c>
     </row>
@@ -4867,25 +4903,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GOTO.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>60-62</t>
+          <t>242-278</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>365</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.1B</t>
+          <t>-104512900</t>
         </is>
       </c>
     </row>
@@ -4896,236 +4932,232 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>WIFI.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2499-2641</t>
+          <t>11415-11835</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2694000</t>
+          <t>328500</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>GTSI.JK</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5209-5341</t>
+          <t>257-291</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>375</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>33741800</t>
+          <t>-3409300</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>HUMI.JK</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3875-3945</t>
+          <t>201-231</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>105416300</t>
+          <t>-571700</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>136-156</t>
+          <t>341-351</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>394</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1255200</t>
+          <t>37538300</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BRIS.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2330-2390</t>
+          <t>5015-5285</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1137600</t>
+          <t>81700</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1781-1859</t>
+          <t>8182-8718</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>10435</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1514600</t>
+          <t>-202100</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LPKR.JK</t>
+          <t>DADA.JK</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>103-109</t>
+          <t>50-50</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-266800</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>TRUE.JK</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1086-1114</t>
+          <t>163-197</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>295</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-34214900</t>
+          <t>314000</t>
         </is>
       </c>
     </row>
@@ -5140,25 +5172,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>CPRO.JK</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2338-2422</t>
+          <t>56-58</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>69</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2865100</t>
+          <t>12850400</t>
         </is>
       </c>
     </row>
@@ -5169,25 +5201,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>JPFA.JK</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6385-6515</t>
+          <t>2230-2330</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-8356000</t>
+          <t>5002500</t>
         </is>
       </c>
     </row>
@@ -5198,25 +5230,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>AMRT.JK</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2338-2422</t>
+          <t>1516-1584</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>5002500</t>
+          <t>37773100</t>
         </is>
       </c>
     </row>
@@ -5227,25 +5259,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AMRT.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1635-1705</t>
+          <t>6054-6196</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>37773100</t>
+          <t>-8356000</t>
         </is>
       </c>
     </row>
@@ -5256,32 +5288,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CPRO.JK</t>
+          <t>ICBP.JK</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>62-64</t>
+          <t>7371-7579</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>12850400</t>
+          <t>-1298800</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -5289,25 +5321,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>LPKR.JK</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2264-2356</t>
+          <t>88-96</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>116</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4049500</t>
+          <t>-266800</t>
         </is>
       </c>
     </row>
@@ -5318,261 +5350,298 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EXCL.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3089-3251</t>
+          <t>1000-1030</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4119100</t>
+          <t>-34214900</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EMTK.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>868-912</t>
+          <t>3144-3256</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-5460200</t>
+          <t>13783000</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>EMTK.JK</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3493-3587</t>
+          <t>758-802</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>953</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>13783000</t>
+          <t>-5460200</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>ISAT.JK</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>29</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2132-2228</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2605</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>4049500</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>INET.JK</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>23</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>362-394</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="D47" t="n">
+        <v>20</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>286-318</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>-15489100</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>PWON.JK</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>57</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>362-370</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>37538300</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TRIN.JK</t>
+          <t>EXCL.JK</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>972-1068</t>
+          <t>2732-2908</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3499700</t>
+          <t>4119100</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DADA.JK</t>
+          <t>GOTO.JK</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>50-50</t>
+          <t>56-58</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.1B</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>IRSX.JK</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>5502-5798</t>
+          <t>439-497</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>664</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>81700</t>
+          <t>4580900</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>WIFI.JK</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>9198-9852</t>
+          <t>2086-2234</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-202100</t>
+          <t>-2694000</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>RLCO.JK</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>33</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>5478-6222</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>8053</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-15000</t>
         </is>
       </c>
     </row>
@@ -5819,10 +5888,10 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5909,16 +5978,16 @@
         <v>0.38872</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>8.741258999999999</v>
+        <v>8.254189500000001</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>1.6745117</v>
+        <v>1.580866</v>
       </c>
       <c r="J2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>603.46</v>
+        <v>603.33</v>
       </c>
     </row>
     <row r="3">
@@ -5948,16 +6017,16 @@
         <v>0.34335998</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>10.330464</v>
+        <v>8.722222</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>1.2013952</v>
+        <v>1.0140808</v>
       </c>
       <c r="J3" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>36.01</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -5987,16 +6056,16 @@
         <v>0.43205002</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7.2777824</v>
+        <v>6.3756747</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>1.3903273</v>
+        <v>1.2184892</v>
       </c>
       <c r="J4" s="14" t="n">
         <v>2.444</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>122.29</v>
+        <v>122.34</v>
       </c>
     </row>
     <row r="5">
@@ -6017,25 +6086,25 @@
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.17468001</v>
+        <v>0.17465</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.264</v>
+        <v>0.17</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0.25638</v>
+        <v>0.40405998</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>10.537379</v>
+        <v>9.946896000000001</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>1.8180939</v>
+        <v>1.7149916</v>
       </c>
       <c r="J5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>371.06</v>
+        <v>370.97</v>
       </c>
     </row>
     <row r="6">
@@ -6044,76 +6113,76 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0.25308</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>0.27552</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>10.460251</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>2.3364198</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>23.671</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>126.67</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>JPFA.JK</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
-        <v>0.24911</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>4.381</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>0.71615</v>
-      </c>
-      <c r="H6" t="n">
-        <v>38.120106</v>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>9.130706999999999</v>
-      </c>
-      <c r="J6" s="14" t="n">
-        <v>5.093</v>
-      </c>
-      <c r="K6" s="11" t="n">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NCKL.JK</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>19</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0.25308</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>0.27552</v>
-      </c>
-      <c r="H7" t="n">
-        <v>12.15086</v>
-      </c>
-      <c r="I7" s="15" t="n">
-        <v>2.715537</v>
+      <c r="E7" s="13" t="n">
+        <v>0.23401</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0.06594999999999999</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>7.944804</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>1.4325405</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>23.671</v>
+        <v>59.254</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>126.74</v>
+        <v>286.98</v>
       </c>
     </row>
     <row r="8">
@@ -6122,11 +6191,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6134,25 +6203,25 @@
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0.20716</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>0.05786</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>8.291816000000001</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>1.6271101</v>
+        <v>0.24911</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>4.381</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>0.71615</v>
+      </c>
+      <c r="H8" t="n">
+        <v>29.057592</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>6.9418387</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>62.876</v>
+        <v>5.093</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>287.03</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="9">
@@ -6182,16 +6251,16 @@
         <v>0.31919</v>
       </c>
       <c r="H9" t="n">
-        <v>14.388489</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>2.095457</v>
+        <v>12.9925585</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>1.8912387</v>
       </c>
       <c r="J9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>164.02</v>
+        <v>163.94</v>
       </c>
     </row>
     <row r="10">
@@ -6221,55 +6290,55 @@
         <v>0.27632</v>
       </c>
       <c r="H10" t="n">
-        <v>21.459229</v>
+        <v>19.024391</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>14.084507</v>
+        <v>12.483995</v>
       </c>
       <c r="J10" s="11" t="n">
         <v>0.378</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>51.26</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>HRTA.JK</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="13" t="n">
         <v>0.28483</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="13" t="n">
         <v>1.009</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="13" t="n">
         <v>0.023759998</v>
       </c>
-      <c r="H11" t="n">
-        <v>20.833332</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>5.2929325</v>
+      <c r="H11" s="12" t="n">
+        <v>19.301294</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>4.9008636</v>
       </c>
       <c r="J11" s="14" t="n">
         <v>139.825</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>155.52</v>
+        <v>155.43</v>
       </c>
     </row>
     <row r="12">
@@ -6299,16 +6368,16 @@
         <v>0.048460003</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>9.000423</v>
+        <v>9.271032</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>1.206247</v>
+        <v>1.2417248</v>
       </c>
       <c r="J12" s="14" t="n">
         <v>4.935</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>94.44</v>
+        <v>94.38</v>
       </c>
     </row>
     <row r="13">
@@ -6338,55 +6407,55 @@
         <v>0.21154</v>
       </c>
       <c r="H13" t="n">
-        <v>32.895885</v>
+        <v>31.00911</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>134285.7</v>
+        <v>126428.57</v>
       </c>
       <c r="J13" s="14" t="n">
         <v>118.6</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>57.15</v>
+        <v>57.08</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>TPIA.JK</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="13" t="n">
         <v>0.42018002</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="13" t="n">
         <v>4.295</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="13" t="n">
         <v>0.2208</v>
       </c>
-      <c r="H14" t="n">
-        <v>22.075054</v>
+      <c r="H14" s="12" t="n">
+        <v>17.594633</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>148888.89</v>
+        <v>118888.88</v>
       </c>
       <c r="J14" s="14" t="n">
         <v>82.7</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>303.51</v>
+        <v>304.07</v>
       </c>
     </row>
     <row r="15">
@@ -6395,7 +6464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -6407,25 +6476,25 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.102419995</v>
+        <v>0.1173</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>0.144</v>
+        <v>0.028</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0.30543</v>
+        <v>0.40232</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>8.243243</v>
+        <v>7.727112</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.8071595</v>
-      </c>
-      <c r="J15" s="14" t="n">
-        <v>21.136</v>
+        <v>0.90034115</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>44.4</v>
+        <v>537.0700000000001</v>
       </c>
     </row>
     <row r="16">
@@ -6434,7 +6503,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -6446,25 +6515,25 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.1173</v>
+        <v>0.102419995</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.028</v>
+        <v>0.144</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0.40232</v>
+        <v>0.30543</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>8.196721</v>
+        <v>7.789284</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.9545786000000001</v>
-      </c>
-      <c r="J16" s="11" t="n">
-        <v>0</v>
+        <v>0.7630524</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>21.136</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>536.8</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="17">
@@ -6494,16 +6563,16 @@
         <v>0.06239</v>
       </c>
       <c r="H17" s="17" t="n">
-        <v>79.36508000000001</v>
+        <v>64.69824</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>30268.2</v>
+        <v>24808.428</v>
       </c>
       <c r="J17" s="11" t="n">
         <v>0.173</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>99.54000000000001</v>
+        <v>100.08</v>
       </c>
     </row>
     <row r="18">
@@ -6512,7 +6581,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -6524,25 +6593,25 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.15277</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>0.09748999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>0.52018</v>
       </c>
       <c r="H18" t="n">
-        <v>13.513514</v>
+        <v>18.867924</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>2.05118</v>
+        <v>3.2115743</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>138.994</v>
+        <v>2.39</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>170.94</v>
+        <v>272.95</v>
       </c>
     </row>
     <row r="19">
@@ -6551,7 +6620,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -6563,25 +6632,25 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>0.52018</v>
+        <v>0.15277</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>0.09748999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>20.703554</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>3.5233777</v>
+        <v>12.761225</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>1.9357456</v>
       </c>
       <c r="J19" s="14" t="n">
-        <v>2.39</v>
+        <v>138.994</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>272.9</v>
+        <v>170.83</v>
       </c>
     </row>
     <row r="20">
@@ -6590,7 +6659,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>BBCA.JK</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -6601,26 +6670,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E20" s="16" t="n">
-        <v>-0.04084</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>-0.69613</v>
+      <c r="E20" s="8" t="n">
+        <v>0.21143</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>0.53282</v>
       </c>
       <c r="H20" t="n">
+        <v>14.723204</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>3.0046723</v>
+      </c>
+      <c r="J20" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="14" t="n">
-        <v>15.179375</v>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="K20" s="15" t="n">
-        <v>-0.7</v>
+      <c r="K20" s="11" t="n">
+        <v>466.95</v>
       </c>
     </row>
     <row r="21">
@@ -6629,7 +6698,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BBCA.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -6640,26 +6709,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E21" s="8" t="n">
-        <v>0.21143</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>-0.027</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>0.53282</v>
+      <c r="E21" s="16" t="n">
+        <v>-0.04084</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>-0.69613</v>
       </c>
       <c r="H21" t="n">
-        <v>15.361066</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>3.1357853</v>
+        <v>0</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>11.423653</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="11" t="n">
-        <v>467.09</v>
+        <v>0.049</v>
+      </c>
+      <c r="K21" s="15" t="n">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="22">
@@ -6689,16 +6758,16 @@
         <v>0.30952</v>
       </c>
       <c r="H22" s="17" t="n">
-        <v>262.94498</v>
+        <v>216.5605</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>13.178383</v>
+        <v>11.029293</v>
       </c>
       <c r="J22" s="11" t="n">
         <v>0.261</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>6.18</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="23">
@@ -6728,16 +6797,16 @@
         <v>0.15842</v>
       </c>
       <c r="H23" t="n">
-        <v>16.862644</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>5.1016817</v>
+        <v>15.88942</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>4.8084817</v>
       </c>
       <c r="J23" s="15" t="n">
         <v>1.461</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>77.39</v>
+        <v>77.41</v>
       </c>
     </row>
     <row r="24">
@@ -6767,16 +6836,16 @@
         <v>0.13921</v>
       </c>
       <c r="H24" s="17" t="n">
-        <v>77.51938</v>
+        <v>64.36837</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>533333.3</v>
+        <v>445000</v>
       </c>
       <c r="J24" s="14" t="n">
         <v>201.586</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>20.64</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="25">
@@ -6785,7 +6854,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -6797,25 +6866,25 @@
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.12082</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>0.008</v>
+        <v>0.12380999</v>
+      </c>
+      <c r="F25" s="16" t="n">
+        <v>-0.075</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.0806</v>
-      </c>
-      <c r="H25" s="10" t="n">
-        <v>11.037731</v>
+        <v>0.18375</v>
+      </c>
+      <c r="H25" t="n">
+        <v>28.705566</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>20964.912</v>
+        <v>62941.17</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>32.802</v>
+        <v>51.917</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>216.53</v>
+        <v>74.55</v>
       </c>
     </row>
     <row r="26">
@@ -6824,7 +6893,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -6836,25 +6905,25 @@
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.11936</v>
-      </c>
-      <c r="F26" s="16" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0.12082</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>0.008</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.06455</v>
-      </c>
-      <c r="H26" s="17" t="n">
-        <v>62.124252</v>
+        <v>0.0806</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>10.785398</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>12.849741</v>
-      </c>
-      <c r="J26" s="11" t="n">
-        <v>0.216</v>
+        <v>20526.316</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>32.802</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>9.98</v>
+        <v>216.96</v>
       </c>
     </row>
     <row r="27">
@@ -6884,16 +6953,16 @@
         <v>0.10163</v>
       </c>
       <c r="H27" t="n">
-        <v>14.367817</v>
+        <v>13.252383</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>2.169561</v>
+        <v>2.001913</v>
       </c>
       <c r="J27" s="14" t="n">
         <v>2.102</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>76.56</v>
+        <v>76.59</v>
       </c>
     </row>
     <row r="28">
@@ -6923,16 +6992,16 @@
         <v>0.09752</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>18.181818</v>
+        <v>14.95668</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>82916.664</v>
+        <v>68333.336</v>
       </c>
       <c r="J28" s="14" t="n">
         <v>107.818</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>109.45</v>
+        <v>109.65</v>
       </c>
     </row>
     <row r="29">
@@ -6941,11 +7010,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PNLF.JK</t>
+          <t>IRSX.JK</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6953,25 +7022,25 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.05041</v>
+        <v>0.11936</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.15737</v>
-      </c>
-      <c r="H29" s="10" t="n">
-        <v>5.2437363</v>
-      </c>
-      <c r="I29" s="11" t="n">
-        <v>0.27760157</v>
+        <v>0.06455</v>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>55.384617</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>9.699482</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>51.49</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -7001,10 +7070,10 @@
         <v>0.041550003</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>9.130435</v>
+        <v>8.260869</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>0.9399618</v>
+        <v>0.8504416299999999</v>
       </c>
       <c r="J30" s="14" t="n">
         <v>43.245</v>
@@ -7019,37 +7088,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>PNLF.JK</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>-0.29015</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>0.671</v>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>0.05041</v>
+      </c>
+      <c r="F31" s="16" t="n">
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>-0.21053</v>
-      </c>
-      <c r="H31" t="n">
+        <v>0.15737</v>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>4.856255</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>0.25703847</v>
+      </c>
+      <c r="J31" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="15" t="n">
-        <v>4.715777</v>
-      </c>
-      <c r="J31" s="14" t="n">
-        <v>65.76600000000001</v>
-      </c>
-      <c r="K31" s="15" t="n">
-        <v>0</v>
+      <c r="K31" s="11" t="n">
+        <v>51.48</v>
       </c>
     </row>
     <row r="32">
@@ -7079,16 +7148,16 @@
         <v>0.31559</v>
       </c>
       <c r="H32" s="17" t="n">
-        <v>70.92198999999999</v>
+        <v>58.088234</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>423529.38</v>
+        <v>348529.4</v>
       </c>
       <c r="J32" s="14" t="n">
         <v>36.548</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>101.52</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33">
@@ -7097,7 +7166,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -7109,25 +7178,25 @@
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.05801</v>
+        <v>0.0678</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>0.01754</v>
-      </c>
-      <c r="H33" t="n">
-        <v>36.101616</v>
+        <v>0.946</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>0.24195999</v>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>154.45074</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>255208.33</v>
+        <v>6.351526</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>276.511</v>
+        <v>2.054</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>169.66</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="34">
@@ -7136,7 +7205,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -7148,25 +7217,25 @@
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.045900002</v>
+        <v>0.05801</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0.329</v>
+        <v>0.317</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.19652</v>
-      </c>
-      <c r="H34" s="17" t="n">
-        <v>175.40686</v>
+        <v>0.01754</v>
+      </c>
+      <c r="H34" t="n">
+        <v>31.159975</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>107777.78</v>
+        <v>220833.33</v>
       </c>
       <c r="J34" s="14" t="n">
-        <v>12.694</v>
+        <v>276.511</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>5.53</v>
+        <v>170.09</v>
       </c>
     </row>
     <row r="35">
@@ -7175,7 +7244,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -7187,25 +7256,25 @@
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.06432</v>
+        <v>0.045900002</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>1.905</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>0.24544</v>
+        <v>0.329</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>0.19652</v>
       </c>
       <c r="H35" s="17" t="n">
-        <v>270</v>
+        <v>152.05724</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>9.300494</v>
+        <v>94444.44500000001</v>
       </c>
       <c r="J35" s="14" t="n">
-        <v>2.833</v>
+        <v>12.694</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>1.4</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="36">
@@ -7214,7 +7283,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -7225,26 +7294,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E36" s="8" t="n">
-        <v>0.23723</v>
-      </c>
-      <c r="F36" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="G36" s="9" t="n">
-        <v>0.14588</v>
+      <c r="E36" s="9" t="n">
+        <v>0.06432</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>1.905</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>0.24544</v>
       </c>
       <c r="H36" s="17" t="n">
-        <v>192.3077</v>
+        <v>215.7143</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>41.086205</v>
+        <v>7.4305534</v>
       </c>
       <c r="J36" s="14" t="n">
-        <v>38.133</v>
+        <v>2.833</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>11.18</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="37">
@@ -7253,7 +7322,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -7264,26 +7333,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="8" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="G37" s="8" t="n">
-        <v>0.65328</v>
+      <c r="E37" s="8" t="n">
+        <v>0.23723</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>0.14588</v>
       </c>
       <c r="H37" s="17" t="n">
-        <v>90.05146000000001</v>
+        <v>167.72151</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>131250</v>
+        <v>35.448795</v>
       </c>
       <c r="J37" s="14" t="n">
-        <v>34.873</v>
+        <v>38.133</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>11.66</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="38">
@@ -7292,7 +7361,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -7304,25 +7373,25 @@
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.0678</v>
+        <v>0</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.946</v>
+        <v>0.421</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>0.24195999</v>
+        <v>0.65328</v>
       </c>
       <c r="H38" s="17" t="n">
-        <v>172.3982</v>
+        <v>76.62671</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>7.1595597</v>
+        <v>111874.99</v>
       </c>
       <c r="J38" s="14" t="n">
-        <v>2.054</v>
+        <v>34.873</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>55.25</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="39">
@@ -7352,16 +7421,16 @@
         <v>0.23266001</v>
       </c>
       <c r="H39" s="17" t="n">
-        <v>454.4199</v>
+        <v>408.41583</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>1645000</v>
+        <v>1485000</v>
       </c>
       <c r="J39" s="14" t="n">
         <v>239.827</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>18.1</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="40">
@@ -7370,37 +7439,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="E40" s="8" t="n">
-        <v>0.22769</v>
-      </c>
-      <c r="F40" s="16" t="n">
-        <v>-0.132</v>
+      <c r="E40" s="16" t="n">
+        <v>-0.29015</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>0.671</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.14828</v>
-      </c>
-      <c r="H40" s="10" t="n">
-        <v>5.931198</v>
-      </c>
-      <c r="I40" s="14" t="n">
-        <v>20786.518</v>
+        <v>-0.21053</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>4.8576045</v>
       </c>
       <c r="J40" s="14" t="n">
-        <v>27.582</v>
-      </c>
-      <c r="K40" s="11" t="n">
-        <v>1559.55</v>
+        <v>65.76600000000001</v>
+      </c>
+      <c r="K40" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -7409,7 +7478,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -7420,26 +7489,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E41" s="9" t="n">
-        <v>0.15961</v>
+      <c r="E41" s="8" t="n">
+        <v>0.2018</v>
       </c>
       <c r="F41" s="16" t="n">
         <v>-0.012</v>
       </c>
-      <c r="G41" s="9" t="n">
-        <v>0.075219996</v>
-      </c>
-      <c r="H41" s="10" t="n">
-        <v>9.157508999999999</v>
-      </c>
-      <c r="I41" s="11" t="n">
-        <v>1.4488126</v>
+      <c r="G41" s="8" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="H41" t="n">
+        <v>15.727699</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>54324.324</v>
       </c>
       <c r="J41" s="14" t="n">
-        <v>19.582</v>
+        <v>35.836</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>283.92</v>
+        <v>127.8</v>
       </c>
     </row>
   </sheetData>

--- a/reports/HEDGEFUND_TERMINAL.xlsx
+++ b/reports/HEDGEFUND_TERMINAL.xlsx
@@ -491,7 +491,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>04 March 2026</t>
+          <t>06 March 2026</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7"/>
@@ -572,7 +572,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.9M</t>
+          <t>1.8M</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-21.6M</t>
+          <t>-2.9M</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -625,7 +625,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>745400</t>
+          <t>-21.6M</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -650,7 +650,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-5.5M</t>
+          <t>10.2M</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -675,7 +675,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>56.6M</t>
+          <t>-4000</t>
         </is>
       </c>
     </row>
@@ -727,41 +727,41 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>67.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-165.8M</t>
+          <t>-166.6M</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2. Energy</t>
+          <t>2. Consumer Cyclical</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>60.4</v>
+        <v>63.8</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-494.1M</t>
+          <t>297.8M</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3. Consumer Cyclical</t>
+          <t>3. Energy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52.7</v>
+        <v>61</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>297.8M</t>
+          <t>-494.1M</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52.5</v>
+        <v>56.5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>51.8</v>
+        <v>45.7</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -902,7 +902,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -910,40 +910,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2909-3091</t>
+          <t>2939-3021</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2726.785714285714</v>
+        <v>2856.785714285714</v>
       </c>
       <c r="F2" t="n">
-        <v>3341.785714285714</v>
+        <v>3135.714285714286</v>
       </c>
       <c r="G2" t="n">
-        <v>3675.964285714286</v>
+        <v>3250.357142857143</v>
       </c>
       <c r="H2" t="n">
-        <v>3926.785714285714</v>
+        <v>3403.214285714286</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>25.36%</t>
+          <t>8.09%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>26.27</v>
+        <v>3073934999.61</v>
       </c>
       <c r="L2" t="n">
-        <v>-2895500</v>
+        <v>1793800</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -961,36 +961,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>840-910</t>
+          <t>2659-2861</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>770.5357142857143</v>
+        <v>2455.714285714286</v>
       </c>
       <c r="F3" t="n">
-        <v>1011.607142857143</v>
+        <v>3137.857142857143</v>
       </c>
       <c r="G3" t="n">
-        <v>1112.767857142857</v>
+        <v>3451.642857142858</v>
       </c>
       <c r="H3" t="n">
-        <v>1249.107142857143</v>
+        <v>3782.857142857143</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.45%</t>
+          <t>24.58%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10812872355.39</v>
+        <v>25.5</v>
       </c>
       <c r="L3" t="n">
-        <v>-21636100</v>
+        <v>-2895500</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1012,40 +1012,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6238-6712</t>
+          <t>813-887</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5765.178571428572</v>
+        <v>739.6428571428571</v>
       </c>
       <c r="F4" t="n">
-        <v>7338.392857142857</v>
+        <v>994.4642857142858</v>
       </c>
       <c r="G4" t="n">
-        <v>8072.232142857143</v>
+        <v>1093.910714285714</v>
       </c>
       <c r="H4" t="n">
-        <v>8800.892857142857</v>
+        <v>1245.714285714286</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>28.58%</t>
+          <t>29.50%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>691.24</v>
+        <v>11208588751.85</v>
       </c>
       <c r="L4" t="n">
-        <v>745400</v>
+        <v>-21636100</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1063,40 +1063,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1280-1370</t>
+          <t>2324-2416</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1190</v>
+        <v>2231.785714285714</v>
       </c>
       <c r="F5" t="n">
-        <v>1495.892857142857</v>
+        <v>2552.142857142857</v>
       </c>
       <c r="G5" t="n">
-        <v>1645.482142857143</v>
+        <v>2807.357142857143</v>
       </c>
       <c r="H5" t="n">
-        <v>1789.642857142857</v>
+        <v>2869.642857142857</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17.78%</t>
+          <t>10.69%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>76.26000000000001</v>
+        <v>461.97</v>
       </c>
       <c r="L5" t="n">
-        <v>-5503000</v>
+        <v>10200200</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1114,40 +1114,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2037-2243</t>
+          <t>10044-10556</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1831.964285714286</v>
+        <v>9531.25</v>
       </c>
       <c r="F6" t="n">
-        <v>2537.321428571428</v>
+        <v>11271.42857142857</v>
       </c>
       <c r="G6" t="n">
-        <v>2791.053571428572</v>
+        <v>12398.57142857143</v>
       </c>
       <c r="H6" t="n">
-        <v>3224.821428571428</v>
+        <v>12940.17857142857</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.49%</t>
+          <t>14.26%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.56</v>
+        <v>68.78</v>
       </c>
       <c r="L6" t="n">
-        <v>56554200</v>
+        <v>-4000</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1157,48 +1157,48 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2298-2382</t>
+          <t>2356-2444</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2213.571428571428</v>
+        <v>2267.142857142857</v>
       </c>
       <c r="F7" t="n">
-        <v>2507.5</v>
+        <v>2572.857142857143</v>
       </c>
       <c r="G7" t="n">
-        <v>2758.25</v>
+        <v>2830.142857142857</v>
       </c>
       <c r="H7" t="n">
-        <v>2800</v>
+        <v>2872.857142857143</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10.52%</t>
+          <t>15.22%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>454.82</v>
+        <v>55.29</v>
       </c>
       <c r="L7" t="n">
-        <v>10200200</v>
+        <v>-2979900</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1216,36 +1216,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1952-2068</t>
+          <t>3936-4144</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1835.892857142857</v>
+        <v>3728.214285714286</v>
       </c>
       <c r="F8" t="n">
-        <v>2240.535714285714</v>
+        <v>4420.357142857143</v>
       </c>
       <c r="G8" t="n">
-        <v>2464.589285714286</v>
+        <v>4862.392857142858</v>
       </c>
       <c r="H8" t="n">
-        <v>2643.035714285714</v>
+        <v>5065.357142857143</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20.15%</t>
+          <t>16.58%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>17.58</v>
+        <v>39.97</v>
       </c>
       <c r="L8" t="n">
-        <v>-25253200</v>
+        <v>-30506300</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1259,48 +1259,48 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10055-10545</t>
+          <t>1711-1939</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9566.071428571429</v>
+        <v>1484.285714285714</v>
       </c>
       <c r="F9" t="n">
-        <v>11225</v>
+        <v>2265.892857142857</v>
       </c>
       <c r="G9" t="n">
-        <v>12347.5</v>
+        <v>2492.482142857143</v>
       </c>
       <c r="H9" t="n">
-        <v>12812.5</v>
+        <v>3029.642857142857</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12.86%</t>
+          <t>6.23%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>45.48</v>
+        <v>1.77</v>
       </c>
       <c r="L9" t="n">
-        <v>-4000</v>
+        <v>56554200</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1310,48 +1310,48 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2823-2897</t>
+          <t>1922-2038</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2749.642857142857</v>
+        <v>1805.892857142857</v>
       </c>
       <c r="F10" t="n">
-        <v>2998.571428571428</v>
+        <v>2210.535714285714</v>
       </c>
       <c r="G10" t="n">
-        <v>3236.071428571428</v>
+        <v>2431.589285714286</v>
       </c>
       <c r="H10" t="n">
-        <v>3298.428571428572</v>
+        <v>2613.035714285714</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7.42%</t>
+          <t>18.35%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2818040467.88</v>
+        <v>16.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1793800</v>
+        <v>-25253200</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1369,40 +1369,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2356-2444</t>
+          <t>3369-3591</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2268.214285714286</v>
+        <v>3145.714285714286</v>
       </c>
       <c r="F11" t="n">
-        <v>2572.5</v>
+        <v>3905.357142857143</v>
       </c>
       <c r="G11" t="n">
-        <v>2829.75</v>
+        <v>4295.892857142858</v>
       </c>
       <c r="H11" t="n">
-        <v>2872.5</v>
+        <v>4637.857142857143</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.68%</t>
+          <t>23.40%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>56.96</v>
+        <v>8891980896.129999</v>
       </c>
       <c r="L11" t="n">
-        <v>-2979900</v>
+        <v>6595200</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1412,48 +1412,48 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4907-5053</t>
+          <t>3601-3899</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4760.892857142857</v>
+        <v>3302.142857142857</v>
       </c>
       <c r="F12" t="n">
-        <v>5256.071428571429</v>
+        <v>4341.785714285714</v>
       </c>
       <c r="G12" t="n">
-        <v>5729.821428571429</v>
+        <v>4775.964285714285</v>
       </c>
       <c r="H12" t="n">
-        <v>5781.678571428572</v>
+        <v>5374.285714285714</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>33.73%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>3.44</v>
+        <v>533.61</v>
       </c>
       <c r="L12" t="n">
-        <v>33741800</v>
+        <v>-1117600</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1463,48 +1463,48 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3942-4158</t>
+          <t>1699-1831</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3726.428571428572</v>
+        <v>1567.321428571429</v>
       </c>
       <c r="F13" t="n">
-        <v>4451.428571428572</v>
+        <v>2024.285714285714</v>
       </c>
       <c r="G13" t="n">
-        <v>4896.571428571429</v>
+        <v>2226.714285714286</v>
       </c>
       <c r="H13" t="n">
-        <v>5136.428571428572</v>
+        <v>2475.535714285714</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17.80%</t>
+          <t>13.15%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>42.83</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-30506300</v>
+        <v>766200</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1514,48 +1514,48 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3325-3535</t>
+          <t>747-793</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3116.071428571428</v>
+        <v>701.9642857142858</v>
       </c>
       <c r="F14" t="n">
-        <v>3834.642857142857</v>
+        <v>858.0357142857143</v>
       </c>
       <c r="G14" t="n">
-        <v>4218.107142857143</v>
+        <v>943.8392857142859</v>
       </c>
       <c r="H14" t="n">
-        <v>4534.642857142857</v>
+        <v>1010.535714285714</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23.35%</t>
+          <t>2.91%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>8873218352.25</v>
+        <v>2.1</v>
       </c>
       <c r="L14" t="n">
-        <v>6595200</v>
+        <v>-4702400</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1565,44 +1565,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>INKP.JK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3755-4045</t>
+          <t>8821-9579</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3465</v>
+        <v>8064.285714285714</v>
       </c>
       <c r="F15" t="n">
-        <v>4474.642857142857</v>
+        <v>10655.35714285714</v>
       </c>
       <c r="G15" t="n">
-        <v>4922.107142857143</v>
+        <v>11732.14285714286</v>
       </c>
       <c r="H15" t="n">
-        <v>5477.142857142857</v>
+        <v>13167.85714285714</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>34.49%</t>
+          <t>10.61%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>545.65</v>
+        <v>6.92</v>
       </c>
       <c r="L15" t="n">
-        <v>-1117600</v>
+        <v>-1912500</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1616,48 +1616,48 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1759-1881</t>
+          <t>1317-1403</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1637.857142857143</v>
+        <v>1230.357142857143</v>
       </c>
       <c r="F16" t="n">
-        <v>2058.571428571428</v>
+        <v>1527.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2264.428571428572</v>
+        <v>1680.25</v>
       </c>
       <c r="H16" t="n">
-        <v>2473.571428571428</v>
+        <v>1817.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12.55%</t>
+          <t>16.09%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>62.1</v>
+        <v>59.65</v>
       </c>
       <c r="L16" t="n">
-        <v>766200</v>
+        <v>-5503000</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ARCI.JK</t>
+          <t>EMAS.JK</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1675,36 +1675,36 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1723-1817</t>
+          <t>7807-8293</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1628.571428571428</v>
+        <v>7321.428571428572</v>
       </c>
       <c r="F17" t="n">
-        <v>1940.892857142857</v>
+        <v>8943.75</v>
       </c>
       <c r="G17" t="n">
-        <v>2134.982142857143</v>
+        <v>9838.125</v>
       </c>
       <c r="H17" t="n">
-        <v>2229.642857142857</v>
+        <v>10462.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8.02%</t>
+          <t>24.56%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>3.86</v>
+        <v>9334296337.620001</v>
       </c>
       <c r="L17" t="n">
-        <v>-11431200</v>
+        <v>-658500</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1718,48 +1718,48 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>HRUM.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9370-10080</t>
+          <t>1034-1106</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8658.928571428572</v>
+        <v>962.3214285714286</v>
       </c>
       <c r="F18" t="n">
-        <v>11098.21428571429</v>
+        <v>1210.892857142857</v>
       </c>
       <c r="G18" t="n">
-        <v>12208.03571428572</v>
+        <v>1331.982142857143</v>
       </c>
       <c r="H18" t="n">
-        <v>13473.21428571429</v>
+        <v>1455.892857142857</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>10.95%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>7.11</v>
+        <v>2.85</v>
       </c>
       <c r="L18" t="n">
-        <v>-1912500</v>
+        <v>746000</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MBMA.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1777,36 +1777,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>674-746</t>
+          <t>249-287</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>602.8571428571429</v>
+        <v>211.1071428571429</v>
       </c>
       <c r="F19" t="n">
-        <v>847.5</v>
+        <v>341.9285714285714</v>
       </c>
       <c r="G19" t="n">
-        <v>945</v>
+        <v>376.1214285714286</v>
       </c>
       <c r="H19" t="n">
-        <v>1085</v>
+        <v>470.1785714285714</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18.78%</t>
+          <t>65.11%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>26.51</v>
+        <v>14.76</v>
       </c>
       <c r="L19" t="n">
-        <v>-73678300</v>
+        <v>-104512900</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1820,48 +1820,48 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>721-759</t>
+          <t>11262-11688</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>682.1428571428571</v>
+        <v>10834.82142857143</v>
       </c>
       <c r="F20" t="n">
-        <v>814.4642857142858</v>
+        <v>12325.89285714286</v>
       </c>
       <c r="G20" t="n">
-        <v>895.9107142857144</v>
+        <v>13558.48214285714</v>
       </c>
       <c r="H20" t="n">
-        <v>943.2142857142858</v>
+        <v>13813.39285714286</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>17.63%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1.59</v>
+        <v>6699663422.45</v>
       </c>
       <c r="L20" t="n">
-        <v>-4702400</v>
+        <v>328500</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1879,36 +1879,36 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>158-168</t>
+          <t>5962-6438</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>148.2142857142857</v>
+        <v>5487.5</v>
       </c>
       <c r="F21" t="n">
-        <v>182.3928571428571</v>
+        <v>7088.392857142857</v>
       </c>
       <c r="G21" t="n">
-        <v>196.8571428571428</v>
+        <v>7797.232142857143</v>
       </c>
       <c r="H21" t="n">
-        <v>216.1428571428571</v>
+        <v>8607.142857142857</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>47.29%</t>
+          <t>25.39%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>32.1</v>
+        <v>127.37</v>
       </c>
       <c r="L21" t="n">
-        <v>316433400</v>
+        <v>745400</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2387,414 +2387,414 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>80.2</v>
+        <v>114.8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>98</v>
       </c>
       <c r="C3" t="n">
-        <v>79.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-15.1%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>97</v>
       </c>
       <c r="C4" t="n">
-        <v>78.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-15.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>96</v>
       </c>
       <c r="C5" t="n">
-        <v>77.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-14.2%</t>
+          <t>-3.3%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>95</v>
       </c>
       <c r="C6" t="n">
-        <v>76.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.6%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>76.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-2.8%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>74.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-15.1%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C9" t="n">
-        <v>74.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-17.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C10" t="n">
-        <v>74.8</v>
+        <v>67.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-13.2%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>90</v>
       </c>
       <c r="C11" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-11.7%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C12" t="n">
-        <v>72.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-11.6%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C13" t="n">
-        <v>70.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-11.5%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-1.9%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>INKP.JK</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-23.3%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>57.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ARCI.JK</t>
+          <t>EMAS.JK</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>83</v>
       </c>
       <c r="C17" t="n">
-        <v>62.6</v>
+        <v>52</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-7.5%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>HRUM.JK</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-16.7%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MBMA.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>81</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-15.7%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-7.1%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>79</v>
       </c>
       <c r="C21" t="n">
-        <v>55</v>
+        <v>48.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-21.5%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BULL.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>78</v>
       </c>
       <c r="C22" t="n">
-        <v>54.8</v>
+        <v>48</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-18.3%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EMAS.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C23" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-18.4%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>PSAB.JK</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C24" t="n">
-        <v>52</v>
+        <v>46.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-19.8%</t>
         </is>
       </c>
     </row>
@@ -2808,918 +2808,918 @@
         <v>75</v>
       </c>
       <c r="C25" t="n">
-        <v>49.8</v>
+        <v>44.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-7.1%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>ARCI.JK</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C26" t="n">
-        <v>49</v>
+        <v>42.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-17.2%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HRUM.JK</t>
+          <t>MBMA.JK</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C27" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-21.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C28" t="n">
-        <v>49</v>
+        <v>40.6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>BULL.JK</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>70</v>
       </c>
       <c r="C29" t="n">
-        <v>48</v>
+        <v>39.8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-35.2%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PSAB.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>69</v>
       </c>
       <c r="C30" t="n">
-        <v>46.8</v>
+        <v>38.4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-12.6%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SUPA.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>68</v>
       </c>
       <c r="C31" t="n">
-        <v>45</v>
+        <v>37.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-7.3%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>40.6</v>
+        <v>34</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.8%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VKTR.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>66</v>
       </c>
       <c r="C33" t="n">
-        <v>38.8</v>
+        <v>30</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-33.8%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RATU.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>65</v>
       </c>
       <c r="C34" t="n">
-        <v>35.4</v>
+        <v>29</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-10.3%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>JPFA.JK</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>64</v>
       </c>
       <c r="C35" t="n">
-        <v>34</v>
+        <v>28.2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C36" t="n">
-        <v>34</v>
+        <v>25.4</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-52.3%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMMN.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C37" t="n">
-        <v>32</v>
+        <v>25.4</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-63.3%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GTSI.JK</t>
+          <t>SUPA.JK</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C38" t="n">
-        <v>31.8</v>
+        <v>25</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-42.9%</t>
+          <t>-28.9%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CPRO.JK</t>
+          <t>VKTR.JK</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C39" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-36.3%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>LPKR.JK</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C40" t="n">
-        <v>28.2</v>
+        <v>23.6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-28.1%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HUMI.JK</t>
+          <t>AMMN.JK</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C41" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-39.3%</t>
+          <t>-24.8%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TOBA.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C42" t="n">
-        <v>26.8</v>
+        <v>22</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-19.4%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TPIA.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>55</v>
       </c>
       <c r="C43" t="n">
-        <v>24.6</v>
+        <v>21.6</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-16.7%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LPKR.JK</t>
+          <t>BRIS.JK</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>54</v>
       </c>
       <c r="C44" t="n">
-        <v>23.6</v>
+        <v>20.8</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-9.0%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>53</v>
       </c>
       <c r="C45" t="n">
-        <v>23.4</v>
+        <v>20.4</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-45.4%</t>
+          <t>-21.2%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BBCA.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>52</v>
       </c>
       <c r="C46" t="n">
-        <v>22.8</v>
+        <v>20</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-50.9%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>AMRT.JK</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>51</v>
       </c>
       <c r="C47" t="n">
-        <v>21.6</v>
+        <v>19.8</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-24.0%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BRIS.JK</t>
+          <t>DADA.JK</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>50</v>
       </c>
       <c r="C48" t="n">
-        <v>20.8</v>
+        <v>18.6</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-20.6%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>20.4</v>
+        <v>18</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-17.2%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AMRT.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>48</v>
       </c>
       <c r="C50" t="n">
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-12.8%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DADA.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C51" t="n">
-        <v>18.6</v>
+        <v>18</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-21.2%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>DSSA.JK</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C52" t="n">
-        <v>18</v>
+        <v>17.4</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-35.0%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>BBYB.JK</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C53" t="n">
-        <v>18</v>
+        <v>17.4</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-47.8%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C54" t="n">
-        <v>18</v>
+        <v>16.8</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-19.0%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>GOTO.JK</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>43</v>
       </c>
       <c r="C55" t="n">
-        <v>17.4</v>
+        <v>16.8</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-21.1%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BBYB.JK</t>
+          <t>EMTK.JK</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C56" t="n">
-        <v>17.4</v>
+        <v>16.2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-46.8%</t>
+          <t>-50.0%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>ICBP.JK</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>40</v>
       </c>
       <c r="C57" t="n">
-        <v>16.8</v>
+        <v>15</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GOTO.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C58" t="n">
-        <v>16.8</v>
+        <v>14.8</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-48.3%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EMTK.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C59" t="n">
-        <v>16.2</v>
+        <v>14.8</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-28.7%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BUMI.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C60" t="n">
-        <v>15</v>
+        <v>13.2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-47.2%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ICBP.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C61" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-35.0%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C62" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-31.0%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>NICL.JK</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C63" t="n">
-        <v>13.2</v>
+        <v>10.8</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-44.2%</t>
+          <t>-46.8%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C64" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-40.0%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NICL.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>32</v>
       </c>
       <c r="C65" t="n">
-        <v>10.8</v>
+        <v>8.4</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-46.9%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DEWA.JK</t>
+          <t>BBCA.JK</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C66" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-42.8%</t>
+          <t>-15.7%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BBKP.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>30</v>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-54.3%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>COIN.JK</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C68" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-71.8%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>PBSA.JK</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C69" t="n">
         <v>7.8</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-54.0%</t>
+          <t>-53.5%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>COIN.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C70" t="n">
-        <v>7.8</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-50.2%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PBSA.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C71" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-54.3%</t>
+          <t>-58.2%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>IRSX.JK</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C72" t="n">
-        <v>7.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-37.6%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>PNLF.JK</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C73" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-55.9%</t>
+          <t>-25.7%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>CPRO.JK</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C74" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-40.4%</t>
+          <t>-33.7%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PNLF.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-61.6%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3730,14 +3730,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-58.9%</t>
+          <t>-38.9%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-35.1%</t>
+          <t>-53.5%</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-67.7%</t>
+          <t>-69.0%</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-54.2%</t>
+          <t>-54.6%</t>
         </is>
       </c>
     </row>
@@ -3802,212 +3802,212 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-54.3%</t>
+          <t>-53.7%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>WIFI.JK</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C81" t="n">
-        <v>5.399999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-50.6%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>EXCL.JK</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C82" t="n">
-        <v>5.399999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-62.2%</t>
+          <t>-38.5%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>WIFI.JK</t>
+          <t>GTSI.JK</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C83" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-45.8%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>TOBA.JK</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C84" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-35.9%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SSIA.JK</t>
+          <t>DEWA.JK</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-39.7%</t>
+          <t>-46.3%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DSSA.JK</t>
+          <t>BUMI.JK</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C86" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-50.4%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EXCL.JK</t>
+          <t>RMKE.JK</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>8</v>
       </c>
       <c r="C87" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>-63.2%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>BBKP.JK</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-31.9%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>RMKE.JK</t>
+          <t>TRUE.JK</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-62.9%</t>
+          <t>-67.5%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TRUE.JK</t>
+          <t>BKSL.JK</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-66.0%</t>
+          <t>-34.6%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BKSL.JK</t>
+          <t>HUMI.JK</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C91" t="n">
-        <v>-1.2</v>
+        <v>-3</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-36.6%</t>
+          <t>-41.0%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>TRIN.JK</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -4018,43 +4018,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-56.3%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>SSIA.JK</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-38.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>TRIN.JK</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>3</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-3</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>-51.4%</t>
+          <t>-38.3%</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4103,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4129,7 +4111,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -4137,17 +4119,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2909-3091</t>
+          <t>2939-3021</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-2895500</t>
+          <t>1793800</t>
         </is>
       </c>
     </row>
@@ -4158,25 +4140,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>158-168</t>
+          <t>813-887</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>316433400</t>
+          <t>-21636100</t>
         </is>
       </c>
     </row>
@@ -4187,25 +4169,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VKTR.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>728-832</t>
+          <t>10044-10556</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>12399</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2430100</t>
+          <t>-4000</t>
         </is>
       </c>
     </row>
@@ -4216,25 +4198,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>224-268</t>
+          <t>2356-2444</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7483200</t>
+          <t>-2979900</t>
         </is>
       </c>
     </row>
@@ -4245,32 +4227,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>268-316</t>
+          <t>1711-1939</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-4347200</t>
+          <t>56554200</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4278,7 +4260,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -4286,17 +4268,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>840-910</t>
+          <t>2659-2861</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-21636100</t>
+          <t>-2895500</t>
         </is>
       </c>
     </row>
@@ -4307,25 +4289,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2037-2243</t>
+          <t>129-137</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>162</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>56554200</t>
+          <t>316433400</t>
         </is>
       </c>
     </row>
@@ -4336,25 +4318,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10055-10545</t>
+          <t>246-286</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12348</t>
+          <t>380</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-4000</t>
+          <t>7483200</t>
         </is>
       </c>
     </row>
@@ -4365,25 +4347,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>VKTR.JK</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2823-2897</t>
+          <t>770-880</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1793800</t>
+          <t>-2430100</t>
         </is>
       </c>
     </row>
@@ -4394,32 +4376,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2356-2444</t>
+          <t>979-1151</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2979900</t>
+          <t>-16450400</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4427,25 +4409,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6238-6712</t>
+          <t>2324-2416</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>745400</t>
+          <t>10200200</t>
         </is>
       </c>
     </row>
@@ -4456,25 +4438,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1280-1370</t>
+          <t>7533-7917</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5503000</t>
+          <t>-65600</t>
         </is>
       </c>
     </row>
@@ -4485,25 +4467,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1952-2068</t>
+          <t>1008-1042</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-25253200</t>
+          <t>-2798000</t>
         </is>
       </c>
     </row>
@@ -4514,25 +4496,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3942-4158</t>
+          <t>316-360</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>484</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-30506300</t>
+          <t>-2360900</t>
         </is>
       </c>
     </row>
@@ -4543,32 +4525,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3325-3535</t>
+          <t>3588-3952</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6595200</t>
+          <t>-128900</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -4576,25 +4558,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2298-2382</t>
+          <t>3936-4144</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10200200</t>
+          <t>-30506300</t>
         </is>
       </c>
     </row>
@@ -4605,25 +4587,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1022-1058</t>
+          <t>1922-2038</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2798000</t>
+          <t>-25253200</t>
         </is>
       </c>
     </row>
@@ -4634,25 +4616,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3851-4269</t>
+          <t>3369-3591</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-128900</t>
+          <t>6595200</t>
         </is>
       </c>
     </row>
@@ -4663,25 +4645,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>860-930</t>
+          <t>747-793</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>944</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-7662000</t>
+          <t>-4702400</t>
         </is>
       </c>
     </row>
@@ -4692,32 +4674,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>INKP.JK</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7246-7604</t>
+          <t>8821-9579</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>11732</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-65600</t>
+          <t>-1912500</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -4725,25 +4707,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4907-5053</t>
+          <t>249-287</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>376</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>33741800</t>
+          <t>-104512900</t>
         </is>
       </c>
     </row>
@@ -4754,25 +4736,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1598-1692</t>
+          <t>11262-11688</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1514600</t>
+          <t>328500</t>
         </is>
       </c>
     </row>
@@ -4783,25 +4765,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SUPA.JK</t>
+          <t>BULL.JK</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>854-916</t>
+          <t>416-472</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>724900</t>
+          <t>-2075700</t>
         </is>
       </c>
     </row>
@@ -4812,25 +4794,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3653-3727</t>
+          <t>6028-6222</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>105416300</t>
+          <t>6227500</t>
         </is>
       </c>
     </row>
@@ -4841,32 +4823,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>PBSA.JK</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4112-4188</t>
+          <t>1201-1299</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8426900</t>
+          <t>-430700</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -4874,25 +4856,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BULL.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>446-502</t>
+          <t>3630-3710</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2075700</t>
+          <t>105416300</t>
         </is>
       </c>
     </row>
@@ -4903,25 +4885,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>242-278</t>
+          <t>4902-5058</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-104512900</t>
+          <t>33741800</t>
         </is>
       </c>
     </row>
@@ -4932,25 +4914,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11415-11835</t>
+          <t>4226-4314</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>328500</t>
+          <t>8426900</t>
         </is>
       </c>
     </row>
@@ -4961,25 +4943,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GTSI.JK</t>
+          <t>SUPA.JK</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>257-291</t>
+          <t>843-907</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3409300</t>
+          <t>724900</t>
         </is>
       </c>
     </row>
@@ -4990,32 +4972,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HUMI.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>201-231</t>
+          <t>1572-1668</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-571700</t>
+          <t>-1514600</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -5023,25 +5005,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>341-351</t>
+          <t>2109-2211</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>37538300</t>
+          <t>4049500</t>
         </is>
       </c>
     </row>
@@ -5052,25 +5034,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5015-5285</t>
+          <t>3132-3248</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>81700</t>
+          <t>13783000</t>
         </is>
       </c>
     </row>
@@ -5081,25 +5063,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>EMTK.JK</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8182-8718</t>
+          <t>712-758</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>907</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-202100</t>
+          <t>-5460200</t>
         </is>
       </c>
     </row>
@@ -5110,25 +5092,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DADA.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>50-50</t>
+          <t>275-305</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>390</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15489100</t>
         </is>
       </c>
     </row>
@@ -5139,32 +5121,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TRUE.JK</t>
+          <t>EXCL.JK</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>163-197</t>
+          <t>2669-2851</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>314000</t>
+          <t>4119100</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -5172,25 +5154,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CPRO.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>56-58</t>
+          <t>343-353</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>12850400</t>
+          <t>37538300</t>
         </is>
       </c>
     </row>
@@ -5201,25 +5183,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>DADA.JK</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2230-2330</t>
+          <t>50-50</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>5002500</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -5230,25 +5212,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AMRT.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1516-1584</t>
+          <t>176-190</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>37773100</t>
+          <t>-18379100</t>
         </is>
       </c>
     </row>
@@ -5259,25 +5241,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6054-6196</t>
+          <t>8059-8541</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>10149</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-8356000</t>
+          <t>-202100</t>
         </is>
       </c>
     </row>
@@ -5288,32 +5270,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ICBP.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7371-7579</t>
+          <t>4869-5131</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1298800</t>
+          <t>81700</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -5321,25 +5303,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LPKR.JK</t>
+          <t>JPFA.JK</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>88-96</t>
+          <t>2298-2402</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-266800</t>
+          <t>5002500</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5332,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>AMRT.JK</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -5358,166 +5340,166 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1000-1030</t>
+          <t>1482-1558</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-34214900</t>
+          <t>37773100</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3144-3256</t>
+          <t>6203-6347</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>13783000</t>
+          <t>-8356000</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EMTK.JK</t>
+          <t>ICBP.JK</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>758-802</t>
+          <t>7342-7558</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-5460200</t>
+          <t>-1298800</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2132-2228</t>
+          <t>1926-2024</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>4049500</t>
+          <t>2865100</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>LPKR.JK</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>286-318</t>
+          <t>89-95</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-15489100</t>
+          <t>-266800</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EXCL.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2732-2908</t>
+          <t>1009-1041</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>4119100</t>
+          <t>-34214900</t>
         </is>
       </c>
     </row>
@@ -5536,11 +5518,11 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>56-58</t>
+          <t>55-57</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5565,16 +5547,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>439-497</t>
+          <t>462-518</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>669</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5594,16 +5576,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2086-2234</t>
+          <t>2024-2176</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5627,16 +5609,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>5478-6222</t>
+          <t>5621-6379</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5888,7 +5870,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
@@ -5978,7 +5960,7 @@
         <v>0.38872</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>8.254189500000001</v>
+        <v>8.255831000000001</v>
       </c>
       <c r="I2" s="11" t="n">
         <v>1.580866</v>
@@ -5987,7 +5969,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>603.33</v>
+        <v>603.21</v>
       </c>
     </row>
     <row r="3">
@@ -6017,10 +5999,10 @@
         <v>0.34335998</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>8.722222</v>
+        <v>8.555555</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>1.0140808</v>
+        <v>0.9947035</v>
       </c>
       <c r="J3" s="11" t="n">
         <v>0</v>
@@ -6056,16 +6038,16 @@
         <v>0.43205002</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>6.3756747</v>
+        <v>6.007356</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>1.2184892</v>
+        <v>1.1481917</v>
       </c>
       <c r="J4" s="14" t="n">
         <v>2.444</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>122.34</v>
+        <v>122.35</v>
       </c>
     </row>
     <row r="5">
@@ -6095,16 +6077,16 @@
         <v>0.40405998</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>9.946896000000001</v>
+        <v>9.757265</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>1.7149916</v>
+        <v>1.7056962</v>
       </c>
       <c r="J5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>370.97</v>
+        <v>376.13</v>
       </c>
     </row>
     <row r="6">
@@ -6134,16 +6116,16 @@
         <v>0.27552</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>10.460251</v>
+        <v>10.734864</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>2.3364198</v>
+        <v>2.3981366</v>
       </c>
       <c r="J6" s="14" t="n">
         <v>23.671</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>126.67</v>
+        <v>126.69</v>
       </c>
     </row>
     <row r="7">
@@ -6173,16 +6155,16 @@
         <v>0.06594999999999999</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>7.944804</v>
+        <v>8.186442</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>1.4325405</v>
+        <v>1.4640687</v>
       </c>
       <c r="J7" s="14" t="n">
         <v>59.254</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>286.98</v>
+        <v>287.06</v>
       </c>
     </row>
     <row r="8">
@@ -6212,16 +6194,16 @@
         <v>0.71615</v>
       </c>
       <c r="H8" t="n">
-        <v>29.057592</v>
+        <v>27.559055</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>6.9418387</v>
+        <v>6.566604</v>
       </c>
       <c r="J8" s="14" t="n">
         <v>5.093</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="9">
@@ -6251,16 +6233,16 @@
         <v>0.31919</v>
       </c>
       <c r="H9" t="n">
-        <v>12.9925585</v>
+        <v>13.600049</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>1.8912387</v>
+        <v>1.9800292</v>
       </c>
       <c r="J9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>163.94</v>
+        <v>163.97</v>
       </c>
     </row>
     <row r="10">
@@ -6290,16 +6272,16 @@
         <v>0.27632</v>
       </c>
       <c r="H10" t="n">
-        <v>19.024391</v>
+        <v>19.395712</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>12.483995</v>
+        <v>12.740077</v>
       </c>
       <c r="J10" s="11" t="n">
         <v>0.378</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>51.25</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="11">
@@ -6329,16 +6311,16 @@
         <v>0.023759998</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>19.301294</v>
+        <v>17.75262</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>4.9008636</v>
+        <v>4.5087943</v>
       </c>
       <c r="J11" s="14" t="n">
         <v>139.825</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>155.43</v>
+        <v>155.47</v>
       </c>
     </row>
     <row r="12">
@@ -6368,16 +6350,16 @@
         <v>0.048460003</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>9.271032</v>
+        <v>9.001377</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>1.2417248</v>
+        <v>1.206247</v>
       </c>
       <c r="J12" s="14" t="n">
         <v>4.935</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>94.38</v>
+        <v>94.43000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -6407,55 +6389,55 @@
         <v>0.21154</v>
       </c>
       <c r="H13" t="n">
-        <v>31.00911</v>
+        <v>29.227558</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>126428.57</v>
+        <v>120000</v>
       </c>
       <c r="J13" s="14" t="n">
         <v>118.6</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>57.08</v>
+        <v>57.48</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>TPIA.JK</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BBNI.JK</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E14" s="13" t="n">
-        <v>0.42018002</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>4.295</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <v>0.2208</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>17.594633</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>118888.88</v>
-      </c>
-      <c r="J14" s="14" t="n">
-        <v>82.7</v>
+      <c r="E14" s="9" t="n">
+        <v>0.1173</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>7.94951</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>0.92637515</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>304.07</v>
+        <v>537.14</v>
       </c>
     </row>
     <row r="15">
@@ -6464,7 +6446,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -6476,25 +6458,25 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.1173</v>
+        <v>0.102419995</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>0.028</v>
+        <v>0.144</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0.40232</v>
+        <v>0.30543</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>7.727112</v>
+        <v>7.8378377</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.90034115</v>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>0</v>
+        <v>0.7674631</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>21.136</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>537.0700000000001</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="16">
@@ -6503,11 +6485,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -6515,25 +6497,25 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.102419995</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>0.30543</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>7.789284</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>0.7630524</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>21.136</v>
+        <v>0.02158</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>0.06239</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>61.6486</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>23754.79</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>0.173</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>44.42</v>
+        <v>100.57</v>
       </c>
     </row>
     <row r="17">
@@ -6542,7 +6524,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -6554,25 +6536,25 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.02158</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>0.212</v>
+        <v>0.15277</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>0.091</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.06239</v>
-      </c>
-      <c r="H17" s="17" t="n">
-        <v>64.69824</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>24808.428</v>
-      </c>
-      <c r="J17" s="11" t="n">
-        <v>0.173</v>
+        <v>0.09748999999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12.63823</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>1.9179865</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>138.994</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>100.08</v>
+        <v>170.91</v>
       </c>
     </row>
     <row r="18">
@@ -6581,7 +6563,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -6593,25 +6575,25 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0</v>
+        <v>0.07034</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.791</v>
+        <v>0.647</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>0.52018</v>
-      </c>
-      <c r="H18" t="n">
-        <v>18.867924</v>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v>3.2115743</v>
-      </c>
-      <c r="J18" s="14" t="n">
-        <v>2.39</v>
+        <v>0.26583</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>150.79942</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>5.537505</v>
+      </c>
+      <c r="J18" s="15" t="n">
+        <v>1.864</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>272.95</v>
+        <v>55.04</v>
       </c>
     </row>
     <row r="19">
@@ -6620,7 +6602,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -6632,25 +6614,25 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.15277</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>0.09748999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>0.52018</v>
       </c>
       <c r="H19" t="n">
-        <v>12.761225</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>1.9357456</v>
+        <v>18.312334</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>3.1180332</v>
       </c>
       <c r="J19" s="14" t="n">
-        <v>138.994</v>
+        <v>2.39</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>170.83</v>
+        <v>273.04</v>
       </c>
     </row>
     <row r="20">
@@ -6680,16 +6662,16 @@
         <v>0.53282</v>
       </c>
       <c r="H20" t="n">
-        <v>14.723204</v>
+        <v>14.983519</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>3.0046723</v>
+        <v>3.0593028</v>
       </c>
       <c r="J20" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>466.95</v>
+        <v>467.18</v>
       </c>
     </row>
     <row r="21">
@@ -6722,13 +6704,13 @@
         <v>0</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>11.423653</v>
+        <v>11.345408</v>
       </c>
       <c r="J21" s="11" t="n">
         <v>0.049</v>
       </c>
       <c r="K21" s="15" t="n">
-        <v>-0.71</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="22">
@@ -6758,16 +6740,16 @@
         <v>0.30952</v>
       </c>
       <c r="H22" s="17" t="n">
-        <v>216.5605</v>
+        <v>209.33977</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>11.029293</v>
+        <v>10.5427065</v>
       </c>
       <c r="J22" s="11" t="n">
         <v>0.261</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>6.28</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="23">
@@ -6797,16 +6779,16 @@
         <v>0.15842</v>
       </c>
       <c r="H23" t="n">
-        <v>15.88942</v>
+        <v>16.14987</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>4.8084817</v>
+        <v>4.886668</v>
       </c>
       <c r="J23" s="15" t="n">
         <v>1.461</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>77.41</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -6836,16 +6818,16 @@
         <v>0.13921</v>
       </c>
       <c r="H24" s="17" t="n">
-        <v>64.36837</v>
+        <v>63.279</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>445000</v>
+        <v>440000</v>
       </c>
       <c r="J24" s="14" t="n">
         <v>201.586</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>20.74</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="25">
@@ -6854,7 +6836,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -6866,25 +6848,25 @@
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.12380999</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>-0.075</v>
+        <v>0.12082</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>0.008</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.18375</v>
-      </c>
-      <c r="H25" t="n">
-        <v>28.705566</v>
+        <v>0.0806</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>10.863586</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>62941.17</v>
+        <v>20789.475</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>51.917</v>
+        <v>32.802</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>74.55</v>
+        <v>218.16</v>
       </c>
     </row>
     <row r="26">
@@ -6893,7 +6875,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -6905,25 +6887,25 @@
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.12082</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>0.008</v>
+        <v>0.12380999</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>-0.075</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.0806</v>
-      </c>
-      <c r="H26" s="10" t="n">
-        <v>10.785398</v>
+        <v>0.18375</v>
+      </c>
+      <c r="H26" t="n">
+        <v>24.275074</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>20526.316</v>
+        <v>53676.47</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>32.802</v>
+        <v>51.917</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>216.96</v>
+        <v>75.18000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -6953,16 +6935,16 @@
         <v>0.10163</v>
       </c>
       <c r="H27" t="n">
-        <v>13.252383</v>
+        <v>13.372472</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>2.001913</v>
+        <v>2.0216365</v>
       </c>
       <c r="J27" s="14" t="n">
         <v>2.102</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>76.59</v>
+        <v>76.65000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -6992,16 +6974,16 @@
         <v>0.09752</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>14.95668</v>
+        <v>14.110708</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>68333.336</v>
+        <v>64791.668</v>
       </c>
       <c r="J28" s="14" t="n">
         <v>107.818</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>109.65</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="29">
@@ -7031,16 +7013,16 @@
         <v>0.06455</v>
       </c>
       <c r="H29" s="17" t="n">
-        <v>55.384617</v>
+        <v>59.68331</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>9.699482</v>
+        <v>10.15544</v>
       </c>
       <c r="J29" s="11" t="n">
         <v>0.216</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>8.449999999999999</v>
+        <v>8.210000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -7049,7 +7031,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CPRO.JK</t>
+          <t>PNLF.JK</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -7061,25 +7043,25 @@
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.10436</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>0.081</v>
+        <v>0.05041</v>
+      </c>
+      <c r="F30" s="16" t="n">
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.041550003</v>
+        <v>0.15737</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>8.260869</v>
+        <v>4.815534</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>0.8504416299999999</v>
-      </c>
-      <c r="J30" s="14" t="n">
-        <v>43.245</v>
+        <v>0.25498217</v>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>6.9</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="31">
@@ -7088,7 +7070,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PNLF.JK</t>
+          <t>CPRO.JK</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -7100,25 +7082,25 @@
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.05041</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>-0.07199999999999999</v>
+        <v>0.10436</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>0.081</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.15737</v>
+        <v>0.041550003</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>4.856255</v>
+        <v>8.260869</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>0.25703847</v>
-      </c>
-      <c r="J31" s="11" t="n">
-        <v>0</v>
+        <v>0.8504416299999999</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>43.245</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>51.48</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="32">
@@ -7148,16 +7130,16 @@
         <v>0.31559</v>
       </c>
       <c r="H32" s="17" t="n">
-        <v>58.088234</v>
+        <v>54.06195</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>348529.4</v>
+        <v>326470.56</v>
       </c>
       <c r="J32" s="14" t="n">
         <v>36.548</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>102</v>
+        <v>102.66</v>
       </c>
     </row>
     <row r="33">
@@ -7166,7 +7148,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -7177,26 +7159,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E33" s="9" t="n">
-        <v>0.0678</v>
+      <c r="E33" s="16" t="n">
+        <v>-0.29015</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.946</v>
-      </c>
-      <c r="G33" s="8" t="n">
-        <v>0.24195999</v>
-      </c>
-      <c r="H33" s="17" t="n">
-        <v>154.45074</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <v>6.351526</v>
+        <v>0.671</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>-0.21053</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>4.715777</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>2.054</v>
-      </c>
-      <c r="K33" s="11" t="n">
-        <v>54.71</v>
+        <v>65.76600000000001</v>
+      </c>
+      <c r="K33" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -7205,7 +7187,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -7216,26 +7198,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E34" s="9" t="n">
-        <v>0.05801</v>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <v>0.01754</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31.159975</v>
+      <c r="E34" s="8" t="n">
+        <v>0.22038001</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>0.23266001</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>423.28766</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>220833.33</v>
+        <v>1545000</v>
       </c>
       <c r="J34" s="14" t="n">
-        <v>276.511</v>
+        <v>239.827</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>170.09</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="35">
@@ -7244,7 +7226,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -7256,25 +7238,25 @@
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.045900002</v>
+        <v>0.05801</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.329</v>
+        <v>0.317</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.19652</v>
-      </c>
-      <c r="H35" s="17" t="n">
-        <v>152.05724</v>
+        <v>0.01754</v>
+      </c>
+      <c r="H35" t="n">
+        <v>29.029615</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>94444.44500000001</v>
+        <v>206666.67</v>
       </c>
       <c r="J35" s="14" t="n">
-        <v>12.694</v>
+        <v>276.511</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>5.59</v>
+        <v>170.86</v>
       </c>
     </row>
     <row r="36">
@@ -7283,7 +7265,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -7295,25 +7277,25 @@
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.06432</v>
+        <v>0.045900002</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>1.905</v>
-      </c>
-      <c r="G36" s="8" t="n">
-        <v>0.24544</v>
+        <v>0.329</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>0.19652</v>
       </c>
       <c r="H36" s="17" t="n">
-        <v>215.7143</v>
+        <v>143.88489</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>7.4305534</v>
+        <v>88888.89</v>
       </c>
       <c r="J36" s="14" t="n">
-        <v>2.833</v>
+        <v>12.694</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>1.4</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="37">
@@ -7322,7 +7304,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -7333,26 +7315,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E37" s="8" t="n">
-        <v>0.23723</v>
+      <c r="E37" s="9" t="n">
+        <v>0.15447</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>0.145</v>
+        <v>0.034</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.14588</v>
-      </c>
-      <c r="H37" s="17" t="n">
-        <v>167.72151</v>
+        <v>0.091759995</v>
+      </c>
+      <c r="H37" t="n">
+        <v>39.336395</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>35.448795</v>
+        <v>78541.664</v>
       </c>
       <c r="J37" s="14" t="n">
-        <v>38.133</v>
+        <v>68.20699999999999</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>11.06</v>
+        <v>95.84</v>
       </c>
     </row>
     <row r="38">
@@ -7361,7 +7343,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -7373,25 +7355,25 @@
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0</v>
+        <v>0.06432</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.421</v>
+        <v>1.905</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>0.65328</v>
+        <v>0.24544</v>
       </c>
       <c r="H38" s="17" t="n">
-        <v>76.62671</v>
+        <v>207.14287</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>111874.99</v>
+        <v>7.1352997</v>
       </c>
       <c r="J38" s="14" t="n">
-        <v>34.873</v>
+        <v>2.833</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>11.68</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="39">
@@ -7400,7 +7382,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -7412,25 +7394,25 @@
         </is>
       </c>
       <c r="E39" s="8" t="n">
-        <v>0.22038001</v>
+        <v>0.23723</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G39" s="8" t="n">
-        <v>0.23266001</v>
+        <v>0.145</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>0.14588</v>
       </c>
       <c r="H39" s="17" t="n">
-        <v>408.41583</v>
+        <v>166.81778</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>1485000</v>
+        <v>35.162148</v>
       </c>
       <c r="J39" s="14" t="n">
-        <v>239.827</v>
+        <v>38.133</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>18.18</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="40">
@@ -7439,7 +7421,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -7450,26 +7432,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E40" s="16" t="n">
-        <v>-0.29015</v>
+      <c r="E40" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.671</v>
-      </c>
-      <c r="G40" s="9" t="n">
-        <v>-0.21053</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <v>4.8576045</v>
+        <v>0.421</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>0.65328</v>
+      </c>
+      <c r="H40" s="17" t="n">
+        <v>75.78323</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <v>111874.99</v>
       </c>
       <c r="J40" s="14" t="n">
-        <v>65.76600000000001</v>
-      </c>
-      <c r="K40" s="15" t="n">
-        <v>0</v>
+        <v>34.873</v>
+      </c>
+      <c r="K40" s="11" t="n">
+        <v>11.81</v>
       </c>
     </row>
     <row r="41">
@@ -7478,7 +7460,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -7489,26 +7471,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E41" s="8" t="n">
-        <v>0.2018</v>
+      <c r="E41" s="9" t="n">
+        <v>0.15961</v>
       </c>
       <c r="F41" s="16" t="n">
         <v>-0.012</v>
       </c>
-      <c r="G41" s="8" t="n">
-        <v>0.31149</v>
-      </c>
-      <c r="H41" t="n">
-        <v>15.727699</v>
-      </c>
-      <c r="I41" s="14" t="n">
-        <v>54324.324</v>
+      <c r="G41" s="9" t="n">
+        <v>0.075219996</v>
+      </c>
+      <c r="H41" s="10" t="n">
+        <v>10.495545</v>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>1.6605622</v>
       </c>
       <c r="J41" s="14" t="n">
-        <v>35.836</v>
+        <v>19.582</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>127.8</v>
+        <v>283.93</v>
       </c>
     </row>
   </sheetData>

--- a/reports/HEDGEFUND_TERMINAL.xlsx
+++ b/reports/HEDGEFUND_TERMINAL.xlsx
@@ -491,7 +491,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>06 March 2026</t>
+          <t>09 March 2026</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7"/>
@@ -572,7 +572,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.8M</t>
+          <t>-4000</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -650,7 +650,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.2M</t>
+          <t>-25.3M</t>
         </is>
       </c>
     </row>
@@ -667,15 +667,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4000</t>
+          <t>1.8M</t>
         </is>
       </c>
     </row>
@@ -727,71 +727,71 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>67.8</v>
+        <v>69</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-166.6M</t>
+          <t>-165.8M</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2. Consumer Cyclical</t>
+          <t>2. Energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63.8</v>
+        <v>57.8</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>297.8M</t>
+          <t>-494.1M</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3. Energy</t>
+          <t>3. Healthcare</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-494.1M</t>
+          <t>-34.5M</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4. Healthcare</t>
+          <t>4. Financial Services</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>56.5</v>
+        <v>50.9</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-34.5M</t>
+          <t>115.7M</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5. Financial Services</t>
+          <t>5. Consumer Cyclical</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>45.7</v>
+        <v>49.5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>115.7M</t>
+          <t>297.8M</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -910,40 +910,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2939-3021</t>
+          <t>10184-10716</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2856.785714285714</v>
+        <v>9651.785714285714</v>
       </c>
       <c r="F2" t="n">
-        <v>3135.714285714286</v>
+        <v>11460.71428571429</v>
       </c>
       <c r="G2" t="n">
-        <v>3250.357142857143</v>
+        <v>12606.78571428572</v>
       </c>
       <c r="H2" t="n">
-        <v>3403.214285714286</v>
+        <v>13198.21428571429</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.09%</t>
+          <t>15.09%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3073934999.61</v>
+        <v>155.87</v>
       </c>
       <c r="L2" t="n">
-        <v>1793800</v>
+        <v>-4000</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -961,20 +961,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2659-2861</t>
+          <t>2489-2711</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2455.714285714286</v>
+        <v>2265.714285714286</v>
       </c>
       <c r="F3" t="n">
-        <v>3137.857142857143</v>
+        <v>3017.857142857143</v>
       </c>
       <c r="G3" t="n">
-        <v>3451.642857142858</v>
+        <v>3324.285714285715</v>
       </c>
       <c r="H3" t="n">
-        <v>3782.857142857143</v>
+        <v>3732.857142857143</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>24.58%</t>
+          <t>23.84%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>25.5</v>
+        <v>24.76</v>
       </c>
       <c r="L3" t="n">
         <v>-2895500</v>
@@ -1012,20 +1012,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>813-887</t>
+          <t>801-879</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>739.6428571428571</v>
+        <v>723.75</v>
       </c>
       <c r="F4" t="n">
-        <v>994.4642857142858</v>
+        <v>992.3214285714286</v>
       </c>
       <c r="G4" t="n">
-        <v>1093.910714285714</v>
+        <v>1091.553571428572</v>
       </c>
       <c r="H4" t="n">
-        <v>1245.714285714286</v>
+        <v>1257.321428571428</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>29.50%</t>
+          <t>29.90%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11208588751.85</v>
+        <v>11360474153.16</v>
       </c>
       <c r="L4" t="n">
         <v>-21636100</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1063,40 +1063,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2324-2416</t>
+          <t>1883-2007</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2231.785714285714</v>
+        <v>1758.571428571428</v>
       </c>
       <c r="F5" t="n">
-        <v>2552.142857142857</v>
+        <v>2188.75</v>
       </c>
       <c r="G5" t="n">
-        <v>2807.357142857143</v>
+        <v>2407.625</v>
       </c>
       <c r="H5" t="n">
-        <v>2869.642857142857</v>
+        <v>2612.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10.69%</t>
+          <t>18.01%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>461.97</v>
+        <v>15.82</v>
       </c>
       <c r="L5" t="n">
-        <v>10200200</v>
+        <v>-25253200</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1106,48 +1106,48 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10044-10556</t>
+          <t>2904-2996</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9531.25</v>
+        <v>2812.857142857143</v>
       </c>
       <c r="F6" t="n">
-        <v>11271.42857142857</v>
+        <v>3124.285714285714</v>
       </c>
       <c r="G6" t="n">
-        <v>12398.57142857143</v>
+        <v>3424.285714285714</v>
       </c>
       <c r="H6" t="n">
-        <v>12940.17857142857</v>
+        <v>3436.714285714286</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14.26%</t>
+          <t>8.35%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>68.78</v>
+        <v>3173800703.82</v>
       </c>
       <c r="L6" t="n">
-        <v>-4000</v>
+        <v>1793800</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1165,20 +1165,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2356-2444</t>
+          <t>2304-2396</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2267.142857142857</v>
+        <v>2210.714285714286</v>
       </c>
       <c r="F7" t="n">
-        <v>2572.857142857143</v>
+        <v>2529.285714285714</v>
       </c>
       <c r="G7" t="n">
-        <v>2830.142857142857</v>
+        <v>2782.214285714286</v>
       </c>
       <c r="H7" t="n">
-        <v>2872.857142857143</v>
+        <v>2839.285714285714</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.22%</t>
+          <t>15.02%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>55.29</v>
+        <v>54.59</v>
       </c>
       <c r="L7" t="n">
         <v>-2979900</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1216,40 +1216,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3936-4144</t>
+          <t>1544-1776</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3728.214285714286</v>
+        <v>1310.714285714286</v>
       </c>
       <c r="F8" t="n">
-        <v>4420.357142857143</v>
+        <v>2112.321428571428</v>
       </c>
       <c r="G8" t="n">
-        <v>4862.392857142858</v>
+        <v>2420</v>
       </c>
       <c r="H8" t="n">
-        <v>5065.357142857143</v>
+        <v>2896.071428571428</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16.58%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>39.97</v>
+        <v>1.87</v>
       </c>
       <c r="L8" t="n">
-        <v>-30506300</v>
+        <v>56554200</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1267,36 +1267,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1711-1939</t>
+          <t>3206-3454</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1484.285714285714</v>
+        <v>2959.285714285714</v>
       </c>
       <c r="F9" t="n">
-        <v>2265.892857142857</v>
+        <v>3792.142857142857</v>
       </c>
       <c r="G9" t="n">
-        <v>2492.482142857143</v>
+        <v>4171.357142857143</v>
       </c>
       <c r="H9" t="n">
-        <v>3029.642857142857</v>
+        <v>4582.142857142857</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.23%</t>
+          <t>23.21%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1.77</v>
+        <v>8821417906.99</v>
       </c>
       <c r="L9" t="n">
-        <v>56554200</v>
+        <v>6595200</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1310,44 +1310,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1922-2038</t>
+          <t>3531-3849</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1805.892857142857</v>
+        <v>3213.214285714286</v>
       </c>
       <c r="F10" t="n">
-        <v>2210.535714285714</v>
+        <v>4316.071428571428</v>
       </c>
       <c r="G10" t="n">
-        <v>2431.589285714286</v>
+        <v>4747.678571428572</v>
       </c>
       <c r="H10" t="n">
-        <v>2613.035714285714</v>
+        <v>5406.071428571429</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18.35%</t>
+          <t>32.82%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>16.1</v>
+        <v>519.23</v>
       </c>
       <c r="L10" t="n">
-        <v>-25253200</v>
+        <v>-1117600</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1369,40 +1369,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3369-3591</t>
+          <t>729-781</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3145.714285714286</v>
+        <v>678.3928571428571</v>
       </c>
       <c r="F11" t="n">
-        <v>3905.357142857143</v>
+        <v>854.4642857142858</v>
       </c>
       <c r="G11" t="n">
-        <v>4295.892857142858</v>
+        <v>939.9107142857144</v>
       </c>
       <c r="H11" t="n">
-        <v>4637.857142857143</v>
+        <v>1026.964285714286</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>23.40%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8891980896.129999</v>
+        <v>2.36</v>
       </c>
       <c r="L11" t="n">
-        <v>6595200</v>
+        <v>-4702400</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1412,44 +1412,44 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3601-3899</t>
+          <t>3708-3932</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3302.142857142857</v>
+        <v>3482.5</v>
       </c>
       <c r="F12" t="n">
-        <v>4341.785714285714</v>
+        <v>4221.785714285715</v>
       </c>
       <c r="G12" t="n">
-        <v>4775.964285714285</v>
+        <v>4643.964285714286</v>
       </c>
       <c r="H12" t="n">
-        <v>5374.285714285714</v>
+        <v>4896.785714285715</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>33.73%</t>
+          <t>16.00%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>533.61</v>
+        <v>38.61</v>
       </c>
       <c r="L12" t="n">
-        <v>-1117600</v>
+        <v>-30506300</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1467,24 +1467,24 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1699-1831</t>
+          <t>1619-1761</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1567.321428571429</v>
+        <v>1476.25</v>
       </c>
       <c r="F13" t="n">
-        <v>2024.285714285714</v>
+        <v>1970.714285714286</v>
       </c>
       <c r="G13" t="n">
-        <v>2226.714285714286</v>
+        <v>2167.785714285715</v>
       </c>
       <c r="H13" t="n">
-        <v>2475.535714285714</v>
+        <v>2459.464285714286</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1493,11 +1493,11 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13.15%</t>
+          <t>13.30%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>65.01000000000001</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="L13" t="n">
         <v>766200</v>
@@ -1514,48 +1514,48 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>747-793</t>
+          <t>5821-6329</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>701.9642857142858</v>
+        <v>5311.607142857143</v>
       </c>
       <c r="F14" t="n">
-        <v>858.0357142857143</v>
+        <v>7036.607142857142</v>
       </c>
       <c r="G14" t="n">
-        <v>943.8392857142859</v>
+        <v>7743.75</v>
       </c>
       <c r="H14" t="n">
-        <v>1010.535714285714</v>
+        <v>8686.607142857143</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>23.77%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>2.1</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-4702400</v>
+        <v>745400</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1565,44 +1565,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8821-9579</t>
+          <t>1223-1317</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8064.285714285714</v>
+        <v>1129.107142857143</v>
       </c>
       <c r="F15" t="n">
-        <v>10655.35714285714</v>
+        <v>1447.142857142857</v>
       </c>
       <c r="G15" t="n">
-        <v>11732.14285714286</v>
+        <v>1591.857142857143</v>
       </c>
       <c r="H15" t="n">
-        <v>13167.85714285714</v>
+        <v>1750.892857142857</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10.61%</t>
+          <t>15.31%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>6.92</v>
+        <v>44.15</v>
       </c>
       <c r="L15" t="n">
-        <v>-1912500</v>
+        <v>-5503000</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>MBMA.JK</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1624,36 +1624,36 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1317-1403</t>
+          <t>622-698</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1230.357142857143</v>
+        <v>545.3571428571429</v>
       </c>
       <c r="F16" t="n">
-        <v>1527.5</v>
+        <v>803.2142857142857</v>
       </c>
       <c r="G16" t="n">
-        <v>1680.25</v>
+        <v>908.2142857142857</v>
       </c>
       <c r="H16" t="n">
-        <v>1817.5</v>
+        <v>1048.214285714286</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>16.09%</t>
+          <t>17.72%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>59.65</v>
+        <v>25.07</v>
       </c>
       <c r="L16" t="n">
-        <v>-5503000</v>
+        <v>-73678300</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EMAS.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1675,40 +1675,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7807-8293</t>
+          <t>4739-4901</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7321.428571428572</v>
+        <v>4576.25</v>
       </c>
       <c r="F17" t="n">
-        <v>8943.75</v>
+        <v>5112.321428571428</v>
       </c>
       <c r="G17" t="n">
-        <v>9838.125</v>
+        <v>5604.821428571428</v>
       </c>
       <c r="H17" t="n">
-        <v>10462.5</v>
+        <v>5623.553571428572</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24.56%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>9334296337.620001</v>
+        <v>3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>-658500</v>
+        <v>33741800</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1718,48 +1718,48 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HRUM.JK</t>
+          <t>EMAS.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1034-1106</t>
+          <t>7738-8262</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>962.3214285714286</v>
+        <v>7215.178571428572</v>
       </c>
       <c r="F18" t="n">
-        <v>1210.892857142857</v>
+        <v>8968.75</v>
       </c>
       <c r="G18" t="n">
-        <v>1331.982142857143</v>
+        <v>9865.625</v>
       </c>
       <c r="H18" t="n">
-        <v>1455.892857142857</v>
+        <v>10618.75</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>24.04%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2.85</v>
+        <v>9134808051.059999</v>
       </c>
       <c r="L18" t="n">
-        <v>746000</v>
+        <v>-658500</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1777,20 +1777,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>249-287</t>
+          <t>224-264</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>211.1071428571429</v>
+        <v>184.6428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>341.9285714285714</v>
+        <v>320.7857142857143</v>
       </c>
       <c r="G19" t="n">
-        <v>376.1214285714286</v>
+        <v>352.8642857142858</v>
       </c>
       <c r="H19" t="n">
-        <v>470.1785714285714</v>
+        <v>453.7857142857143</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1799,11 +1799,11 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>65.11%</t>
+          <t>63.76%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>14.76</v>
+        <v>14.48</v>
       </c>
       <c r="L19" t="n">
         <v>-104512900</v>
@@ -1828,20 +1828,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11262-11688</t>
+          <t>10870-11380</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10834.82142857143</v>
+        <v>10358.92857142857</v>
       </c>
       <c r="F20" t="n">
-        <v>12325.89285714286</v>
+        <v>12143.75</v>
       </c>
       <c r="G20" t="n">
-        <v>13558.48214285714</v>
+        <v>13358.125</v>
       </c>
       <c r="H20" t="n">
-        <v>13813.39285714286</v>
+        <v>13925</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1850,11 +1850,11 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17.63%</t>
+          <t>17.21%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>6699663422.45</v>
+        <v>6538221289.39</v>
       </c>
       <c r="L20" t="n">
         <v>328500</v>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1879,36 +1879,36 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5962-6438</t>
+          <t>116-124</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5487.5</v>
+        <v>108.5357142857143</v>
       </c>
       <c r="F21" t="n">
-        <v>7088.392857142857</v>
+        <v>130.4642857142857</v>
       </c>
       <c r="G21" t="n">
-        <v>7797.232142857143</v>
+        <v>143.5107142857143</v>
       </c>
       <c r="H21" t="n">
-        <v>8607.142857142857</v>
+        <v>145.9642857142857</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>25.39%</t>
+          <t>51.53%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>127.37</v>
+        <v>56.81</v>
       </c>
       <c r="L21" t="n">
-        <v>745400</v>
+        <v>316433400</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2387,18 +2387,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>114.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-1.2%</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-20.0%</t>
         </is>
       </c>
     </row>
@@ -2434,43 +2434,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-16.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>96</v>
       </c>
       <c r="C5" t="n">
-        <v>76.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-14.7%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C6" t="n">
         <v>74.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
     </row>
@@ -2488,97 +2488,97 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-4.9%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-24.5%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>92</v>
       </c>
       <c r="C9" t="n">
-        <v>69.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-15.5%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" t="n">
-        <v>67.8</v>
+        <v>67</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-13.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>90</v>
       </c>
       <c r="C11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-3.8%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>63.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-19.7%</t>
         </is>
       </c>
     </row>
@@ -2589,104 +2589,104 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-15.3%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>58.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-23.1%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-17.8%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>MBMA.JK</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>84</v>
       </c>
       <c r="C16" t="n">
-        <v>57.4</v>
+        <v>57</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-27.1%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EMAS.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>83</v>
       </c>
       <c r="C17" t="n">
-        <v>52</v>
+        <v>52.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-10.3%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HRUM.JK</t>
+          <t>EMAS.JK</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C18" t="n">
         <v>52</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-8.0%</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-23.3%</t>
         </is>
       </c>
     </row>
@@ -2722,1267 +2722,1267 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-9.9%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>79</v>
       </c>
       <c r="C21" t="n">
-        <v>48.4</v>
+        <v>48</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-26.4%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>UNTR.JK</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>78</v>
       </c>
       <c r="C22" t="n">
-        <v>48</v>
+        <v>44.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-7.5%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C23" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PSAB.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>76</v>
       </c>
       <c r="C24" t="n">
-        <v>46.8</v>
+        <v>40.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-10.1%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UNTR.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>75</v>
       </c>
       <c r="C25" t="n">
-        <v>44.8</v>
+        <v>40</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-25.7%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ARCI.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" t="n">
-        <v>42.6</v>
+        <v>39.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-16.3%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MBMA.JK</t>
+          <t>DADA.JK</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C27" t="n">
-        <v>42</v>
+        <v>38.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-20.6%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>ARCI.JK</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" t="n">
-        <v>40.6</v>
+        <v>34.6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-21.7%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BULL.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>70</v>
       </c>
       <c r="C29" t="n">
-        <v>39.8</v>
+        <v>34</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-35.2%</t>
+          <t>-13.4%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>69</v>
       </c>
       <c r="C30" t="n">
-        <v>38.4</v>
+        <v>28.2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-47.7%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>68</v>
       </c>
       <c r="C31" t="n">
-        <v>37.4</v>
+        <v>26.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-21.3%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>PSAB.JK</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C32" t="n">
-        <v>34</v>
+        <v>26.8</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-27.3%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>TPIA.JK</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>66</v>
       </c>
       <c r="C33" t="n">
-        <v>30</v>
+        <v>24.6</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-18.1%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>INKP.JK</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>65</v>
       </c>
       <c r="C34" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-26.0%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>HRUM.JK</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>64</v>
       </c>
       <c r="C35" t="n">
-        <v>28.2</v>
+        <v>22</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-22.2%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RATU.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C36" t="n">
-        <v>25.4</v>
+        <v>22</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-52.3%</t>
+          <t>-25.4%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C37" t="n">
-        <v>25.4</v>
+        <v>21.6</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-63.3%</t>
+          <t>-19.1%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SUPA.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>25</v>
+        <v>21.4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-19.0%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>VKTR.JK</t>
+          <t>BRIS.JK</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C39" t="n">
-        <v>24</v>
+        <v>20.8</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-10.6%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LPKR.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C40" t="n">
-        <v>23.6</v>
+        <v>20.4</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-68.5%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AMMN.JK</t>
+          <t>AMRT.JK</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C41" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-28.2%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C42" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-20.9%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C43" t="n">
-        <v>21.6</v>
+        <v>18</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-25.0%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BRIS.JK</t>
+          <t>BBYB.JK</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>54</v>
       </c>
       <c r="C44" t="n">
-        <v>20.8</v>
+        <v>17.4</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-50.8%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>GOTO.JK</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>53</v>
       </c>
       <c r="C45" t="n">
-        <v>20.4</v>
+        <v>16.8</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-22.5%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>IRSX.JK</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>52</v>
       </c>
       <c r="C46" t="n">
-        <v>20</v>
+        <v>16.6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-42.7%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AMRT.JK</t>
+          <t>EMTK.JK</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>51</v>
       </c>
       <c r="C47" t="n">
-        <v>19.8</v>
+        <v>16.2</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-52.0%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DADA.JK</t>
+          <t>ICBP.JK</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>50</v>
       </c>
       <c r="C48" t="n">
-        <v>18.6</v>
+        <v>15</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-16.9%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C49" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-38.3%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>LPKR.JK</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>48</v>
       </c>
       <c r="C50" t="n">
-        <v>18</v>
+        <v>13.6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-32.8%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>JPFA.JK</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C51" t="n">
-        <v>18</v>
+        <v>13.2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-25.9%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DSSA.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C52" t="n">
-        <v>17.4</v>
+        <v>12.8</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-55.6%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BBYB.JK</t>
+          <t>AMMN.JK</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>45</v>
       </c>
       <c r="C53" t="n">
-        <v>17.4</v>
+        <v>12</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-30.1%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C54" t="n">
-        <v>16.8</v>
+        <v>12</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-32.2%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GOTO.JK</t>
+          <t>NICL.JK</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>43</v>
       </c>
       <c r="C55" t="n">
-        <v>16.8</v>
+        <v>10.8</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-52.1%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EMTK.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>41</v>
       </c>
       <c r="C56" t="n">
-        <v>16.2</v>
+        <v>10.4</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-54.2%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ICBP.JK</t>
+          <t>BULL.JK</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>40</v>
       </c>
       <c r="C57" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-44.5%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>39</v>
       </c>
       <c r="C58" t="n">
-        <v>14.8</v>
+        <v>8.4</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-48.3%</t>
+          <t>-42.0%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>39</v>
       </c>
       <c r="C59" t="n">
-        <v>14.8</v>
+        <v>8.4</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-49.1%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>BBCA.JK</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C60" t="n">
-        <v>13.2</v>
+        <v>7.8</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-47.2%</t>
+          <t>-17.2%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>COIN.JK</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C61" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-73.0%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>PBSA.JK</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C62" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-56.7%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NICL.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C63" t="n">
-        <v>10.8</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-46.8%</t>
+          <t>-51.0%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C64" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-40.0%</t>
+          <t>-59.7%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>PNLF.JK</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>32</v>
       </c>
       <c r="C65" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-29.9%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BBCA.JK</t>
+          <t>CPRO.JK</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C66" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-37.2%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>30</v>
       </c>
       <c r="C67" t="n">
-        <v>7.8</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-54.3%</t>
+          <t>-61.3%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>COIN.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>30</v>
       </c>
       <c r="C68" t="n">
-        <v>7.8</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-42.4%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PBSA.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>30</v>
       </c>
       <c r="C69" t="n">
-        <v>7.8</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-53.5%</t>
+          <t>-56.0%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C70" t="n">
-        <v>7.199999999999999</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-50.2%</t>
+          <t>-70.9%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C71" t="n">
-        <v>6.6</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-58.2%</t>
+          <t>-56.8%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C72" t="n">
-        <v>6.6</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-55.6%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PNLF.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-25.0%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CPRO.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>22</v>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-51.6%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>WIFI.JK</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C75" t="n">
-        <v>5.399999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-61.6%</t>
+          <t>-54.2%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C76" t="n">
-        <v>5.399999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-52.0%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C77" t="n">
-        <v>5.399999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-53.5%</t>
+          <t>-32.1%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C78" t="n">
-        <v>5.399999999999999</v>
+        <v>3</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-69.0%</t>
+          <t>-16.0%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>DSSA.JK</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C79" t="n">
-        <v>5.399999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-54.6%</t>
+          <t>-36.9%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>EXCL.JK</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>5.399999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-53.7%</t>
+          <t>-42.5%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>WIFI.JK</t>
+          <t>GTSI.JK</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-50.6%</t>
+          <t>-51.2%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EXCL.JK</t>
+          <t>TOBA.JK</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C82" t="n">
         <v>1.8</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-42.7%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GTSI.JK</t>
+          <t>DEWA.JK</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C83" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-45.8%</t>
+          <t>-49.7%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TOBA.JK</t>
+          <t>BUMI.JK</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C84" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-52.6%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DEWA.JK</t>
+          <t>SUPA.JK</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-46.3%</t>
+          <t>-31.3%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BUMI.JK</t>
+          <t>RMKE.JK</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-63.1%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>RMKE.JK</t>
+          <t>BBKP.JK</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-63.2%</t>
+          <t>-34.0%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BBKP.JK</t>
+          <t>TRUE.JK</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-70.8%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TRUE.JK</t>
+          <t>BKSL.JK</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-67.5%</t>
+          <t>-40.8%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BKSL.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C90" t="n">
-        <v>-1.2</v>
+        <v>-3</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-44.2%</t>
         </is>
       </c>
     </row>
@@ -3993,14 +3993,14 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C91" t="n">
         <v>-3</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-46.1%</t>
         </is>
       </c>
     </row>
@@ -4011,32 +4011,50 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C92" t="n">
         <v>-3</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-56.3%</t>
+          <t>-62.6%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SSIA.JK</t>
+          <t>VKTR.JK</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93" t="n">
         <v>-6</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-40.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SSIA.JK</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>2</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-6</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>-39.8%</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4129,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -4119,17 +4137,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2939-3021</t>
+          <t>10184-10716</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>12607</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1793800</t>
+          <t>-4000</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4166,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>813-887</t>
+          <t>801-879</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4169,25 +4187,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10044-10556</t>
+          <t>2904-2996</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-4000</t>
+          <t>1793800</t>
         </is>
       </c>
     </row>
@@ -4206,12 +4224,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2356-2444</t>
+          <t>2304-2396</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4231,16 +4249,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1711-1939</t>
+          <t>1544-1776</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4268,12 +4286,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2659-2861</t>
+          <t>2489-2711</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4293,16 +4311,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>129-137</t>
+          <t>116-124</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>144</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4322,16 +4340,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>246-286</t>
+          <t>228-268</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>379</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4347,25 +4365,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VKTR.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>770-880</t>
+          <t>258-306</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>442</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2430100</t>
+          <t>-4347200</t>
         </is>
       </c>
     </row>
@@ -4380,16 +4398,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>979-1151</t>
+          <t>964-1136</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4401,7 +4419,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4409,7 +4427,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -4417,17 +4435,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2324-2416</t>
+          <t>1883-2007</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10200200</t>
+          <t>-25253200</t>
         </is>
       </c>
     </row>
@@ -4438,25 +4456,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7533-7917</t>
+          <t>3206-3454</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-65600</t>
+          <t>6595200</t>
         </is>
       </c>
     </row>
@@ -4467,25 +4485,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1008-1042</t>
+          <t>729-781</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>940</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2798000</t>
+          <t>-4702400</t>
         </is>
       </c>
     </row>
@@ -4496,25 +4514,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>316-360</t>
+          <t>3708-3932</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2360900</t>
+          <t>-30506300</t>
         </is>
       </c>
     </row>
@@ -4525,32 +4543,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3588-3952</t>
+          <t>5821-6329</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-128900</t>
+          <t>745400</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -4558,25 +4576,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3936-4144</t>
+          <t>4739-4901</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-30506300</t>
+          <t>33741800</t>
         </is>
       </c>
     </row>
@@ -4587,25 +4605,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1922-2038</t>
+          <t>4240-4340</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-25253200</t>
+          <t>8426900</t>
         </is>
       </c>
     </row>
@@ -4616,25 +4634,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3369-3591</t>
+          <t>3528-3612</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6595200</t>
+          <t>105416300</t>
         </is>
       </c>
     </row>
@@ -4645,25 +4663,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>747-793</t>
+          <t>94-114</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-4702400</t>
+          <t>-1255200</t>
         </is>
       </c>
     </row>
@@ -4674,25 +4692,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8821-9579</t>
+          <t>1450-1550</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1912500</t>
+          <t>-1514600</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4733,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>249-287</t>
+          <t>224-264</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>353</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4744,12 +4762,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11262-11688</t>
+          <t>10870-11380</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13558</t>
+          <t>13358</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4765,25 +4783,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BULL.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>416-472</t>
+          <t>5748-5952</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2075700</t>
+          <t>6227500</t>
         </is>
       </c>
     </row>
@@ -4794,25 +4812,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>BULL.JK</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6028-6222</t>
+          <t>352-408</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>562</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6227500</t>
+          <t>-2075700</t>
         </is>
       </c>
     </row>
@@ -4827,16 +4845,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1201-1299</t>
+          <t>1112-1218</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4848,7 +4866,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -4856,25 +4874,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3630-3710</t>
+          <t>1996-2104</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>105416300</t>
+          <t>10200200</t>
         </is>
       </c>
     </row>
@@ -4885,25 +4903,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4902-5058</t>
+          <t>957-993</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>33741800</t>
+          <t>-2798000</t>
         </is>
       </c>
     </row>
@@ -4914,25 +4932,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4226-4314</t>
+          <t>3374-3746</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8426900</t>
+          <t>-128900</t>
         </is>
       </c>
     </row>
@@ -4943,25 +4961,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SUPA.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>843-907</t>
+          <t>809-881</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>724900</t>
+          <t>-7662000</t>
         </is>
       </c>
     </row>
@@ -4972,32 +4990,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1572-1668</t>
+          <t>7135-7565</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1514600</t>
+          <t>-65600</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -5005,25 +5023,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>DADA.JK</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2109-2211</t>
+          <t>50-50</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4049500</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -5034,25 +5052,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3132-3248</t>
+          <t>331-341</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>385</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>13783000</t>
+          <t>37538300</t>
         </is>
       </c>
     </row>
@@ -5063,25 +5081,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EMTK.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>712-758</t>
+          <t>7701-8199</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5460200</t>
+          <t>-202100</t>
         </is>
       </c>
     </row>
@@ -5092,25 +5110,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>275-305</t>
+          <t>4584-4876</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-15489100</t>
+          <t>81700</t>
         </is>
       </c>
     </row>
@@ -5121,32 +5139,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EXCL.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2669-2851</t>
+          <t>162-178</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4119100</t>
+          <t>-18379100</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -5154,25 +5172,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>343-353</t>
+          <t>3040-3160</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>37538300</t>
+          <t>13783000</t>
         </is>
       </c>
     </row>
@@ -5183,25 +5201,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DADA.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>50-50</t>
+          <t>1943-2057</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4049500</t>
         </is>
       </c>
     </row>
@@ -5212,25 +5230,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>EMTK.JK</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>176-190</t>
+          <t>680-730</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>881</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-18379100</t>
+          <t>-5460200</t>
         </is>
       </c>
     </row>
@@ -5241,25 +5259,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>8059-8541</t>
+          <t>256-288</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>10149</t>
+          <t>374</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-202100</t>
+          <t>-15489100</t>
         </is>
       </c>
     </row>
@@ -5270,32 +5288,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>EXCL.JK</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4869-5131</t>
+          <t>2485-2675</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>81700</t>
+          <t>4119100</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -5303,25 +5321,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2298-2402</t>
+          <t>977-1013</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5002500</t>
+          <t>-34214900</t>
         </is>
       </c>
     </row>
@@ -5332,61 +5350,65 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>LPKR.JK</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>48</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>83-89</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-266800</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>AMRT.JK</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>51</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>1482-1558</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>1831</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="D44" t="n">
+        <v>58</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1396-1474</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1736</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>37773100</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="n">
-        <v>3</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>INDF.JK</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>48</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>6203-6347</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>7062</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-8356000</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5394,16 +5416,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7342-7558</t>
+          <t>7010-7240</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5415,91 +5437,87 @@
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>JPFA.JK</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1926-2024</t>
+          <t>2113-2227</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2865100</t>
+          <t>5002500</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LPKR.JK</t>
+          <t>CPRO.JK</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>89-95</t>
+          <t>53-55</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-266800</t>
+          <t>12850400</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1009-1041</t>
+          <t>1829-1931</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-34214900</t>
+          <t>2865100</t>
         </is>
       </c>
     </row>
@@ -5518,16 +5536,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>55-57</t>
+          <t>54-56</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5547,16 +5565,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>462-518</t>
+          <t>421-479</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>632</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5576,16 +5594,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2024-2176</t>
+          <t>1865-2025</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5609,16 +5627,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>5621-6379</t>
+          <t>5510-6290</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5870,10 +5888,10 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5960,16 +5978,16 @@
         <v>0.38872</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>8.255831000000001</v>
+        <v>7.9923058</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>1.580866</v>
+        <v>1.5300751</v>
       </c>
       <c r="J2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>603.21</v>
+        <v>603.08</v>
       </c>
     </row>
     <row r="3">
@@ -5999,16 +6017,16 @@
         <v>0.34335998</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>8.555555</v>
+        <v>8.053319</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>0.9947035</v>
+        <v>0.9365715</v>
       </c>
       <c r="J3" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>36</v>
+        <v>36.01</v>
       </c>
     </row>
     <row r="4">
@@ -6038,16 +6056,16 @@
         <v>0.43205002</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>6.007356</v>
+        <v>5.7645135</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>1.1481917</v>
+        <v>1.1013267</v>
       </c>
       <c r="J4" s="14" t="n">
         <v>2.444</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>122.35</v>
+        <v>122.3</v>
       </c>
     </row>
     <row r="5">
@@ -6077,16 +6095,16 @@
         <v>0.40405998</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>9.757265</v>
+        <v>9.49039</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>1.7056962</v>
+        <v>1.6592195</v>
       </c>
       <c r="J5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>376.13</v>
+        <v>376.17</v>
       </c>
     </row>
     <row r="6">
@@ -6116,94 +6134,94 @@
         <v>0.27552</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>10.734864</v>
+        <v>10.030011</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>2.3981366</v>
+        <v>2.2394364</v>
       </c>
       <c r="J6" s="14" t="n">
         <v>23.671</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>126.69</v>
+        <v>126.62</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PADI.JK</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>22</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0.24911</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>4.381</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>0.71615</v>
+      </c>
+      <c r="H7" t="n">
+        <v>27.225132</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>6.504065</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>5.093</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>JPFA.JK</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C8" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E8" s="13" t="n">
         <v>0.23401</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F8" s="13" t="n">
         <v>0.213</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G8" s="13" t="n">
         <v>0.06594999999999999</v>
       </c>
-      <c r="H7" s="12" t="n">
-        <v>8.186442</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>1.4640687</v>
-      </c>
-      <c r="J7" s="14" t="n">
+      <c r="H8" s="12" t="n">
+        <v>7.5625567</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>1.3519273</v>
+      </c>
+      <c r="J8" s="14" t="n">
         <v>59.254</v>
       </c>
-      <c r="K7" s="11" t="n">
-        <v>287.06</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PADI.JK</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>22</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0.24911</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>4.381</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>0.71615</v>
-      </c>
-      <c r="H8" t="n">
-        <v>27.559055</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>6.566604</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>5.093</v>
-      </c>
       <c r="K8" s="11" t="n">
-        <v>3.81</v>
+        <v>286.94</v>
       </c>
     </row>
     <row r="9">
@@ -6212,37 +6230,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BRIS.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E9" s="9" t="n">
-        <v>0.15604</v>
+      <c r="E9" s="8" t="n">
+        <v>0.24216999</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>0.31919</v>
-      </c>
-      <c r="H9" t="n">
-        <v>13.600049</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>1.9800292</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>0</v>
+        <v>0.025</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>0.15481</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>6.665986</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>24415.887</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>22.636</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>163.97</v>
+        <v>1567.66</v>
       </c>
     </row>
     <row r="10">
@@ -6251,76 +6269,76 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NICL.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>19</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>0.15277</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>0.09748999999999999</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>11.70549</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>1.7759134</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>138.994</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>170.86</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BRIS.JK</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>18</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E10" s="8" t="n">
-        <v>0.65794</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>-0.261</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>0.27632</v>
-      </c>
-      <c r="H10" t="n">
-        <v>19.395712</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>12.740077</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>51.3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>HRTA.JK</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>0.28483</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>1.009</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>0.023759998</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>17.75262</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>4.5087943</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>139.825</v>
+      <c r="E11" s="9" t="n">
+        <v>0.15604</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="H11" t="n">
+        <v>13.343081</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>1.9445131</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>155.47</v>
+        <v>164.13</v>
       </c>
     </row>
     <row r="12">
@@ -6329,76 +6347,76 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>NICL.JK</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E12" s="9" t="n">
-        <v>0.13904001</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>0.048460003</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>9.001377</v>
-      </c>
-      <c r="I12" s="11" t="n">
-        <v>1.206247</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <v>4.935</v>
+      <c r="E12" s="8" t="n">
+        <v>0.65794</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>-0.261</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>0.27632</v>
+      </c>
+      <c r="H12" t="n">
+        <v>17.4328</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>11.459667</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>0.378</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>94.43000000000001</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ARCI.JK</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>16</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>HRTA.JK</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E13" s="8" t="n">
-        <v>0.28336</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>0.879</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>0.21154</v>
-      </c>
-      <c r="H13" t="n">
-        <v>29.227558</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>120000</v>
+      <c r="E13" s="13" t="n">
+        <v>0.28483</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>0.023759998</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>16.732094</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>4.247415</v>
       </c>
       <c r="J13" s="14" t="n">
-        <v>118.6</v>
+        <v>139.825</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>57.48</v>
+        <v>155.39</v>
       </c>
     </row>
     <row r="14">
@@ -6407,11 +6425,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6419,25 +6437,25 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1173</v>
+        <v>0.14062001</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>0.40232</v>
+        <v>0.075</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>0.04955</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>7.94951</v>
+        <v>8.894536</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.92637515</v>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>0</v>
+        <v>1.1540078</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>12.229</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>537.14</v>
+        <v>94.44</v>
       </c>
     </row>
     <row r="15">
@@ -6446,76 +6464,76 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>ARCI.JK</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0.28336</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>0.21154</v>
+      </c>
+      <c r="H15" t="n">
+        <v>27.671425</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>113571.42</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>57.46</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>TPIA.JK</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>0.102419995</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>0.30543</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>7.8378377</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>0.7674631</v>
-      </c>
-      <c r="J15" s="14" t="n">
-        <v>21.136</v>
-      </c>
-      <c r="K15" s="11" t="n">
-        <v>44.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>INCO.JK</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>14</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>0.02158</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>0.06239</v>
-      </c>
-      <c r="H16" s="17" t="n">
-        <v>61.6486</v>
+      <c r="E16" s="13" t="n">
+        <v>0.42018002</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>4.295</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>19.639935</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>23754.79</v>
-      </c>
-      <c r="J16" s="11" t="n">
-        <v>0.173</v>
+        <v>133333.33</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>82.7</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>100.57</v>
+        <v>305.5</v>
       </c>
     </row>
     <row r="17">
@@ -6524,11 +6542,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6536,25 +6554,25 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.15277</v>
+        <v>0.1173</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>0.09748999999999999</v>
-      </c>
-      <c r="H17" t="n">
-        <v>12.63823</v>
+        <v>0.028</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>7.986299</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>1.9179865</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <v>138.994</v>
+        <v>0.93071413</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>170.91</v>
+        <v>537.17</v>
       </c>
     </row>
     <row r="18">
@@ -6563,11 +6581,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -6575,25 +6593,25 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.07034</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>0.647</v>
+        <v>0.102419995</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>0.144</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>0.26583</v>
-      </c>
-      <c r="H18" s="17" t="n">
-        <v>150.79942</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <v>5.537505</v>
-      </c>
-      <c r="J18" s="15" t="n">
-        <v>1.864</v>
+        <v>0.30543</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>7.5675673</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>0.74099886</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>21.136</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>55.04</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="19">
@@ -6602,7 +6620,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -6614,25 +6632,25 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0</v>
+        <v>0.02158</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>0.52018</v>
-      </c>
-      <c r="H19" t="n">
-        <v>18.312334</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>3.1180332</v>
-      </c>
-      <c r="J19" s="14" t="n">
-        <v>2.39</v>
+        <v>0.212</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>0.06239</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>60.483868</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>23275.861</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>0.173</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>273.04</v>
+        <v>100.44</v>
       </c>
     </row>
     <row r="20">
@@ -6641,37 +6659,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BBCA.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E20" s="8" t="n">
-        <v>0.21143</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>-0.027</v>
+      <c r="E20" s="9" t="n">
+        <v>0.07034</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0.647</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>0.53282</v>
-      </c>
-      <c r="H20" t="n">
-        <v>14.983519</v>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v>3.0593028</v>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>0</v>
+        <v>0.26583</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>145.12596</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>5.3039956</v>
+      </c>
+      <c r="J20" s="15" t="n">
+        <v>1.864</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>467.18</v>
+        <v>54.78</v>
       </c>
     </row>
     <row r="21">
@@ -6680,37 +6698,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E21" s="16" t="n">
-        <v>-0.04084</v>
+      <c r="E21" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>-0.69613</v>
+        <v>0.791</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>0.52018</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>11.345408</v>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="K21" s="15" t="n">
-        <v>-0.72</v>
+        <v>17.326008</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>2.9496593</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>273</v>
       </c>
     </row>
     <row r="22">
@@ -6719,7 +6737,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COIN.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -6730,26 +6748,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="16" t="n">
+        <v>-0.04084</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>-0.69613</v>
+      </c>
+      <c r="H22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>8.94</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>0.30952</v>
-      </c>
-      <c r="H22" s="17" t="n">
-        <v>209.33977</v>
-      </c>
       <c r="I22" s="14" t="n">
-        <v>10.5427065</v>
+        <v>11.032432</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>0.261</v>
-      </c>
-      <c r="K22" s="11" t="n">
-        <v>6.21</v>
+        <v>0.049</v>
+      </c>
+      <c r="K22" s="15" t="n">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="23">
@@ -6758,7 +6776,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PBSA.JK</t>
+          <t>BBCA.JK</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -6770,25 +6788,25 @@
         </is>
       </c>
       <c r="E23" s="8" t="n">
-        <v>0.31697</v>
+        <v>0.21143</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>-0.192</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>0.15842</v>
+        <v>-0.027</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>0.53282</v>
       </c>
       <c r="H23" t="n">
-        <v>16.14987</v>
+        <v>14.724781</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>4.886668</v>
-      </c>
-      <c r="J23" s="15" t="n">
-        <v>1.461</v>
+        <v>3.0046723</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>77.40000000000001</v>
+        <v>466.9</v>
       </c>
     </row>
     <row r="24">
@@ -6797,37 +6815,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>COIN.JK</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E24" s="8" t="n">
-        <v>0.33183</v>
+      <c r="E24" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>0.13921</v>
+        <v>8.94</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>0.30952</v>
       </c>
       <c r="H24" s="17" t="n">
-        <v>63.279</v>
+        <v>199.51924</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>440000</v>
-      </c>
-      <c r="J24" s="14" t="n">
-        <v>201.586</v>
+        <v>10.096668</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>0.261</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>20.86</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="25">
@@ -6836,37 +6854,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>PBSA.JK</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E25" s="9" t="n">
-        <v>0.12082</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>0.008</v>
+      <c r="E25" s="8" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="F25" s="16" t="n">
+        <v>-0.192</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.0806</v>
-      </c>
-      <c r="H25" s="10" t="n">
-        <v>10.863586</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>20789.475</v>
-      </c>
-      <c r="J25" s="14" t="n">
-        <v>32.802</v>
+        <v>0.15842</v>
+      </c>
+      <c r="H25" t="n">
+        <v>15.055571</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>4.5543747</v>
+      </c>
+      <c r="J25" s="15" t="n">
+        <v>1.461</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>218.16</v>
+        <v>77.38</v>
       </c>
     </row>
     <row r="26">
@@ -6875,37 +6893,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E26" s="9" t="n">
-        <v>0.12380999</v>
-      </c>
-      <c r="F26" s="16" t="n">
-        <v>-0.075</v>
+      <c r="E26" s="8" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0.415</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.18375</v>
-      </c>
-      <c r="H26" t="n">
-        <v>24.275074</v>
+        <v>0.13921</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>61.776062</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>53676.47</v>
+        <v>426666.66</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>51.917</v>
+        <v>201.586</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>75.18000000000001</v>
+        <v>20.72</v>
       </c>
     </row>
     <row r="27">
@@ -6914,7 +6932,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -6926,64 +6944,64 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.14554</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>0.126</v>
+        <v>0.12380999</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>-0.075</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.10163</v>
+        <v>0.18375</v>
       </c>
       <c r="H27" t="n">
-        <v>13.372472</v>
-      </c>
-      <c r="I27" s="15" t="n">
-        <v>2.0216365</v>
+        <v>27.31611</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>48823.527</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>2.102</v>
+        <v>51.917</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>76.65000000000001</v>
+        <v>60.77</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="n">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>BRPT.JK</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PGAS.JK</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>11</v>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E28" s="13" t="n">
-        <v>0.35876</v>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>3.509</v>
-      </c>
-      <c r="G28" s="13" t="n">
-        <v>0.09752</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>14.110708</v>
+      <c r="E28" s="9" t="n">
+        <v>0.12082</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>0.0806</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>9.412305</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>64791.668</v>
+        <v>17982.457</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>107.818</v>
+        <v>32.802</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>110.2</v>
+        <v>217.8</v>
       </c>
     </row>
     <row r="29">
@@ -6992,7 +7010,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -7004,25 +7022,25 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.11936</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0.14554</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>0.126</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.06455</v>
-      </c>
-      <c r="H29" s="17" t="n">
-        <v>59.68331</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>10.15544</v>
-      </c>
-      <c r="J29" s="11" t="n">
-        <v>0.216</v>
+        <v>0.10163</v>
+      </c>
+      <c r="H29" t="n">
+        <v>12.994645</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>1.9624665</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>2.102</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>8.210000000000001</v>
+        <v>76.56999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -7031,11 +7049,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PNLF.JK</t>
+          <t>IRSX.JK</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7043,64 +7061,64 @@
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.05041</v>
+        <v>0.11936</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.15737</v>
-      </c>
-      <c r="H30" s="10" t="n">
-        <v>4.815534</v>
-      </c>
-      <c r="I30" s="11" t="n">
-        <v>0.25498217</v>
+        <v>0.06455</v>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>57.03422</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>9.326425</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>51.5</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>CPRO.JK</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>10</v>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>BRPT.JK</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E31" s="9" t="n">
-        <v>0.10436</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>0.041550003</v>
-      </c>
-      <c r="H31" s="10" t="n">
-        <v>8.260869</v>
-      </c>
-      <c r="I31" s="11" t="n">
-        <v>0.8504416299999999</v>
+      <c r="E31" s="13" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>3.509</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>0.09752</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>13.6252165</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>62500</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>43.245</v>
+        <v>107.818</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>6.9</v>
+        <v>110.09</v>
       </c>
     </row>
     <row r="32">
@@ -7109,37 +7127,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RATU.JK</t>
+          <t>PNLF.JK</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>0.45251998</v>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>0.05041</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>-0.183</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>0.31559</v>
-      </c>
-      <c r="H32" s="17" t="n">
-        <v>54.06195</v>
-      </c>
-      <c r="I32" s="14" t="n">
-        <v>326470.56</v>
-      </c>
-      <c r="J32" s="14" t="n">
-        <v>36.548</v>
+        <v>-0.07199999999999999</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>0.15737</v>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v>4.5454545</v>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>0.24058802</v>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>102.66</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="33">
@@ -7148,37 +7166,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>CPRO.JK</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>-0.29015</v>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>0.671</v>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>0.10436</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>0.081</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>-0.21053</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v>4.715777</v>
+        <v>0.041550003</v>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>7.826087</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>0.8056815000000001</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>65.76600000000001</v>
-      </c>
-      <c r="K33" s="15" t="n">
-        <v>0</v>
+        <v>43.245</v>
+      </c>
+      <c r="K33" s="11" t="n">
+        <v>6.9</v>
       </c>
     </row>
     <row r="34">
@@ -7187,7 +7205,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -7198,26 +7216,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E34" s="8" t="n">
-        <v>0.22038001</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G34" s="8" t="n">
-        <v>0.23266001</v>
-      </c>
-      <c r="H34" s="17" t="n">
-        <v>423.28766</v>
-      </c>
-      <c r="I34" s="14" t="n">
-        <v>1545000</v>
+      <c r="E34" s="16" t="n">
+        <v>-0.29015</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>-0.21053</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>4.042094</v>
       </c>
       <c r="J34" s="14" t="n">
-        <v>239.827</v>
-      </c>
-      <c r="K34" s="11" t="n">
-        <v>18.25</v>
+        <v>65.76600000000001</v>
+      </c>
+      <c r="K34" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -7226,7 +7244,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -7237,26 +7255,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E35" s="9" t="n">
-        <v>0.05801</v>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="G35" s="9" t="n">
-        <v>0.01754</v>
-      </c>
-      <c r="H35" t="n">
-        <v>29.029615</v>
+      <c r="E35" s="8" t="n">
+        <v>0.45251998</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>-0.183</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>52.144535</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>206666.67</v>
+        <v>313235.28</v>
       </c>
       <c r="J35" s="14" t="n">
-        <v>276.511</v>
+        <v>36.548</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>170.86</v>
+        <v>102.12</v>
       </c>
     </row>
     <row r="36">
@@ -7265,7 +7283,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -7277,25 +7295,25 @@
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.045900002</v>
+        <v>0.05801</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.329</v>
+        <v>0.317</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.19652</v>
-      </c>
-      <c r="H36" s="17" t="n">
-        <v>143.88489</v>
+        <v>0.01754</v>
+      </c>
+      <c r="H36" t="n">
+        <v>29.246279</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>88888.89</v>
+        <v>207916.67</v>
       </c>
       <c r="J36" s="14" t="n">
-        <v>12.694</v>
+        <v>276.511</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>5.56</v>
+        <v>170.62</v>
       </c>
     </row>
     <row r="37">
@@ -7304,7 +7322,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -7316,25 +7334,25 @@
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.15447</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>0.034</v>
+        <v>0.045900002</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>0.329</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.091759995</v>
-      </c>
-      <c r="H37" t="n">
-        <v>39.336395</v>
+        <v>0.19652</v>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>134.82143</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>78541.664</v>
+        <v>83888.89</v>
       </c>
       <c r="J37" s="14" t="n">
-        <v>68.20699999999999</v>
+        <v>12.694</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>95.84</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="38">
@@ -7343,7 +7361,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -7355,25 +7373,25 @@
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.06432</v>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>1.905</v>
-      </c>
-      <c r="G38" s="8" t="n">
-        <v>0.24544</v>
-      </c>
-      <c r="H38" s="17" t="n">
-        <v>207.14287</v>
+        <v>0.15447</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>0.091759995</v>
+      </c>
+      <c r="H38" t="n">
+        <v>37.324387</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>7.1352997</v>
+        <v>74166.664</v>
       </c>
       <c r="J38" s="14" t="n">
-        <v>2.833</v>
+        <v>68.20699999999999</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>1.4</v>
+        <v>95.38</v>
       </c>
     </row>
     <row r="39">
@@ -7382,7 +7400,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -7393,26 +7411,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E39" s="8" t="n">
-        <v>0.23723</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="G39" s="9" t="n">
-        <v>0.14588</v>
+      <c r="E39" s="9" t="n">
+        <v>0.06432</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>1.905</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>0.24544</v>
       </c>
       <c r="H39" s="17" t="n">
-        <v>166.81778</v>
+        <v>195.68346</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>35.162148</v>
+        <v>6.692419</v>
       </c>
       <c r="J39" s="14" t="n">
-        <v>38.133</v>
+        <v>2.833</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>11.03</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="40">
@@ -7421,7 +7439,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -7432,26 +7450,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="8" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>0.65328</v>
+      <c r="E40" s="8" t="n">
+        <v>0.23723</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>0.14588</v>
       </c>
       <c r="H40" s="17" t="n">
-        <v>75.78323</v>
+        <v>158.5145</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>111874.99</v>
+        <v>33.44226</v>
       </c>
       <c r="J40" s="14" t="n">
-        <v>34.873</v>
+        <v>38.133</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>11.81</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="41">
@@ -7460,11 +7478,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7472,25 +7490,25 @@
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.15961</v>
-      </c>
-      <c r="F41" s="16" t="n">
-        <v>-0.012</v>
-      </c>
-      <c r="G41" s="9" t="n">
-        <v>0.075219996</v>
-      </c>
-      <c r="H41" s="10" t="n">
-        <v>10.495545</v>
-      </c>
-      <c r="I41" s="11" t="n">
-        <v>1.6605622</v>
+        <v>0</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>0.65328</v>
+      </c>
+      <c r="H41" s="17" t="n">
+        <v>72.09897599999999</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>105624.99</v>
       </c>
       <c r="J41" s="14" t="n">
-        <v>19.582</v>
+        <v>34.873</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>283.93</v>
+        <v>11.72</v>
       </c>
     </row>
   </sheetData>

--- a/reports/HEDGEFUND_TERMINAL.xlsx
+++ b/reports/HEDGEFUND_TERMINAL.xlsx
@@ -491,7 +491,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09 March 2026</t>
+          <t>11 March 2026</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -650,7 +650,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-25.3M</t>
+          <t>745400</t>
         </is>
       </c>
     </row>
@@ -667,15 +667,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.8M</t>
+          <t>-5.5M</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>69</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57.8</v>
+        <v>60.4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -753,37 +753,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3. Healthcare</t>
+          <t>3. Consumer Cyclical</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>55</v>
+        <v>58.5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-34.5M</t>
+          <t>297.8M</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4. Financial Services</t>
+          <t>4. Healthcare</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>50.9</v>
+        <v>53.5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>115.7M</t>
+          <t>-34.5M</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5. Consumer Cyclical</t>
+          <t>5. Financial Services</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>297.8M</t>
+          <t>115.7M</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -910,33 +910,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10184-10716</t>
+          <t>10104-10646</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9651.785714285714</v>
+        <v>9560.714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>11460.71428571429</v>
+        <v>11407.14285714286</v>
       </c>
       <c r="G2" t="n">
-        <v>12606.78571428572</v>
+        <v>12547.85714285714</v>
       </c>
       <c r="H2" t="n">
-        <v>13198.21428571429</v>
+        <v>13182.14285714286</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15.09%</t>
+          <t>15.96%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>155.87</v>
+        <v>6065695380.45</v>
       </c>
       <c r="L2" t="n">
         <v>-4000</v>
@@ -961,20 +961,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2489-2711</t>
+          <t>2587-2813</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2265.714285714286</v>
+        <v>2361.428571428572</v>
       </c>
       <c r="F3" t="n">
-        <v>3017.857142857143</v>
+        <v>3123.571428571428</v>
       </c>
       <c r="G3" t="n">
-        <v>3324.285714285715</v>
+        <v>3435.928571428572</v>
       </c>
       <c r="H3" t="n">
-        <v>3732.857142857143</v>
+        <v>3848.571428571428</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>23.84%</t>
+          <t>22.22%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>24.76</v>
+        <v>23.15</v>
       </c>
       <c r="L3" t="n">
         <v>-2895500</v>
@@ -1012,20 +1012,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>801-879</t>
+          <t>766-844</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>723.75</v>
+        <v>689.2857142857143</v>
       </c>
       <c r="F4" t="n">
-        <v>992.3214285714286</v>
+        <v>955</v>
       </c>
       <c r="G4" t="n">
-        <v>1091.553571428572</v>
+        <v>1050.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1257.321428571428</v>
+        <v>1215</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>29.90%</t>
+          <t>30.17%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11360474153.16</v>
+        <v>11462714164.39</v>
       </c>
       <c r="L4" t="n">
         <v>-21636100</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1063,40 +1063,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1883-2007</t>
+          <t>6059-6591</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1758.571428571428</v>
+        <v>5526.785714285715</v>
       </c>
       <c r="F5" t="n">
-        <v>2188.75</v>
+        <v>7333.035714285714</v>
       </c>
       <c r="G5" t="n">
-        <v>2407.625</v>
+        <v>8066.339285714286</v>
       </c>
       <c r="H5" t="n">
-        <v>2612.5</v>
+        <v>9064.285714285714</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18.01%</t>
+          <t>22.12%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>15.82</v>
+        <v>76.02</v>
       </c>
       <c r="L5" t="n">
-        <v>-25253200</v>
+        <v>745400</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1106,48 +1106,48 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2904-2996</t>
+          <t>1306-1404</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2812.857142857143</v>
+        <v>1207.678571428572</v>
       </c>
       <c r="F6" t="n">
-        <v>3124.285714285714</v>
+        <v>1537.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3424.285714285714</v>
+        <v>1691.25</v>
       </c>
       <c r="H6" t="n">
-        <v>3436.714285714286</v>
+        <v>1848.75</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8.35%</t>
+          <t>14.70%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3173800703.82</v>
+        <v>42.43</v>
       </c>
       <c r="L6" t="n">
-        <v>1793800</v>
+        <v>-5503000</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1165,40 +1165,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2304-2396</t>
+          <t>2905-2995</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2210.714285714286</v>
+        <v>2813.928571428572</v>
       </c>
       <c r="F7" t="n">
-        <v>2529.285714285714</v>
+        <v>3122.857142857143</v>
       </c>
       <c r="G7" t="n">
-        <v>2782.214285714286</v>
+        <v>3420.357142857143</v>
       </c>
       <c r="H7" t="n">
-        <v>2839.285714285714</v>
+        <v>3435.142857142857</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.02%</t>
+          <t>8.66%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>54.59</v>
+        <v>3291362138.87</v>
       </c>
       <c r="L7" t="n">
-        <v>-2979900</v>
+        <v>1793800</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1216,40 +1216,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1544-1776</t>
+          <t>2334-2426</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1310.714285714286</v>
+        <v>2240.714285714286</v>
       </c>
       <c r="F8" t="n">
-        <v>2112.321428571428</v>
+        <v>2559.285714285714</v>
       </c>
       <c r="G8" t="n">
-        <v>2420</v>
+        <v>2815.214285714286</v>
       </c>
       <c r="H8" t="n">
-        <v>2896.071428571428</v>
+        <v>2869.285714285714</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>14.70%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1.87</v>
+        <v>53.44</v>
       </c>
       <c r="L8" t="n">
-        <v>56554200</v>
+        <v>-2979900</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1267,40 +1267,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3206-3454</t>
+          <t>3904-4136</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2959.285714285714</v>
+        <v>3670.714285714286</v>
       </c>
       <c r="F9" t="n">
-        <v>3792.142857142857</v>
+        <v>4428.928571428572</v>
       </c>
       <c r="G9" t="n">
-        <v>4171.357142857143</v>
+        <v>4871.821428571429</v>
       </c>
       <c r="H9" t="n">
-        <v>4582.142857142857</v>
+        <v>5111.428571428572</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>23.21%</t>
+          <t>15.40%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>8821417906.99</v>
+        <v>37.2</v>
       </c>
       <c r="L9" t="n">
-        <v>6595200</v>
+        <v>-30506300</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1310,48 +1310,48 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3531-3849</t>
+          <t>3375-3625</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3213.214285714286</v>
+        <v>3125</v>
       </c>
       <c r="F10" t="n">
-        <v>4316.071428571428</v>
+        <v>3966.785714285714</v>
       </c>
       <c r="G10" t="n">
-        <v>4747.678571428572</v>
+        <v>4363.464285714286</v>
       </c>
       <c r="H10" t="n">
-        <v>5406.071428571429</v>
+        <v>4764.285714285714</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>32.82%</t>
+          <t>23.05%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>519.23</v>
+        <v>8759309511</v>
       </c>
       <c r="L10" t="n">
-        <v>-1117600</v>
+        <v>6595200</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1361,44 +1361,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>729-781</t>
+          <t>3839-4161</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>678.3928571428571</v>
+        <v>3515.714285714286</v>
       </c>
       <c r="F11" t="n">
-        <v>854.4642857142858</v>
+        <v>4636.071428571428</v>
       </c>
       <c r="G11" t="n">
-        <v>939.9107142857144</v>
+        <v>5099.678571428572</v>
       </c>
       <c r="H11" t="n">
-        <v>1026.964285714286</v>
+        <v>5743.571428571429</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>31.68%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2.36</v>
+        <v>501.3</v>
       </c>
       <c r="L11" t="n">
-        <v>-4702400</v>
+        <v>-1117600</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1412,48 +1412,48 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3708-3932</t>
+          <t>1653-1797</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3482.5</v>
+        <v>1509.107142857143</v>
       </c>
       <c r="F12" t="n">
-        <v>4221.785714285715</v>
+        <v>2008.571428571429</v>
       </c>
       <c r="G12" t="n">
-        <v>4643.964285714286</v>
+        <v>2209.428571428572</v>
       </c>
       <c r="H12" t="n">
-        <v>4896.785714285715</v>
+        <v>2502.321428571428</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16.00%</t>
+          <t>13.23%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>38.61</v>
+        <v>65.42</v>
       </c>
       <c r="L12" t="n">
-        <v>-30506300</v>
+        <v>766200</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>INKP.JK</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1471,40 +1471,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1619-1761</t>
+          <t>9278-10122</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1476.25</v>
+        <v>8433.035714285714</v>
       </c>
       <c r="F13" t="n">
-        <v>1970.714285714286</v>
+        <v>11316.96428571429</v>
       </c>
       <c r="G13" t="n">
-        <v>2167.785714285715</v>
+        <v>12511.60714285714</v>
       </c>
       <c r="H13" t="n">
-        <v>2459.464285714286</v>
+        <v>14104.46428571429</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13.30%</t>
+          <t>9.99%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>65.73999999999999</v>
+        <v>6.38</v>
       </c>
       <c r="L13" t="n">
-        <v>766200</v>
+        <v>-1912500</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1514,48 +1514,48 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5821-6329</t>
+          <t>708-762</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5311.607142857143</v>
+        <v>653.5714285714286</v>
       </c>
       <c r="F14" t="n">
-        <v>7036.607142857142</v>
+        <v>840.3571428571429</v>
       </c>
       <c r="G14" t="n">
-        <v>7743.75</v>
+        <v>924.3928571428572</v>
       </c>
       <c r="H14" t="n">
-        <v>8686.607142857143</v>
+        <v>1022.857142857143</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23.77%</t>
+          <t>4.10%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>81.59999999999999</v>
+        <v>2.62</v>
       </c>
       <c r="L14" t="n">
-        <v>745400</v>
+        <v>-4702400</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1573,40 +1573,40 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1223-1317</t>
+          <t>3684-3996</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1129.107142857143</v>
+        <v>3371.785714285714</v>
       </c>
       <c r="F15" t="n">
-        <v>1447.142857142857</v>
+        <v>4389.285714285714</v>
       </c>
       <c r="G15" t="n">
-        <v>1591.857142857143</v>
+        <v>4828.214285714285</v>
       </c>
       <c r="H15" t="n">
-        <v>1750.892857142857</v>
+        <v>5306.785714285714</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15.31%</t>
+          <t>10.59%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>44.15</v>
+        <v>10.55</v>
       </c>
       <c r="L15" t="n">
-        <v>-5503000</v>
+        <v>32300</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MBMA.JK</t>
+          <t>ARCI.JK</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1624,36 +1624,36 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>622-698</t>
+          <t>1677-1793</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>545.3571428571429</v>
+        <v>1561.964285714286</v>
       </c>
       <c r="F16" t="n">
-        <v>803.2142857142857</v>
+        <v>1942.142857142857</v>
       </c>
       <c r="G16" t="n">
-        <v>908.2142857142857</v>
+        <v>2136.357142857143</v>
       </c>
       <c r="H16" t="n">
-        <v>1048.214285714286</v>
+        <v>2290.892857142857</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17.72%</t>
+          <t>5.10%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>25.07</v>
+        <v>2.72</v>
       </c>
       <c r="L16" t="n">
-        <v>-73678300</v>
+        <v>-11431200</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1675,36 +1675,36 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4739-4901</t>
+          <t>1564-1796</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4576.25</v>
+        <v>1330.714285714286</v>
       </c>
       <c r="F17" t="n">
-        <v>5112.321428571428</v>
+        <v>2132.321428571428</v>
       </c>
       <c r="G17" t="n">
-        <v>5604.821428571428</v>
+        <v>2420</v>
       </c>
       <c r="H17" t="n">
-        <v>5623.553571428572</v>
+        <v>2916.071428571428</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>7.93%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>3.35</v>
+        <v>1.99</v>
       </c>
       <c r="L17" t="n">
-        <v>33741800</v>
+        <v>56554200</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EMAS.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1726,36 +1726,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7738-8262</t>
+          <t>1899-2021</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7215.178571428572</v>
+        <v>1776.25</v>
       </c>
       <c r="F18" t="n">
-        <v>8968.75</v>
+        <v>2200.714285714286</v>
       </c>
       <c r="G18" t="n">
-        <v>9865.625</v>
+        <v>2420.785714285715</v>
       </c>
       <c r="H18" t="n">
-        <v>10618.75</v>
+        <v>2619.464285714286</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>24.04%</t>
+          <t>17.27%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>9134808051.059999</v>
+        <v>15.22</v>
       </c>
       <c r="L18" t="n">
-        <v>-658500</v>
+        <v>-25253200</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1777,40 +1777,40 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>224-264</t>
+          <t>4831-4989</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>184.6428571428571</v>
+        <v>4672.142857142857</v>
       </c>
       <c r="F19" t="n">
-        <v>320.7857142857143</v>
+        <v>5190.178571428572</v>
       </c>
       <c r="G19" t="n">
-        <v>352.8642857142858</v>
+        <v>5658.928571428572</v>
       </c>
       <c r="H19" t="n">
-        <v>453.7857142857143</v>
+        <v>5709.196428571429</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>63.76%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>14.48</v>
+        <v>3.16</v>
       </c>
       <c r="L19" t="n">
-        <v>-104512900</v>
+        <v>33741800</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1820,28 +1820,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>EMAS.JK</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10870-11380</t>
+          <t>7751-8249</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10358.92857142857</v>
+        <v>7252.678571428572</v>
       </c>
       <c r="F20" t="n">
-        <v>12143.75</v>
+        <v>8918.75</v>
       </c>
       <c r="G20" t="n">
-        <v>13358.125</v>
+        <v>9810.625</v>
       </c>
       <c r="H20" t="n">
-        <v>13925</v>
+        <v>10481.25</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1850,18 +1850,18 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17.21%</t>
+          <t>23.73%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>6538221289.39</v>
+        <v>9018943865.370001</v>
       </c>
       <c r="L20" t="n">
-        <v>328500</v>
+        <v>-658500</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1871,44 +1871,44 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>HRUM.JK</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>116-124</t>
+          <t>1035-1115</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>108.5357142857143</v>
+        <v>954.4642857142857</v>
       </c>
       <c r="F21" t="n">
-        <v>130.4642857142857</v>
+        <v>1227.678571428571</v>
       </c>
       <c r="G21" t="n">
-        <v>143.5107142857143</v>
+        <v>1350.446428571429</v>
       </c>
       <c r="H21" t="n">
-        <v>145.9642857142857</v>
+        <v>1490.178571428571</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>51.53%</t>
+          <t>4.27%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>56.81</v>
+        <v>2.51</v>
       </c>
       <c r="L21" t="n">
-        <v>316433400</v>
+        <v>746000</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.9%</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-16.9%</t>
         </is>
       </c>
     </row>
@@ -2434,93 +2434,93 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-19.5%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>96</v>
       </c>
       <c r="C5" t="n">
-        <v>74.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-19.9%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" t="n">
-        <v>74.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-12.3%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>73</v>
+        <v>74.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-1.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>71.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-3.6%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>92</v>
       </c>
       <c r="C9" t="n">
-        <v>67</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2531,522 +2531,522 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C10" t="n">
         <v>67</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.2%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-5.7%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C12" t="n">
-        <v>63.6</v>
+        <v>67</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-13.5%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>INKP.JK</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>88</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-19.2%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" t="n">
-        <v>58.4</v>
+        <v>66</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-6.4%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>86</v>
       </c>
       <c r="C15" t="n">
-        <v>57.4</v>
+        <v>63</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-16.5%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MBMA.JK</t>
+          <t>ARCI.JK</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>84</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>62.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-27.1%</t>
+          <t>-14.5%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>83</v>
       </c>
       <c r="C17" t="n">
-        <v>52.4</v>
+        <v>61.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-23.6%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EMAS.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>82</v>
       </c>
       <c r="C18" t="n">
-        <v>52</v>
+        <v>59.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-14.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>81</v>
       </c>
       <c r="C19" t="n">
-        <v>49</v>
+        <v>52.4</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-8.7%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>EMAS.JK</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-8.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>HRUM.JK</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-16.3%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UNTR.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>78</v>
       </c>
       <c r="C22" t="n">
-        <v>44.8</v>
+        <v>49</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-23.3%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C23" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-6.9%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>76</v>
       </c>
       <c r="C24" t="n">
-        <v>40.6</v>
+        <v>48</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-33.7%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>PSAB.JK</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>75</v>
       </c>
       <c r="C25" t="n">
-        <v>40</v>
+        <v>46.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-22.9%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>UNTR.JK</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>74</v>
       </c>
       <c r="C26" t="n">
-        <v>39.6</v>
+        <v>44.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-6.9%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DADA.JK</t>
+          <t>MBMA.JK</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>73</v>
       </c>
       <c r="C27" t="n">
-        <v>38.6</v>
+        <v>42</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-16.6%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ARCI.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>72</v>
       </c>
       <c r="C28" t="n">
-        <v>34.6</v>
+        <v>40.6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-10.3%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>BULL.JK</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>70</v>
       </c>
       <c r="C29" t="n">
-        <v>34</v>
+        <v>39.8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-41.9%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>69</v>
       </c>
       <c r="C30" t="n">
-        <v>28.2</v>
+        <v>34</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-11.9%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>68</v>
       </c>
       <c r="C31" t="n">
-        <v>26.8</v>
+        <v>31.6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-19.6%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PSAB.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>26.8</v>
+        <v>28.2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-45.7%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TPIA.JK</t>
+          <t>VKTR.JK</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>66</v>
       </c>
       <c r="C33" t="n">
-        <v>24.6</v>
+        <v>27</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-37.1%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>65</v>
       </c>
       <c r="C34" t="n">
-        <v>23</v>
+        <v>26.8</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-24.9%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HRUM.JK</t>
+          <t>TPIA.JK</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>64</v>
       </c>
       <c r="C35" t="n">
-        <v>22</v>
+        <v>24.6</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-21.5%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C36" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-8.0%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>62</v>
       </c>
       <c r="C37" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-22.6%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-18.7%</t>
         </is>
       </c>
     </row>
@@ -3064,14 +3064,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-9.8%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-68.5%</t>
+          <t>-34.7%</t>
         </is>
       </c>
     </row>
@@ -3107,738 +3107,738 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>DADA.JK</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>56</v>
       </c>
       <c r="C42" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-20.6%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C43" t="n">
         <v>18</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-18.9%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BBYB.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C44" t="n">
-        <v>17.4</v>
+        <v>18</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-23.1%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GOTO.JK</t>
+          <t>DSSA.JK</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>53</v>
       </c>
       <c r="C45" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-33.1%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>BBYB.JK</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C46" t="n">
-        <v>16.6</v>
+        <v>17.4</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-42.7%</t>
+          <t>-49.5%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EMTK.JK</t>
+          <t>GOTO.JK</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>51</v>
       </c>
       <c r="C47" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-52.0%</t>
+          <t>-21.4%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ICBP.JK</t>
+          <t>EMTK.JK</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>50</v>
       </c>
       <c r="C48" t="n">
-        <v>15</v>
+        <v>16.2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-50.3%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>BUMI.JK</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49" t="n">
         <v>15</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-48.3%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LPKR.JK</t>
+          <t>ICBP.JK</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>13.6</v>
+        <v>15</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C51" t="n">
-        <v>13.2</v>
+        <v>15</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-35.8%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>LPKR.JK</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>46</v>
       </c>
       <c r="C52" t="n">
-        <v>12.8</v>
+        <v>13.6</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-55.6%</t>
+          <t>-30.5%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AMMN.JK</t>
+          <t>JPFA.JK</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>45</v>
       </c>
       <c r="C53" t="n">
-        <v>12</v>
+        <v>13.2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-20.5%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C54" t="n">
-        <v>12</v>
+        <v>12.8</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-54.6%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NICL.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>43</v>
       </c>
       <c r="C55" t="n">
-        <v>10.8</v>
+        <v>12</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-52.1%</t>
+          <t>-31.9%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RATU.JK</t>
+          <t>EXCL.JK</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>41</v>
       </c>
       <c r="C56" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-54.2%</t>
+          <t>-36.5%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BULL.JK</t>
+          <t>NICL.JK</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>40</v>
       </c>
       <c r="C57" t="n">
-        <v>9.800000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-44.5%</t>
+          <t>-49.2%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>39</v>
       </c>
       <c r="C58" t="n">
-        <v>8.4</v>
+        <v>10.4</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-42.0%</t>
+          <t>-55.7%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>39</v>
       </c>
       <c r="C59" t="n">
-        <v>8.4</v>
+        <v>10.4</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-54.2%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BBCA.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C60" t="n">
-        <v>7.8</v>
+        <v>10.4</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-71.3%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>COIN.JK</t>
+          <t>SUPA.JK</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C61" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-73.0%</t>
+          <t>-29.7%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PBSA.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C62" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-56.7%</t>
+          <t>-40.1%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C63" t="n">
-        <v>7.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-51.0%</t>
+          <t>-47.3%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C64" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-59.7%</t>
+          <t>-17.0%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PNLF.JK</t>
+          <t>BBCA.JK</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>32</v>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-16.0%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CPRO.JK</t>
+          <t>COIN.JK</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>32</v>
       </c>
       <c r="C66" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>-68.5%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>PBSA.JK</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C67" t="n">
-        <v>5.399999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-61.3%</t>
+          <t>-54.6%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C68" t="n">
-        <v>5.399999999999999</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-42.4%</t>
+          <t>-49.8%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C69" t="n">
-        <v>5.399999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-56.0%</t>
+          <t>-59.7%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>IRSX.JK</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C70" t="n">
-        <v>5.399999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-42.9%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>PNLF.JK</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C71" t="n">
-        <v>5.399999999999999</v>
+        <v>6</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-56.8%</t>
+          <t>-28.7%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>CPRO.JK</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C72" t="n">
-        <v>5.399999999999999</v>
+        <v>6</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-55.6%</t>
+          <t>-34.9%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C73" t="n">
         <v>5.399999999999999</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-60.5%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-70.3%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>WIFI.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C75" t="n">
-        <v>4.8</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-54.2%</t>
+          <t>-53.8%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C76" t="n">
-        <v>4.8</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-52.0%</t>
+          <t>-55.7%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C77" t="n">
-        <v>4.8</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-27.0%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>18</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-51.2%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DSSA.JK</t>
+          <t>WIFI.JK</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>17</v>
       </c>
       <c r="C79" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-36.9%</t>
+          <t>-50.8%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EXCL.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C80" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-42.5%</t>
+          <t>-29.8%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GTSI.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C81" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-16.7%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TOBA.JK</t>
+          <t>GTSI.JK</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C82" t="n">
         <v>1.8</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-42.7%</t>
+          <t>-50.4%</t>
         </is>
       </c>
     </row>
@@ -3856,14 +3856,14 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-43.6%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BUMI.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -3874,14 +3874,14 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-52.6%</t>
+          <t>-50.6%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SUPA.JK</t>
+          <t>RMKE.JK</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -3892,14 +3892,14 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-64.2%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>RMKE.JK</t>
+          <t>BBKP.JK</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -3910,14 +3910,14 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-63.1%</t>
+          <t>-31.9%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BBKP.JK</t>
+          <t>TRUE.JK</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -3928,43 +3928,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-71.3%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TRUE.JK</t>
+          <t>BKSL.JK</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-37.4%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BKSL.JK</t>
+          <t>AMMN.JK</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>6</v>
       </c>
       <c r="C89" t="n">
-        <v>-1.2</v>
+        <v>-3</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-40.8%</t>
+          <t>-28.5%</t>
         </is>
       </c>
     </row>
@@ -3975,68 +3975,68 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C90" t="n">
         <v>-3</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-44.2%</t>
+          <t>-42.3%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HUMI.JK</t>
+          <t>TOBA.JK</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C91" t="n">
         <v>-3</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-46.1%</t>
+          <t>-40.6%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TRIN.JK</t>
+          <t>HUMI.JK</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C92" t="n">
         <v>-3</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-62.6%</t>
+          <t>-45.5%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VKTR.JK</t>
+          <t>TRIN.JK</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C93" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-40.2%</t>
+          <t>-62.1%</t>
         </is>
       </c>
     </row>
@@ -4047,14 +4047,14 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94" t="n">
         <v>-6</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-36.6%</t>
         </is>
       </c>
     </row>
@@ -4137,12 +4137,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10184-10716</t>
+          <t>10104-10646</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>801-879</t>
+          <t>766-844</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4191,16 +4191,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2904-2996</t>
+          <t>2905-2995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4220,16 +4220,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2304-2396</t>
+          <t>2334-2426</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4245,25 +4245,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1544-1776</t>
+          <t>3839-4161</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>56554200</t>
+          <t>-1117600</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2489-2711</t>
+          <t>2587-2813</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4311,16 +4311,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>116-124</t>
+          <t>104-112</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>129</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4336,25 +4336,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>VKTR.JK</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>228-268</t>
+          <t>763-867</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7483200</t>
+          <t>-2430100</t>
         </is>
       </c>
     </row>
@@ -4365,25 +4365,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>258-306</t>
+          <t>240-276</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>378</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4347200</t>
+          <t>7483200</t>
         </is>
       </c>
     </row>
@@ -4394,25 +4394,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>964-1136</t>
+          <t>265-311</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>443</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-16450400</t>
+          <t>-4347200</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -4435,17 +4435,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1883-2007</t>
+          <t>6059-6591</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-25253200</t>
+          <t>745400</t>
         </is>
       </c>
     </row>
@@ -4456,25 +4456,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3206-3454</t>
+          <t>1306-1404</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6595200</t>
+          <t>-5503000</t>
         </is>
       </c>
     </row>
@@ -4485,25 +4485,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>729-781</t>
+          <t>3904-4136</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4702400</t>
+          <t>-30506300</t>
         </is>
       </c>
     </row>
@@ -4514,25 +4514,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3708-3932</t>
+          <t>3375-3625</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-30506300</t>
+          <t>6595200</t>
         </is>
       </c>
     </row>
@@ -4543,25 +4543,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>INKP.JK</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5821-6329</t>
+          <t>9278-10122</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>12512</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>745400</t>
+          <t>-1912500</t>
         </is>
       </c>
     </row>
@@ -4580,16 +4580,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4739-4901</t>
+          <t>4831-4989</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4605,25 +4605,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4240-4340</t>
+          <t>3519-3601</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8426900</t>
+          <t>105416300</t>
         </is>
       </c>
     </row>
@@ -4634,25 +4634,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3528-3612</t>
+          <t>98-118</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>105416300</t>
+          <t>-1255200</t>
         </is>
       </c>
     </row>
@@ -4663,25 +4663,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>94-114</t>
+          <t>4208-4312</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1255200</t>
+          <t>8426900</t>
         </is>
       </c>
     </row>
@@ -4696,16 +4696,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1450-1550</t>
+          <t>1505-1605</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4729,16 +4729,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>224-264</t>
+          <t>226-262</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>347</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4758,16 +4758,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10870-11380</t>
+          <t>11220-11780</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4783,25 +4783,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>BULL.JK</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5748-5952</t>
+          <t>372-424</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>562</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6227500</t>
+          <t>-2075700</t>
         </is>
       </c>
     </row>
@@ -4812,25 +4812,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BULL.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>352-408</t>
+          <t>5891-6109</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-2075700</t>
+          <t>6227500</t>
         </is>
       </c>
     </row>
@@ -4845,16 +4845,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1112-1218</t>
+          <t>1167-1273</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4866,7 +4866,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -4874,25 +4874,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1996-2104</t>
+          <t>337-347</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>392</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>10200200</t>
+          <t>37538300</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>DADA.JK</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -4911,17 +4911,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>957-993</t>
+          <t>50-50</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2798000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4932,25 +4932,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3374-3746</t>
+          <t>7947-8453</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>10082</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-128900</t>
+          <t>-202100</t>
         </is>
       </c>
     </row>
@@ -4961,25 +4961,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>809-881</t>
+          <t>4754-5046</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-7662000</t>
+          <t>81700</t>
         </is>
       </c>
     </row>
@@ -4990,32 +4990,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7135-7565</t>
+          <t>168-182</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-65600</t>
+          <t>-18379100</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -5023,25 +5023,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DADA.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>50-50</t>
+          <t>1911-2029</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10200200</t>
         </is>
       </c>
     </row>
@@ -5052,25 +5052,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>331-341</t>
+          <t>983-1017</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>37538300</t>
+          <t>-2798000</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -5089,17 +5089,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>7701-8199</t>
+          <t>3403-3777</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-202100</t>
+          <t>-128900</t>
         </is>
       </c>
     </row>
@@ -5110,25 +5110,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4584-4876</t>
+          <t>800-870</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>81700</t>
+          <t>-7662000</t>
         </is>
       </c>
     </row>
@@ -5139,25 +5139,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>162-178</t>
+          <t>6933-7367</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>8781</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-18379100</t>
+          <t>-65600</t>
         </is>
       </c>
     </row>
@@ -5176,16 +5176,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3040-3160</t>
+          <t>2894-3026</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5201,25 +5201,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>EMTK.JK</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1943-2057</t>
+          <t>706-754</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>903</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4049500</t>
+          <t>-5460200</t>
         </is>
       </c>
     </row>
@@ -5230,25 +5230,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EMTK.JK</t>
+          <t>EXCL.JK</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>680-730</t>
+          <t>2748-2952</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-5460200</t>
+          <t>4119100</t>
         </is>
       </c>
     </row>
@@ -5259,25 +5259,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>256-288</t>
+          <t>1992-2108</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-15489100</t>
+          <t>4049500</t>
         </is>
       </c>
     </row>
@@ -5288,25 +5288,25 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EXCL.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2485-2675</t>
+          <t>263-293</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>375</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4119100</t>
+          <t>-15489100</t>
         </is>
       </c>
     </row>
@@ -5325,16 +5325,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>977-1013</t>
+          <t>982-1018</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5354,16 +5354,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>83-89</t>
+          <t>86-92</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>112</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1396-1474</t>
+          <t>1397-1473</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5416,16 +5416,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7010-7240</t>
+          <t>7132-7368</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5445,16 +5445,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2113-2227</t>
+          <t>2268-2392</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5474,16 +5474,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>53-55</t>
+          <t>55-57</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5503,16 +5503,16 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1829-1931</t>
+          <t>1894-1996</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5565,16 +5565,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>421-479</t>
+          <t>418-478</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>636</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5594,16 +5594,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1865-2025</t>
+          <t>2010-2170</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2470</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5627,16 +5627,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>5510-6290</t>
+          <t>5538-6312</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>0.38872</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>7.9923058</v>
+        <v>8.136412999999999</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>1.5300751</v>
+        <v>1.558645</v>
       </c>
       <c r="J2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>603.08</v>
+        <v>603.46</v>
       </c>
     </row>
     <row r="3">
@@ -6017,16 +6017,16 @@
         <v>0.34335998</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>8.053319</v>
+        <v>8.280077</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>0.9365715</v>
+        <v>0.9624079</v>
       </c>
       <c r="J3" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>36.01</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="4">
@@ -6056,16 +6056,16 @@
         <v>0.43205002</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>5.7645135</v>
+        <v>5.9679527</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>1.1013267</v>
+        <v>1.1403809</v>
       </c>
       <c r="J4" s="14" t="n">
         <v>2.444</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>122.3</v>
+        <v>122.32</v>
       </c>
     </row>
     <row r="5">
@@ -6095,16 +6095,16 @@
         <v>0.40405998</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>9.49039</v>
+        <v>9.470098999999999</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>1.6592195</v>
+        <v>1.6545719</v>
       </c>
       <c r="J5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>376.17</v>
+        <v>375.92</v>
       </c>
     </row>
     <row r="6">
@@ -6134,10 +6134,10 @@
         <v>0.27552</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>10.030011</v>
+        <v>10.701311</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>2.2394364</v>
+        <v>2.38932</v>
       </c>
       <c r="J6" s="14" t="n">
         <v>23.671</v>
@@ -6173,10 +6173,10 @@
         <v>0.71615</v>
       </c>
       <c r="H7" t="n">
-        <v>27.225132</v>
+        <v>28.272251</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>6.504065</v>
+        <v>6.7542214</v>
       </c>
       <c r="J7" s="14" t="n">
         <v>5.093</v>
@@ -6212,16 +6212,16 @@
         <v>0.06594999999999999</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>7.5625567</v>
+        <v>6.77424</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>1.3519273</v>
+        <v>1.4516085</v>
       </c>
       <c r="J8" s="14" t="n">
         <v>59.254</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>286.94</v>
+        <v>343.95</v>
       </c>
     </row>
     <row r="9">
@@ -6251,16 +6251,16 @@
         <v>0.15481</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>6.665986</v>
+        <v>6.5968094</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>24415.887</v>
+        <v>24240.654</v>
       </c>
       <c r="J9" s="14" t="n">
         <v>22.636</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>1567.66</v>
+        <v>1572.73</v>
       </c>
     </row>
     <row r="10">
@@ -6269,11 +6269,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>BRIS.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6281,25 +6281,25 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.15277</v>
+        <v>0.15604</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>0.09748999999999999</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>11.70549</v>
+        <v>0.075</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="H10" t="n">
+        <v>13.4731455</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>1.7759134</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>138.994</v>
+        <v>1.9622712</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>170.86</v>
+        <v>164.03</v>
       </c>
     </row>
     <row r="11">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BRIS.JK</t>
+          <t>NICL.JK</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6319,104 +6319,104 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>0.15604</v>
-      </c>
-      <c r="F11" s="9" t="n">
+      <c r="E11" s="8" t="n">
+        <v>0.65794</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>-0.261</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>0.27632</v>
+      </c>
+      <c r="H11" t="n">
+        <v>18.525742</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>12.163893</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>51.28</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>HRTA.JK</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>0.28483</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>0.023759998</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>17.365578</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>4.410777</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>139.825</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>155.48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ELSA.JK</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>0.14062001</v>
+      </c>
+      <c r="F13" s="9" t="n">
         <v>0.075</v>
       </c>
-      <c r="G11" s="8" t="n">
-        <v>0.31919</v>
-      </c>
-      <c r="H11" t="n">
-        <v>13.343081</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>1.9445131</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="11" t="n">
-        <v>164.13</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NICL.JK</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>18</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0.65794</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>-0.261</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>0.27632</v>
-      </c>
-      <c r="H12" t="n">
-        <v>17.4328</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>11.459667</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="K12" s="11" t="n">
-        <v>51.34</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>HRTA.JK</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>0.28483</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>1.009</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0.023759998</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>16.732094</v>
-      </c>
-      <c r="I13" s="15" t="n">
-        <v>4.247415</v>
+      <c r="G13" s="9" t="n">
+        <v>0.04955</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>8.525736</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>1.1059241</v>
       </c>
       <c r="J13" s="14" t="n">
-        <v>139.825</v>
+        <v>12.229</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>155.39</v>
+        <v>94.42</v>
       </c>
     </row>
     <row r="14">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>ARCI.JK</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -6436,104 +6436,104 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E14" s="9" t="n">
-        <v>0.14062001</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>0.04955</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>8.894536</v>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>1.1540078</v>
+      <c r="E14" s="8" t="n">
+        <v>0.28336</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>0.21154</v>
+      </c>
+      <c r="H14" t="n">
+        <v>30.14246</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>123928.57</v>
       </c>
       <c r="J14" s="14" t="n">
-        <v>12.229</v>
+        <v>118.6</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>94.44</v>
+        <v>57.56</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ARCI.JK</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>TPIA.JK</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E15" s="8" t="n">
-        <v>0.28336</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>0.879</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>0.21154</v>
-      </c>
-      <c r="H15" t="n">
-        <v>27.671425</v>
+      <c r="E15" s="13" t="n">
+        <v>0.42018002</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>4.295</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>18.754076</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>113571.42</v>
+        <v>127777.77</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>118.6</v>
+        <v>82.7</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>57.46</v>
+        <v>306.6</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>TPIA.JK</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PWON.JK</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E16" s="13" t="n">
-        <v>0.42018002</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>4.295</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>0.2208</v>
-      </c>
-      <c r="H16" s="12" t="n">
-        <v>19.639935</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>133333.33</v>
+      <c r="E16" s="9" t="n">
+        <v>0.102419995</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>7.699235</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>0.754231</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>82.7</v>
+        <v>21.136</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>305.5</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="17">
@@ -6563,16 +6563,16 @@
         <v>0.40232</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>7.986299</v>
+        <v>7.9313364</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.93071413</v>
+        <v>0.92420566</v>
       </c>
       <c r="J17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>537.17</v>
+        <v>537.11</v>
       </c>
     </row>
     <row r="18">
@@ -6581,11 +6581,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -6593,25 +6593,25 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.102419995</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>0.30543</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>7.5675673</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>0.74099886</v>
-      </c>
-      <c r="J18" s="14" t="n">
-        <v>21.136</v>
+        <v>0.02158</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>0.06239</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>63.098564</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>24233.715</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>0.173</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>44.4</v>
+        <v>100.24</v>
       </c>
     </row>
     <row r="19">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -6632,25 +6632,25 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.02158</v>
+        <v>0.07034</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>0.06239</v>
+        <v>0.647</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>0.26583</v>
       </c>
       <c r="H19" s="17" t="n">
-        <v>60.483868</v>
+        <v>149.47137</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>23275.861</v>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>0.173</v>
+        <v>5.470788</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>1.864</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>100.44</v>
+        <v>54.86</v>
       </c>
     </row>
     <row r="20">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -6671,25 +6671,25 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.07034</v>
+        <v>0</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.647</v>
+        <v>0.791</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>0.26583</v>
-      </c>
-      <c r="H20" s="17" t="n">
-        <v>145.12596</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>5.3039956</v>
-      </c>
-      <c r="J20" s="15" t="n">
-        <v>1.864</v>
+        <v>0.52018</v>
+      </c>
+      <c r="H20" t="n">
+        <v>17.953978</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>3.0556726</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>2.39</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>54.78</v>
+        <v>272.92</v>
       </c>
     </row>
     <row r="21">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -6710,25 +6710,25 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>0.52018</v>
+        <v>0.15277</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>0.09748999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>17.326008</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>2.9496593</v>
+        <v>12.002341</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>1.8203113</v>
       </c>
       <c r="J21" s="14" t="n">
-        <v>2.39</v>
+        <v>138.994</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>273</v>
+        <v>170.8</v>
       </c>
     </row>
     <row r="22">
@@ -6761,13 +6761,13 @@
         <v>0</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>11.032432</v>
+        <v>11.267164</v>
       </c>
       <c r="J22" s="11" t="n">
         <v>0.049</v>
       </c>
       <c r="K22" s="15" t="n">
-        <v>-0.73</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="23">
@@ -6797,16 +6797,16 @@
         <v>0.53282</v>
       </c>
       <c r="H23" t="n">
-        <v>14.724781</v>
+        <v>14.941839</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>3.0046723</v>
+        <v>3.0483768</v>
       </c>
       <c r="J23" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>466.9</v>
+        <v>466.81</v>
       </c>
     </row>
     <row r="24">
@@ -6836,16 +6836,16 @@
         <v>0.30952</v>
       </c>
       <c r="H24" s="17" t="n">
-        <v>199.51924</v>
+        <v>210.27287</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>10.096668</v>
+        <v>10.623804</v>
       </c>
       <c r="J24" s="11" t="n">
         <v>0.261</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>6.24</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="25">
@@ -6875,16 +6875,16 @@
         <v>0.15842</v>
       </c>
       <c r="H25" t="n">
-        <v>15.055571</v>
+        <v>15.748032</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>4.5543747</v>
+        <v>4.769388</v>
       </c>
       <c r="J25" s="15" t="n">
         <v>1.461</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>77.38</v>
+        <v>77.47</v>
       </c>
     </row>
     <row r="26">
@@ -6914,16 +6914,16 @@
         <v>0.13921</v>
       </c>
       <c r="H26" s="17" t="n">
-        <v>61.776062</v>
+        <v>61.12176</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>426666.66</v>
+        <v>425000</v>
       </c>
       <c r="J26" s="14" t="n">
         <v>201.586</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>20.72</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="27">
@@ -6953,16 +6953,16 @@
         <v>0.18375</v>
       </c>
       <c r="H27" t="n">
-        <v>27.31611</v>
+        <v>27.64977</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>48823.527</v>
+        <v>49411.76</v>
       </c>
       <c r="J27" s="14" t="n">
         <v>51.917</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>60.77</v>
+        <v>60.76</v>
       </c>
     </row>
     <row r="28">
@@ -6992,16 +6992,16 @@
         <v>0.0806</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>9.412305</v>
+        <v>9.023039000000001</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>17982.457</v>
+        <v>17280.701</v>
       </c>
       <c r="J28" s="14" t="n">
         <v>32.802</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>217.8</v>
+        <v>218.33</v>
       </c>
     </row>
     <row r="29">
@@ -7031,94 +7031,94 @@
         <v>0.10163</v>
       </c>
       <c r="H29" t="n">
-        <v>12.994645</v>
+        <v>13.051422</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.9624665</v>
+        <v>1.9723282</v>
       </c>
       <c r="J29" s="14" t="n">
         <v>2.102</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>76.56999999999999</v>
+        <v>76.62</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>BRPT.JK</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>3.509</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>0.09752</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>13.586956</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>62500</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>107.818</v>
+      </c>
+      <c r="K30" s="11" t="n">
+        <v>110.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>IRSX.JK</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C31" t="n">
         <v>11</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E31" s="9" t="n">
         <v>0.11936</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F31" s="16" t="n">
         <v>-0.5590000000000001</v>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G31" s="9" t="n">
         <v>0.06455</v>
       </c>
-      <c r="H30" s="17" t="n">
-        <v>57.03422</v>
-      </c>
-      <c r="I30" s="14" t="n">
-        <v>9.326425</v>
-      </c>
-      <c r="J30" s="11" t="n">
+      <c r="H31" s="17" t="n">
+        <v>61.793102</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>9.284974</v>
+      </c>
+      <c r="J31" s="11" t="n">
         <v>0.216</v>
       </c>
-      <c r="K30" s="11" t="n">
-        <v>7.89</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>BRPT.JK</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="n">
-        <v>0.35876</v>
-      </c>
-      <c r="F31" s="13" t="n">
-        <v>3.509</v>
-      </c>
-      <c r="G31" s="13" t="n">
-        <v>0.09752</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>13.6252165</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>62500</v>
-      </c>
-      <c r="J31" s="14" t="n">
-        <v>107.818</v>
-      </c>
       <c r="K31" s="11" t="n">
-        <v>110.09</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="32">
@@ -7148,10 +7148,10 @@
         <v>0.15737</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>4.5454545</v>
+        <v>4.6231546</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>0.24058802</v>
+        <v>0.24470064</v>
       </c>
       <c r="J32" s="11" t="n">
         <v>0</v>
@@ -7187,10 +7187,10 @@
         <v>0.041550003</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>7.826087</v>
+        <v>8.115942</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>0.8056815000000001</v>
+        <v>0.8355216</v>
       </c>
       <c r="J33" s="14" t="n">
         <v>43.245</v>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -7216,26 +7216,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E34" s="16" t="n">
-        <v>-0.29015</v>
+      <c r="E34" s="9" t="n">
+        <v>0.045900002</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0.671</v>
+        <v>0.329</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>-0.21053</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="15" t="n">
-        <v>4.042094</v>
+        <v>0.19652</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>152.95169</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>95000.00999999999</v>
       </c>
       <c r="J34" s="14" t="n">
-        <v>65.76600000000001</v>
-      </c>
-      <c r="K34" s="15" t="n">
-        <v>0</v>
+        <v>12.694</v>
+      </c>
+      <c r="K34" s="11" t="n">
+        <v>5.59</v>
       </c>
     </row>
     <row r="35">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RATU.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -7255,26 +7255,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E35" s="8" t="n">
-        <v>0.45251998</v>
-      </c>
-      <c r="F35" s="16" t="n">
-        <v>-0.183</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>0.31559</v>
-      </c>
-      <c r="H35" s="17" t="n">
-        <v>52.144535</v>
+      <c r="E35" s="9" t="n">
+        <v>0.15447</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>0.091759995</v>
+      </c>
+      <c r="H35" t="n">
+        <v>37.489555</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>313235.28</v>
+        <v>74791.664</v>
       </c>
       <c r="J35" s="14" t="n">
-        <v>36.548</v>
+        <v>68.20699999999999</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>102.12</v>
+        <v>95.76000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -7294,26 +7294,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E36" s="9" t="n">
-        <v>0.05801</v>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="G36" s="9" t="n">
-        <v>0.01754</v>
-      </c>
-      <c r="H36" t="n">
-        <v>29.246279</v>
+      <c r="E36" s="8" t="n">
+        <v>0.45251998</v>
+      </c>
+      <c r="F36" s="16" t="n">
+        <v>-0.183</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="H36" s="17" t="n">
+        <v>51.814735</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>207916.67</v>
+        <v>313235.28</v>
       </c>
       <c r="J36" s="14" t="n">
-        <v>276.511</v>
+        <v>36.548</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>170.62</v>
+        <v>102.77</v>
       </c>
     </row>
     <row r="37">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -7333,26 +7333,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E37" s="9" t="n">
-        <v>0.045900002</v>
+      <c r="E37" s="16" t="n">
+        <v>-0.29015</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.329</v>
+        <v>0.671</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.19652</v>
-      </c>
-      <c r="H37" s="17" t="n">
-        <v>134.82143</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>83888.89</v>
+        <v>-0.21053</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>3.6875246</v>
       </c>
       <c r="J37" s="14" t="n">
-        <v>12.694</v>
-      </c>
-      <c r="K37" s="11" t="n">
-        <v>5.6</v>
+        <v>65.76600000000001</v>
+      </c>
+      <c r="K37" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -7373,25 +7373,25 @@
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.15447</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>0.034</v>
+        <v>0.05801</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>0.317</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.091759995</v>
+        <v>0.01754</v>
       </c>
       <c r="H38" t="n">
-        <v>37.324387</v>
+        <v>29.79668</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>74166.664</v>
+        <v>212500</v>
       </c>
       <c r="J38" s="14" t="n">
-        <v>68.20699999999999</v>
+        <v>276.511</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>95.38</v>
+        <v>171.16</v>
       </c>
     </row>
     <row r="39">
@@ -7421,10 +7421,10 @@
         <v>0.24544</v>
       </c>
       <c r="H39" s="17" t="n">
-        <v>195.68346</v>
+        <v>200</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>6.692419</v>
+        <v>6.840046</v>
       </c>
       <c r="J39" s="14" t="n">
         <v>2.833</v>
@@ -7460,16 +7460,16 @@
         <v>0.14588</v>
       </c>
       <c r="H40" s="17" t="n">
-        <v>158.5145</v>
+        <v>169.53763</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>33.44226</v>
+        <v>35.735443</v>
       </c>
       <c r="J40" s="14" t="n">
         <v>38.133</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>11.04</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="41">
@@ -7499,16 +7499,16 @@
         <v>0.65328</v>
       </c>
       <c r="H41" s="17" t="n">
-        <v>72.09897599999999</v>
+        <v>70.58326</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>105624.99</v>
+        <v>104374.99</v>
       </c>
       <c r="J41" s="14" t="n">
         <v>34.873</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>11.72</v>
+        <v>11.83</v>
       </c>
     </row>
   </sheetData>

--- a/reports/HEDGEFUND_TERMINAL.xlsx
+++ b/reports/HEDGEFUND_TERMINAL.xlsx
@@ -473,8 +473,8 @@
   <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -491,7 +491,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>11 March 2026</t>
+          <t>12 March 2026</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>-1.8B</t>
+          <t>-1.5B</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>-1.4B</t>
+          <t>-1.2B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-4000</t>
+          <t>991000</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -600,24 +600,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.9M</t>
+          <t>-12.7M</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1. Consumer Cyclical</t>
+          <t>1. Industrials</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>297.8M</t>
+          <t>26.2M</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -625,24 +625,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-21.6M</t>
+          <t>-2.4M</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2. Financial Services</t>
+          <t>2. Consumer Defensive</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>115.7M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -650,19 +650,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>745400</t>
+          <t>6.6M</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3. Consumer Defensive</t>
+          <t>3. Healthcare</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>48.8M</t>
+          <t>6.2M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -675,19 +675,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-5.5M</t>
+          <t>9.2M</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4. Real Estate</t>
+          <t>4. Utilities</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>29.9M</t>
+          <t>3.0M</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -704,12 +704,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5. Communication Services</t>
+          <t>5. Unknown</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.0M</t>
+          <t>2.4M</t>
         </is>
       </c>
     </row>
@@ -727,41 +727,41 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>69.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-165.8M</t>
+          <t>-108.7M</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2. Energy</t>
+          <t>2. Unknown</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>60.4</v>
+        <v>65</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-494.1M</t>
+          <t>2.4M</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3. Consumer Cyclical</t>
+          <t>3. Energy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>58.5</v>
+        <v>63</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>297.8M</t>
+          <t>-738.9M</t>
         </is>
       </c>
     </row>
@@ -772,26 +772,26 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>53.5</v>
+        <v>59</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-34.5M</t>
+          <t>6.2M</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5. Financial Services</t>
+          <t>5. Technology</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>49.5</v>
+        <v>55.7</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>115.7M</t>
+          <t>-210.7M</t>
         </is>
       </c>
     </row>
@@ -910,20 +910,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10104-10646</t>
+          <t>9351-9899</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9560.714285714286</v>
+        <v>8802.678571428572</v>
       </c>
       <c r="F2" t="n">
-        <v>11407.14285714286</v>
+        <v>10657.14285714286</v>
       </c>
       <c r="G2" t="n">
-        <v>12547.85714285714</v>
+        <v>11722.85714285714</v>
       </c>
       <c r="H2" t="n">
-        <v>13182.14285714286</v>
+        <v>12425.89285714286</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -932,18 +932,18 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15.96%</t>
+          <t>16.48%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6065695380.45</v>
+        <v>6262422440.65</v>
       </c>
       <c r="L2" t="n">
-        <v>-4000</v>
+        <v>991000</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -961,36 +961,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2587-2813</t>
+          <t>711-789</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2361.428571428572</v>
+        <v>633.2142857142857</v>
       </c>
       <c r="F3" t="n">
-        <v>3123.571428571428</v>
+        <v>901.4285714285714</v>
       </c>
       <c r="G3" t="n">
-        <v>3435.928571428572</v>
+        <v>1013.928571428571</v>
       </c>
       <c r="H3" t="n">
-        <v>3848.571428571428</v>
+        <v>1163.928571428572</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>22.22%</t>
+          <t>30.17%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>23.15</v>
+        <v>11464380831.06</v>
       </c>
       <c r="L3" t="n">
-        <v>-2895500</v>
+        <v>-12701100</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1012,36 +1012,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>766-844</t>
+          <t>6146-6704</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>689.2857142857143</v>
+        <v>5589.285714285715</v>
       </c>
       <c r="F4" t="n">
-        <v>955</v>
+        <v>7483.035714285714</v>
       </c>
       <c r="G4" t="n">
-        <v>1050.5</v>
+        <v>8231.339285714286</v>
       </c>
       <c r="H4" t="n">
-        <v>1215</v>
+        <v>9301.785714285714</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>30.17%</t>
+          <t>20.38%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11462714164.39</v>
+        <v>70.12</v>
       </c>
       <c r="L4" t="n">
-        <v>-21636100</v>
+        <v>-2404400</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1063,36 +1063,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6059-6591</t>
+          <t>2823-2917</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5526.785714285715</v>
+        <v>2728.571428571428</v>
       </c>
       <c r="F5" t="n">
-        <v>7333.035714285714</v>
+        <v>3050</v>
       </c>
       <c r="G5" t="n">
-        <v>8066.339285714286</v>
+        <v>3355</v>
       </c>
       <c r="H5" t="n">
-        <v>9064.285714285714</v>
+        <v>3360</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>22.12%</t>
+          <t>8.81%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>76.02</v>
+        <v>3346996680.7</v>
       </c>
       <c r="L5" t="n">
-        <v>745400</v>
+        <v>6558700</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1306-1404</t>
+          <t>1276-1374</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1207.678571428572</v>
+        <v>1178.214285714286</v>
       </c>
       <c r="F6" t="n">
-        <v>1537.5</v>
+        <v>1508.392857142857</v>
       </c>
       <c r="G6" t="n">
-        <v>1691.25</v>
+        <v>1659.232142857143</v>
       </c>
       <c r="H6" t="n">
-        <v>1848.75</v>
+        <v>1822.142857142857</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1136,18 +1136,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14.70%</t>
+          <t>13.98%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>42.43</v>
+        <v>40.41</v>
       </c>
       <c r="L6" t="n">
-        <v>-5503000</v>
+        <v>9168500</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1165,36 +1165,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2905-2995</t>
+          <t>1595-1735</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2813.928571428572</v>
+        <v>1456.071428571429</v>
       </c>
       <c r="F7" t="n">
-        <v>3122.857142857143</v>
+        <v>1939.285714285714</v>
       </c>
       <c r="G7" t="n">
-        <v>3420.357142857143</v>
+        <v>2133.214285714286</v>
       </c>
       <c r="H7" t="n">
-        <v>3435.142857142857</v>
+        <v>2416.785714285714</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.66%</t>
+          <t>13.11%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3291362138.87</v>
+        <v>64.81</v>
       </c>
       <c r="L7" t="n">
-        <v>1793800</v>
+        <v>5531200</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1216,36 +1216,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2334-2426</t>
+          <t>693-747</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2240.714285714286</v>
+        <v>638.0357142857142</v>
       </c>
       <c r="F8" t="n">
-        <v>2559.285714285714</v>
+        <v>826.0714285714286</v>
       </c>
       <c r="G8" t="n">
-        <v>2815.214285714286</v>
+        <v>908.6785714285714</v>
       </c>
       <c r="H8" t="n">
-        <v>2869.285714285714</v>
+        <v>1009.821428571429</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14.70%</t>
+          <t>4.38%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>53.44</v>
+        <v>2.73</v>
       </c>
       <c r="L8" t="n">
-        <v>-2979900</v>
+        <v>-4144300</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1267,20 +1267,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3904-4136</t>
+          <t>2569-2791</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3670.714285714286</v>
+        <v>2346.785714285714</v>
       </c>
       <c r="F9" t="n">
-        <v>4428.928571428572</v>
+        <v>3098.571428571428</v>
       </c>
       <c r="G9" t="n">
-        <v>4871.821428571429</v>
+        <v>3408.428571428572</v>
       </c>
       <c r="H9" t="n">
-        <v>5111.428571428572</v>
+        <v>3816.071428571428</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1289,14 +1289,14 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15.40%</t>
+          <t>20.70%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>37.2</v>
+        <v>21.64</v>
       </c>
       <c r="L9" t="n">
-        <v>-30506300</v>
+        <v>-3687900</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1318,20 +1318,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3375-3625</t>
+          <t>11245-11805</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3125</v>
+        <v>10683.92857142857</v>
       </c>
       <c r="F10" t="n">
-        <v>3966.785714285714</v>
+        <v>12643.75</v>
       </c>
       <c r="G10" t="n">
-        <v>4363.464285714286</v>
+        <v>13908.125</v>
       </c>
       <c r="H10" t="n">
-        <v>4764.285714285714</v>
+        <v>14600</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1340,14 +1340,14 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23.05%</t>
+          <t>16.08%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>8759309511</v>
+        <v>6108929941.24</v>
       </c>
       <c r="L10" t="n">
-        <v>6595200</v>
+        <v>165900</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1361,48 +1361,48 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3839-4161</t>
+          <t>1433-1667</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3515.714285714286</v>
+        <v>1200.178571428572</v>
       </c>
       <c r="F11" t="n">
-        <v>4636.071428571428</v>
+        <v>2003.035714285714</v>
       </c>
       <c r="G11" t="n">
-        <v>5099.678571428572</v>
+        <v>2339.464285714286</v>
       </c>
       <c r="H11" t="n">
-        <v>5743.571428571429</v>
+        <v>2788.035714285714</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>31.68%</t>
+          <t>8.38%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>501.3</v>
+        <v>2.04</v>
       </c>
       <c r="L11" t="n">
-        <v>-1117600</v>
+        <v>12210500</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1412,48 +1412,48 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1653-1797</t>
+          <t>2304-2396</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1509.107142857143</v>
+        <v>2210.714285714286</v>
       </c>
       <c r="F12" t="n">
-        <v>2008.571428571429</v>
+        <v>2530.357142857143</v>
       </c>
       <c r="G12" t="n">
-        <v>2209.428571428572</v>
+        <v>2783.392857142858</v>
       </c>
       <c r="H12" t="n">
-        <v>2502.321428571428</v>
+        <v>2842.857142857143</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13.23%</t>
+          <t>14.04%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>65.42</v>
+        <v>51.1</v>
       </c>
       <c r="L12" t="n">
-        <v>766200</v>
+        <v>-4536100</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1471,36 +1471,36 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9278-10122</t>
+          <t>3858-4082</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8433.035714285714</v>
+        <v>3632.5</v>
       </c>
       <c r="F13" t="n">
-        <v>11316.96428571429</v>
+        <v>4363.214285714285</v>
       </c>
       <c r="G13" t="n">
-        <v>12511.60714285714</v>
+        <v>4799.535714285715</v>
       </c>
       <c r="H13" t="n">
-        <v>14104.46428571429</v>
+        <v>5018.214285714285</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9.99%</t>
+          <t>14.60%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>6.38</v>
+        <v>35.32</v>
       </c>
       <c r="L13" t="n">
-        <v>-1912500</v>
+        <v>-4224700</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1514,44 +1514,44 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>708-762</t>
+          <t>1798-1922</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>653.5714285714286</v>
+        <v>1674.642857142857</v>
       </c>
       <c r="F14" t="n">
-        <v>840.3571428571429</v>
+        <v>2102.857142857143</v>
       </c>
       <c r="G14" t="n">
-        <v>924.3928571428572</v>
+        <v>2313.142857142857</v>
       </c>
       <c r="H14" t="n">
-        <v>1022.857142857143</v>
+        <v>2525.357142857143</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>16.23%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>2.62</v>
+        <v>14.36</v>
       </c>
       <c r="L14" t="n">
-        <v>-4702400</v>
+        <v>-1695600</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1573,36 +1573,36 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3684-3996</t>
+          <t>3252-3488</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3371.785714285714</v>
+        <v>3017.5</v>
       </c>
       <c r="F15" t="n">
-        <v>4389.285714285714</v>
+        <v>3806.785714285714</v>
       </c>
       <c r="G15" t="n">
-        <v>4828.214285714285</v>
+        <v>4187.464285714286</v>
       </c>
       <c r="H15" t="n">
-        <v>5306.785714285714</v>
+        <v>4551.785714285714</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10.59%</t>
+          <t>22.37%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>10.55</v>
+        <v>8499441089.94</v>
       </c>
       <c r="L15" t="n">
-        <v>32300</v>
+        <v>4635800</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1616,48 +1616,48 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARCI.JK</t>
+          <t>EMAS.JK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1677-1793</t>
+          <t>7762-8238</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1561.964285714286</v>
+        <v>7287.5</v>
       </c>
       <c r="F16" t="n">
-        <v>1942.142857142857</v>
+        <v>8875</v>
       </c>
       <c r="G16" t="n">
-        <v>2136.357142857143</v>
+        <v>9762.5</v>
       </c>
       <c r="H16" t="n">
-        <v>2290.892857142857</v>
+        <v>10362.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5.10%</t>
+          <t>23.21%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2.72</v>
+        <v>8821565588.219999</v>
       </c>
       <c r="L16" t="n">
-        <v>-11431200</v>
+        <v>184400</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1667,48 +1667,48 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1564-1796</t>
+          <t>3523-3857</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1330.714285714286</v>
+        <v>3188.571428571428</v>
       </c>
       <c r="F17" t="n">
-        <v>2132.321428571428</v>
+        <v>4347.857142857143</v>
       </c>
       <c r="G17" t="n">
-        <v>2420</v>
+        <v>4782.642857142858</v>
       </c>
       <c r="H17" t="n">
-        <v>2916.071428571428</v>
+        <v>5492.857142857143</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7.93%</t>
+          <t>30.12%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1.99</v>
+        <v>476.65</v>
       </c>
       <c r="L17" t="n">
-        <v>56554200</v>
+        <v>-551700</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>INKP.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1726,36 +1726,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1899-2021</t>
+          <t>8807-9643</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1776.25</v>
+        <v>7971.428571428572</v>
       </c>
       <c r="F18" t="n">
-        <v>2200.714285714286</v>
+        <v>10824.10714285714</v>
       </c>
       <c r="G18" t="n">
-        <v>2420.785714285715</v>
+        <v>12005.35714285714</v>
       </c>
       <c r="H18" t="n">
-        <v>2619.464285714286</v>
+        <v>13580.35714285714</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17.27%</t>
+          <t>9.24%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>15.22</v>
+        <v>5.97</v>
       </c>
       <c r="L18" t="n">
-        <v>-25253200</v>
+        <v>-3950500</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1777,36 +1777,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4831-4989</t>
+          <t>216-252</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4672.142857142857</v>
+        <v>179.3571428571429</v>
       </c>
       <c r="F19" t="n">
-        <v>5190.178571428572</v>
+        <v>304.5</v>
       </c>
       <c r="G19" t="n">
-        <v>5658.928571428572</v>
+        <v>342</v>
       </c>
       <c r="H19" t="n">
-        <v>5709.196428571429</v>
+        <v>426.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>61.69%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3.16</v>
+        <v>14.04</v>
       </c>
       <c r="L19" t="n">
-        <v>33741800</v>
+        <v>69119800</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EMAS.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1828,36 +1828,36 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7751-8249</t>
+          <t>3532-3848</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>7252.678571428572</v>
+        <v>3217.5</v>
       </c>
       <c r="F20" t="n">
-        <v>8918.75</v>
+        <v>4245</v>
       </c>
       <c r="G20" t="n">
-        <v>9810.625</v>
+        <v>4669.5</v>
       </c>
       <c r="H20" t="n">
-        <v>10481.25</v>
+        <v>5172.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>23.73%</t>
+          <t>10.47%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>9018943865.370001</v>
+        <v>10.44</v>
       </c>
       <c r="L20" t="n">
-        <v>-658500</v>
+        <v>-15972500</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HRUM.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1879,40 +1879,40 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1035-1115</t>
+          <t>114-122</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>954.4642857142857</v>
+        <v>106.5357142857143</v>
       </c>
       <c r="F21" t="n">
-        <v>1227.678571428571</v>
+        <v>127.7142857142857</v>
       </c>
       <c r="G21" t="n">
-        <v>1350.446428571429</v>
+        <v>140.4857142857143</v>
       </c>
       <c r="H21" t="n">
-        <v>1490.178571428571</v>
+        <v>141.4642857142857</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>53.56%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>2.51</v>
+        <v>195.79</v>
       </c>
       <c r="L21" t="n">
-        <v>746000</v>
+        <v>-1342400</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1958,11 +1958,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>316433400</v>
+        <v>69119800</v>
       </c>
     </row>
     <row r="3">
@@ -1971,11 +1971,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>105416300</v>
+        <v>53796800</v>
       </c>
     </row>
     <row r="4">
@@ -1984,11 +1984,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>56554200</v>
+        <v>13474500</v>
       </c>
     </row>
     <row r="5">
@@ -1997,11 +1997,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMRT.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37773100</v>
+        <v>12210500</v>
       </c>
     </row>
     <row r="6">
@@ -2010,11 +2010,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37538300</v>
+        <v>10894900</v>
       </c>
     </row>
     <row r="7">
@@ -2023,11 +2023,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33741800</v>
+        <v>9168500</v>
       </c>
     </row>
     <row r="8">
@@ -2036,11 +2036,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13783000</v>
+        <v>8526300</v>
       </c>
     </row>
     <row r="9">
@@ -2049,11 +2049,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CPRO.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12850400</v>
+        <v>8111900</v>
       </c>
     </row>
     <row r="10">
@@ -2062,11 +2062,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>AMRT.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11666100</v>
+        <v>7833500</v>
       </c>
     </row>
     <row r="11">
@@ -2075,11 +2075,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10200200</v>
+        <v>6640500</v>
       </c>
     </row>
     <row r="12">
@@ -2088,11 +2088,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8426900</v>
+        <v>6558700</v>
       </c>
     </row>
     <row r="13">
@@ -2101,11 +2101,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7483200</v>
+        <v>5531200</v>
       </c>
     </row>
     <row r="14">
@@ -2114,11 +2114,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BKSL.JK</t>
+          <t>BBKP.JK</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7075200</v>
+        <v>5269000</v>
       </c>
     </row>
     <row r="15">
@@ -2127,11 +2127,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6595200</v>
+        <v>4853200</v>
       </c>
     </row>
     <row r="16">
@@ -2140,11 +2140,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PNLF.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6312700</v>
+        <v>4635800</v>
       </c>
     </row>
     <row r="17">
@@ -2153,11 +2153,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6227500</v>
+        <v>4228100</v>
       </c>
     </row>
     <row r="18">
@@ -2166,11 +2166,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>LPKR.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5002500</v>
+        <v>4122600</v>
       </c>
     </row>
     <row r="19">
@@ -2179,11 +2179,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>HUMI.JK</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4580900</v>
+        <v>4037800</v>
       </c>
     </row>
     <row r="20">
@@ -2192,11 +2192,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EXCL.JK</t>
+          <t>GTSI.JK</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4119100</v>
+        <v>3447700</v>
       </c>
     </row>
     <row r="21">
@@ -2205,11 +2205,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4111100</v>
+        <v>3303200</v>
       </c>
     </row>
     <row r="22">
@@ -2218,11 +2218,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>BRIS.JK</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4049500</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="23">
@@ -2231,11 +2231,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TRIN.JK</t>
+          <t>PNLF.JK</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3499700</v>
+        <v>2908800</v>
       </c>
     </row>
     <row r="24">
@@ -2244,11 +2244,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2865100</v>
+        <v>2435900</v>
       </c>
     </row>
     <row r="25">
@@ -2257,11 +2257,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2074300</v>
+        <v>2385000</v>
       </c>
     </row>
     <row r="26">
@@ -2270,11 +2270,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UNTR.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1859000</v>
+        <v>2076200</v>
       </c>
     </row>
     <row r="27">
@@ -2283,11 +2283,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>JPFA.JK</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1793800</v>
+        <v>1522500</v>
       </c>
     </row>
     <row r="28">
@@ -2296,11 +2296,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1615500</v>
+        <v>995800</v>
       </c>
     </row>
     <row r="29">
@@ -2309,11 +2309,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AMMN.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>937300</v>
+        <v>991000</v>
       </c>
     </row>
     <row r="30">
@@ -2322,11 +2322,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>766200</v>
+        <v>835300</v>
       </c>
     </row>
     <row r="31">
@@ -2335,11 +2335,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HRUM.JK</t>
+          <t>UNTR.JK</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>746000</v>
+        <v>676200</v>
       </c>
     </row>
   </sheetData>
@@ -2398,61 +2398,61 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-9.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>98</v>
       </c>
       <c r="C3" t="n">
-        <v>80.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-25.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>97</v>
       </c>
       <c r="C4" t="n">
-        <v>79.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-18.7%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>96</v>
       </c>
       <c r="C5" t="n">
-        <v>78.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-3.7%</t>
         </is>
       </c>
     </row>
@@ -2466,763 +2466,763 @@
         <v>95</v>
       </c>
       <c r="C6" t="n">
-        <v>77.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-14.2%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>74.8</v>
+        <v>67</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-16.5%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-8.3%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>92</v>
       </c>
       <c r="C9" t="n">
-        <v>70.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.5%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>91</v>
       </c>
       <c r="C10" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-6.7%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" t="n">
-        <v>67</v>
+        <v>61.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-29.5%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-4.9%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>88</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>55.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-16.6%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>52.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-18.4%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>86</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-14.5%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARCI.JK</t>
+          <t>EMAS.JK</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C16" t="n">
-        <v>62.6</v>
+        <v>52</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-8.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C17" t="n">
-        <v>61.6</v>
+        <v>52</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-13.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>INKP.JK</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>82</v>
       </c>
       <c r="C18" t="n">
-        <v>59.8</v>
+        <v>51</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-23.1%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>81</v>
       </c>
       <c r="C19" t="n">
-        <v>52.4</v>
+        <v>49</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-26.4%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EMAS.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-19.8%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HRUM.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>80</v>
       </c>
       <c r="C21" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-27.6%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>ARCI.JK</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>78</v>
       </c>
       <c r="C22" t="n">
-        <v>49</v>
+        <v>47.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-16.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>UNTR.JK</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C23" t="n">
-        <v>49</v>
+        <v>44.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-9.3%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>MBMA.JK</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>76</v>
       </c>
       <c r="C24" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-18.2%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PSAB.JK</t>
+          <t>DADA.JK</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>75</v>
       </c>
       <c r="C25" t="n">
-        <v>46.8</v>
+        <v>38.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-20.6%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UNTR.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>74</v>
       </c>
       <c r="C26" t="n">
-        <v>44.8</v>
+        <v>37.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-9.2%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MBMA.JK</t>
+          <t>HRUM.JK</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>73</v>
       </c>
       <c r="C27" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-19.8%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>WIFI.JK</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>72</v>
       </c>
       <c r="C28" t="n">
-        <v>40.6</v>
+        <v>34.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-46.4%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BULL.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>70</v>
       </c>
       <c r="C29" t="n">
-        <v>39.8</v>
+        <v>31.6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-41.9%</t>
+          <t>-20.2%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>69</v>
       </c>
       <c r="C30" t="n">
-        <v>34</v>
+        <v>28.2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-47.7%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>68</v>
       </c>
       <c r="C31" t="n">
-        <v>31.6</v>
+        <v>25.6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-9.8%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>TPIA.JK</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>28.2</v>
+        <v>24.6</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-45.7%</t>
+          <t>-22.2%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VKTR.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>66</v>
       </c>
       <c r="C33" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-37.1%</t>
+          <t>-7.3%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>65</v>
       </c>
       <c r="C34" t="n">
-        <v>26.8</v>
+        <v>22</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-31.9%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TPIA.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>64</v>
       </c>
       <c r="C35" t="n">
-        <v>24.6</v>
+        <v>21.6</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-18.7%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>63</v>
       </c>
       <c r="C36" t="n">
-        <v>24</v>
+        <v>21.4</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-17.8%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>BRIS.JK</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>62</v>
       </c>
       <c r="C37" t="n">
-        <v>22</v>
+        <v>20.8</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-9.8%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>DSSA.JK</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>21.6</v>
+        <v>17.4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-33.0%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BRIS.JK</t>
+          <t>BBYB.JK</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C39" t="n">
-        <v>20.8</v>
+        <v>17.4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-50.2%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>59</v>
       </c>
       <c r="C40" t="n">
-        <v>20.4</v>
+        <v>16.8</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-23.9%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AMRT.JK</t>
+          <t>GOTO.JK</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C41" t="n">
-        <v>19.8</v>
+        <v>16.8</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-17.4%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DADA.JK</t>
+          <t>EMTK.JK</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>56</v>
       </c>
       <c r="C42" t="n">
-        <v>18.6</v>
+        <v>16.2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-49.3%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>55</v>
       </c>
       <c r="C43" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-37.3%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>LPKR.JK</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C44" t="n">
-        <v>18</v>
+        <v>13.6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-31.2%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DSSA.JK</t>
+          <t>JPFA.JK</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>53</v>
       </c>
       <c r="C45" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-22.2%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BBYB.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" t="n">
-        <v>17.4</v>
+        <v>12.8</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-55.6%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GOTO.JK</t>
+          <t>PSAB.JK</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>51</v>
       </c>
       <c r="C47" t="n">
-        <v>16.8</v>
+        <v>11.8</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>-24.9%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EMTK.JK</t>
+          <t>NICL.JK</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>50</v>
       </c>
       <c r="C48" t="n">
-        <v>16.2</v>
+        <v>10.8</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3233,666 +3233,666 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BUMI.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>49</v>
       </c>
       <c r="C49" t="n">
-        <v>15</v>
+        <v>10.4</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-48.3%</t>
+          <t>-53.3%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ICBP.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>15</v>
+        <v>10.4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-71.0%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C51" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-11.3%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LPKR.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>46</v>
       </c>
       <c r="C52" t="n">
-        <v>13.6</v>
+        <v>8.4</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-41.2%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C53" t="n">
-        <v>13.2</v>
+        <v>8.4</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-47.2%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>BBCA.JK</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>44</v>
       </c>
       <c r="C54" t="n">
-        <v>12.8</v>
+        <v>7.8</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-54.6%</t>
+          <t>-17.8%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C55" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-49.4%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EXCL.JK</t>
+          <t>COIN.JK</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C56" t="n">
-        <v>11.8</v>
+        <v>7.8</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-69.2%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NICL.JK</t>
+          <t>PBSA.JK</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C57" t="n">
-        <v>10.8</v>
+        <v>7.8</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-54.3%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>39</v>
       </c>
       <c r="C58" t="n">
-        <v>10.4</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-55.7%</t>
+          <t>-48.4%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RATU.JK</t>
+          <t>TOBA.JK</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C59" t="n">
-        <v>10.4</v>
+        <v>7</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-54.2%</t>
+          <t>-35.9%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C60" t="n">
-        <v>10.4</v>
+        <v>7</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-71.3%</t>
+          <t>-22.6%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SUPA.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>36</v>
       </c>
       <c r="C61" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-60.4%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>IRSX.JK</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C62" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-40.1%</t>
+          <t>-43.2%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>PNLF.JK</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C63" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-29.3%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>CPRO.JK</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C64" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-34.9%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BBCA.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>32</v>
       </c>
       <c r="C65" t="n">
-        <v>7.8</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-35.9%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>COIN.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>32</v>
       </c>
       <c r="C66" t="n">
-        <v>7.8</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-68.5%</t>
+          <t>-55.4%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PBSA.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>32</v>
       </c>
       <c r="C67" t="n">
-        <v>7.8</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-54.6%</t>
+          <t>-69.6%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C68" t="n">
-        <v>7.199999999999999</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-54.9%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C69" t="n">
-        <v>6.6</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-59.7%</t>
+          <t>-54.3%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C70" t="n">
-        <v>6.6</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-42.9%</t>
+          <t>-28.8%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PNLF.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>25</v>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-27.8%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CPRO.JK</t>
+          <t>AMRT.JK</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>25</v>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-34.9%</t>
+          <t>-28.0%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>23</v>
       </c>
       <c r="C73" t="n">
-        <v>5.399999999999999</v>
+        <v>3</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-60.5%</t>
+          <t>-19.6%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>23</v>
       </c>
       <c r="C74" t="n">
-        <v>5.399999999999999</v>
+        <v>3</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-16.3%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>23</v>
       </c>
       <c r="C75" t="n">
-        <v>5.399999999999999</v>
+        <v>3</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-53.8%</t>
+          <t>-23.1%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C76" t="n">
-        <v>5.399999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-55.7%</t>
+          <t>-61.2%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>BULL.JK</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C77" t="n">
-        <v>5.399999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-42.5%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>EXCL.JK</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-38.1%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>WIFI.JK</t>
+          <t>GTSI.JK</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C79" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-51.2%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>DEWA.JK</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-47.5%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>BUMI.JK</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>15</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-51.3%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GTSI.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C82" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-50.7%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DEWA.JK</t>
+          <t>SUPA.JK</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C83" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-43.6%</t>
+          <t>-30.9%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>RMKE.JK</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-50.6%</t>
+          <t>-63.8%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>RMKE.JK</t>
+          <t>ICBP.JK</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-64.2%</t>
+          <t>-15.5%</t>
         </is>
       </c>
     </row>
@@ -3903,14 +3903,14 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-33.0%</t>
         </is>
       </c>
     </row>
@@ -3921,14 +3921,14 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-71.3%</t>
+          <t>-72.3%</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-35.2%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-32.5%</t>
         </is>
       </c>
     </row>
@@ -3982,14 +3982,14 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-42.3%</t>
+          <t>-44.2%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TOBA.JK</t>
+          <t>VKTR.JK</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-39.0%</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-45.5%</t>
+          <t>-44.1%</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-62.1%</t>
+          <t>-64.1%</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>-36.6%</t>
+          <t>-37.7%</t>
         </is>
       </c>
     </row>
@@ -4137,17 +4137,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10104-10646</t>
+          <t>9351-9899</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12548</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-4000</t>
+          <t>991000</t>
         </is>
       </c>
     </row>
@@ -4162,21 +4162,21 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>766-844</t>
+          <t>711-789</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-21636100</t>
+          <t>-12701100</t>
         </is>
       </c>
     </row>
@@ -4191,21 +4191,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2905-2995</t>
+          <t>2823-2917</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1793800</t>
+          <t>6558700</t>
         </is>
       </c>
     </row>
@@ -4216,25 +4216,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2334-2426</t>
+          <t>1595-1735</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2979900</t>
+          <t>5531200</t>
         </is>
       </c>
     </row>
@@ -4245,32 +4245,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3839-4161</t>
+          <t>1433-1667</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1117600</t>
+          <t>12210500</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4278,25 +4278,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2587-2813</t>
+          <t>6146-6704</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2895500</t>
+          <t>-2404400</t>
         </is>
       </c>
     </row>
@@ -4307,25 +4307,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>104-112</t>
+          <t>1276-1374</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>316433400</t>
+          <t>9168500</t>
         </is>
       </c>
     </row>
@@ -4336,25 +4336,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VKTR.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>763-867</t>
+          <t>693-747</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>909</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2430100</t>
+          <t>-4144300</t>
         </is>
       </c>
     </row>
@@ -4365,25 +4365,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>240-276</t>
+          <t>3858-4082</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7483200</t>
+          <t>-4224700</t>
         </is>
       </c>
     </row>
@@ -4394,32 +4394,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>265-311</t>
+          <t>1798-1922</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-4347200</t>
+          <t>-1695600</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4427,25 +4427,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6059-6591</t>
+          <t>2569-2791</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>745400</t>
+          <t>-3687900</t>
         </is>
       </c>
     </row>
@@ -4456,25 +4456,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1306-1404</t>
+          <t>114-122</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5503000</t>
+          <t>-1342400</t>
         </is>
       </c>
     </row>
@@ -4485,25 +4485,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3904-4136</t>
+          <t>235-269</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>368</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-30506300</t>
+          <t>-2146100</t>
         </is>
       </c>
     </row>
@@ -4514,25 +4514,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3375-3625</t>
+          <t>260-304</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>430</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6595200</t>
+          <t>-23700600</t>
         </is>
       </c>
     </row>
@@ -4543,32 +4543,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9278-10122</t>
+          <t>986-1154</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>12512</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1912500</t>
+          <t>-6086900</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -4576,25 +4576,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4831-4989</t>
+          <t>11245-11805</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>33741800</t>
+          <t>165900</t>
         </is>
       </c>
     </row>
@@ -4605,25 +4605,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3519-3601</t>
+          <t>216-252</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>342</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>105416300</t>
+          <t>69119800</t>
         </is>
       </c>
     </row>
@@ -4634,25 +4634,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>PBSA.JK</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>98-118</t>
+          <t>1177-1283</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1255200</t>
+          <t>90800</t>
         </is>
       </c>
     </row>
@@ -4663,25 +4663,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4208-4312</t>
+          <t>1735-1915</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8426900</t>
+          <t>-5616800</t>
         </is>
       </c>
     </row>
@@ -4692,32 +4692,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1505-1605</t>
+          <t>5843-6057</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1514600</t>
+          <t>-338100</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -4725,25 +4725,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>DADA.JK</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>226-262</t>
+          <t>50-50</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-104512900</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4754,25 +4754,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11220-11780</t>
+          <t>339-349</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>394</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>328500</t>
+          <t>3303200</t>
         </is>
       </c>
     </row>
@@ -4783,25 +4783,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BULL.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>372-424</t>
+          <t>7807-8293</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2075700</t>
+          <t>-983300</t>
         </is>
       </c>
     </row>
@@ -4812,25 +4812,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5891-6109</t>
+          <t>4764-5056</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6227500</t>
+          <t>-588600</t>
         </is>
       </c>
     </row>
@@ -4841,32 +4841,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PBSA.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1167-1273</t>
+          <t>172-186</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-430700</t>
+          <t>8526300</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -4874,25 +4874,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>337-347</t>
+          <t>4806-4954</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>37538300</t>
+          <t>8111900</t>
         </is>
       </c>
     </row>
@@ -4903,25 +4903,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DADA.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50-50</t>
+          <t>94-114</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>169</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-44752700</t>
         </is>
       </c>
     </row>
@@ -4932,25 +4932,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7947-8453</t>
+          <t>3541-3619</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10082</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-202100</t>
+          <t>-22448200</t>
         </is>
       </c>
     </row>
@@ -4961,25 +4961,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4754-5046</t>
+          <t>4239-4341</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>81700</t>
+          <t>-13801800</t>
         </is>
       </c>
     </row>
@@ -4990,32 +4990,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>BRIS.JK</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>168-182</t>
+          <t>2172-2248</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-18379100</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -5023,25 +5023,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>WIFI.JK</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1911-2029</t>
+          <t>2196-2364</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2411</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>10200200</t>
+          <t>-3742900</t>
         </is>
       </c>
     </row>
@@ -5052,25 +5052,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>GOTO.JK</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>983-1017</t>
+          <t>56-58</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2798000</t>
+          <t>-204546500</t>
         </is>
       </c>
     </row>
@@ -5081,567 +5081,567 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>IRSX.JK</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3403-3777</t>
+          <t>416-476</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>636</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-128900</t>
+          <t>-2421000</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>800-870</t>
+          <t>1897-2013</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>2391</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-7662000</t>
+          <t>-2968600</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6933-7367</t>
+          <t>3424-3796</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>8781</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-65600</t>
+          <t>644600</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2894-3026</t>
+          <t>811-879</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>13783000</t>
+          <t>6640500</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EMTK.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>706-754</t>
+          <t>6757-7193</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>8593</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5460200</t>
+          <t>-977300</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EXCL.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2748-2952</t>
+          <t>983-1017</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4119100</t>
+          <t>2385000</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>RLCO.JK</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>65</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5539-6311</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8194</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2435900</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>KLBF.JK</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>64</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>982-1018</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2076200</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>LPKR.JK</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>54</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>85-91</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>4122600</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>ISAT.JK</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>35</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>1992-2108</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2491</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>4049500</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="n">
-        <v>5</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>INET.JK</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>23</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>263-293</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-15489100</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>KLBF.JK</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>61</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>982-1018</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1170</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-34214900</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="n">
+      <c r="D43" t="n">
+        <v>63</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1971-2089</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>995800</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="n">
         <v>2</v>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>LPKR.JK</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>46</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>86-92</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-266800</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Consumer Defensive</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AMRT.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1397-1473</t>
+          <t>2932-3068</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>37773100</t>
+          <t>53796800</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ICBP.JK</t>
+          <t>EMTK.JK</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7132-7368</t>
+          <t>722-768</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>917</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1298800</t>
+          <t>-1970700</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2268-2392</t>
+          <t>269-299</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>383</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5002500</t>
+          <t>-91081100</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>EXCL.JK</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>19</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2677-2883</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>3474</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-5941300</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>JPFA.JK</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>53</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2216-2344</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1522500</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>CPRO.JK</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>25</v>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="D49" t="n">
+        <v>34</v>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>55-57</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>12850400</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="n">
-        <v>5</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>UNVR.JK</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>17</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>1894-1996</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2347</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2865100</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>GOTO.JK</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>51</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>54-56</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.1B</t>
+          <t>-6488800</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>418-478</t>
+          <t>1949-2051</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4580900</t>
+          <t>4228100</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WIFI.JK</t>
+          <t>AMRT.JK</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2010-2170</t>
+          <t>1401-1479</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-2694000</t>
+          <t>7833500</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>5538-6312</t>
+          <t>5943-6107</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-15000</t>
+          <t>835300</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -5693,11 +5693,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GOTO.JK</t>
+          <t>BUMI.JK</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1086768900</v>
+        <v>-586435100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5711,11 +5711,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BUMI.JK</t>
+          <t>GOTO.JK</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-487670800</v>
+        <v>-204546500</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5729,11 +5729,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>DEWA.JK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>316433400</v>
+        <v>-161720500</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -5747,11 +5747,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>105416300</v>
+        <v>-91081100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-104512900</v>
+        <v>69119800</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-73678300</v>
+        <v>-61600100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -5801,11 +5801,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>56554200</v>
+        <v>53796800</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -5819,11 +5819,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMRT.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37773100</v>
+        <v>-44752700</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5837,11 +5837,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>BULL.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37538300</v>
+        <v>-43193300</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5855,11 +5855,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>BBCA.JK</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-34214900</v>
+        <v>-38049200</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
@@ -5978,16 +5978,16 @@
         <v>0.38872</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>8.136412999999999</v>
+        <v>8.090589</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>1.558645</v>
+        <v>1.5491217</v>
       </c>
       <c r="J2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>603.46</v>
+        <v>603.17</v>
       </c>
     </row>
     <row r="3">
@@ -6017,10 +6017,10 @@
         <v>0.34335998</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>8.280077</v>
+        <v>8.168936</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>0.9624079</v>
+        <v>0.9494897</v>
       </c>
       <c r="J3" s="11" t="n">
         <v>0</v>
@@ -6056,16 +6056,16 @@
         <v>0.43205002</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>5.9679527</v>
+        <v>6.090084</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>1.1403809</v>
+        <v>1.1638134</v>
       </c>
       <c r="J4" s="14" t="n">
         <v>2.444</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>122.32</v>
+        <v>122.33</v>
       </c>
     </row>
     <row r="5">
@@ -6095,16 +6095,16 @@
         <v>0.40405998</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>9.470098999999999</v>
+        <v>9.523809</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>1.6545719</v>
+        <v>1.6638672</v>
       </c>
       <c r="J5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>375.92</v>
+        <v>375.9</v>
       </c>
     </row>
     <row r="6">
@@ -6134,16 +6134,16 @@
         <v>0.27552</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>10.701311</v>
+        <v>10.460251</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>2.38932</v>
+        <v>2.3364198</v>
       </c>
       <c r="J6" s="14" t="n">
         <v>23.671</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>126.62</v>
+        <v>126.67</v>
       </c>
     </row>
     <row r="7">
@@ -6173,10 +6173,10 @@
         <v>0.71615</v>
       </c>
       <c r="H7" t="n">
-        <v>28.272251</v>
+        <v>27.225132</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>6.7542214</v>
+        <v>6.504065</v>
       </c>
       <c r="J7" s="14" t="n">
         <v>5.093</v>
@@ -6212,16 +6212,16 @@
         <v>0.06594999999999999</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>6.77424</v>
+        <v>6.626944</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>1.4516085</v>
+        <v>1.4204581</v>
       </c>
       <c r="J8" s="14" t="n">
         <v>59.254</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>343.95</v>
+        <v>344.05</v>
       </c>
     </row>
     <row r="9">
@@ -6251,16 +6251,16 @@
         <v>0.15481</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>6.5968094</v>
+        <v>6.1311984</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>24240.654</v>
+        <v>22488.318</v>
       </c>
       <c r="J9" s="14" t="n">
         <v>22.636</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>1572.73</v>
+        <v>1569.84</v>
       </c>
     </row>
     <row r="10">
@@ -6269,11 +6269,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRIS.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6281,25 +6281,25 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.15604</v>
+        <v>0.15277</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>0.31919</v>
-      </c>
-      <c r="H10" t="n">
-        <v>13.4731455</v>
+        <v>0.091</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>0.09748999999999999</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>11.876207</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>1.9622712</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>0</v>
+        <v>1.8025521</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>138.994</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>164.03</v>
+        <v>170.93</v>
       </c>
     </row>
     <row r="11">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NICL.JK</t>
+          <t>BRIS.JK</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6319,104 +6319,104 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="9" t="n">
+        <v>0.15604</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="H11" t="n">
+        <v>13.477254</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>1.9622712</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>163.98</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NICL.JK</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
         <v>0.65794</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F12" s="16" t="n">
         <v>-0.261</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G12" s="8" t="n">
         <v>0.27632</v>
       </c>
-      <c r="H11" t="n">
-        <v>18.525742</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>12.163893</v>
-      </c>
-      <c r="J11" s="11" t="n">
+      <c r="H12" t="n">
+        <v>18.11453</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>11.907811</v>
+      </c>
+      <c r="J12" s="11" t="n">
         <v>0.378</v>
       </c>
-      <c r="K11" s="11" t="n">
-        <v>51.28</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="K12" s="11" t="n">
+        <v>51.34</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>HRTA.JK</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C13" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E13" s="13" t="n">
         <v>0.28483</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F13" s="13" t="n">
         <v>1.009</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G13" s="13" t="n">
         <v>0.023759998</v>
       </c>
-      <c r="H12" s="12" t="n">
-        <v>17.365578</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>4.410777</v>
-      </c>
-      <c r="J12" s="14" t="n">
+      <c r="H13" s="12" t="n">
+        <v>17.241379</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>4.3781047</v>
+      </c>
+      <c r="J13" s="14" t="n">
         <v>139.825</v>
       </c>
-      <c r="K12" s="11" t="n">
-        <v>155.48</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ELSA.JK</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>16</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>0.14062001</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>0.04955</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>8.525736</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>1.1059241</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <v>12.229</v>
-      </c>
       <c r="K13" s="11" t="n">
-        <v>94.42</v>
+        <v>155.44</v>
       </c>
     </row>
     <row r="14">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ARCI.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -6436,104 +6436,104 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="9" t="n">
+        <v>0.14062001</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>0.04955</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>7.9423914</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>1.0303642</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>12.229</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>94.43000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ARCI.JK</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
         <v>0.28336</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F15" s="8" t="n">
         <v>0.879</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G15" s="8" t="n">
         <v>0.21154</v>
       </c>
-      <c r="H14" t="n">
-        <v>30.14246</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>123928.57</v>
-      </c>
-      <c r="J14" s="14" t="n">
+      <c r="H15" t="n">
+        <v>29.672817</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>121785.71</v>
+      </c>
+      <c r="J15" s="14" t="n">
         <v>118.6</v>
       </c>
-      <c r="K14" s="11" t="n">
-        <v>57.56</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="K15" s="11" t="n">
+        <v>57.46</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>TPIA.JK</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C16" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E16" s="13" t="n">
         <v>0.42018002</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F16" s="13" t="n">
         <v>4.295</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G16" s="13" t="n">
         <v>0.2208</v>
       </c>
-      <c r="H15" s="12" t="n">
-        <v>18.754076</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>127777.77</v>
-      </c>
-      <c r="J15" s="14" t="n">
+      <c r="H16" s="12" t="n">
+        <v>18.621975</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>126666.664</v>
+      </c>
+      <c r="J16" s="14" t="n">
         <v>82.7</v>
       </c>
-      <c r="K15" s="11" t="n">
-        <v>306.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PWON.JK</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>15</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>0.102419995</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>0.30543</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>7.699235</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>0.754231</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>21.136</v>
-      </c>
       <c r="K16" s="11" t="n">
-        <v>44.42</v>
+        <v>306.09</v>
       </c>
     </row>
     <row r="17">
@@ -6563,10 +6563,10 @@
         <v>0.40232</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>7.9313364</v>
+        <v>7.9871907</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.92420566</v>
+        <v>0.93071413</v>
       </c>
       <c r="J17" s="11" t="n">
         <v>0</v>
@@ -6581,11 +6581,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -6593,25 +6593,25 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.02158</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>0.06239</v>
-      </c>
-      <c r="H18" s="17" t="n">
-        <v>63.098564</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <v>24233.715</v>
-      </c>
-      <c r="J18" s="11" t="n">
-        <v>0.173</v>
+        <v>0.102419995</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>7.746003</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>0.7586417</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>21.136</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>100.24</v>
+        <v>44.41</v>
       </c>
     </row>
     <row r="19">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -6632,25 +6632,25 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.07034</v>
+        <v>0.02158</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>0.26583</v>
+        <v>0.212</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>0.06239</v>
       </c>
       <c r="H19" s="17" t="n">
-        <v>149.47137</v>
+        <v>64.10256</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>5.470788</v>
-      </c>
-      <c r="J19" s="15" t="n">
-        <v>1.864</v>
+        <v>24616.857</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>0.173</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>54.86</v>
+        <v>100.23</v>
       </c>
     </row>
     <row r="20">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -6671,25 +6671,25 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0</v>
+        <v>0.07034</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.791</v>
+        <v>0.647</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>0.52018</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17.953978</v>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v>3.0556726</v>
-      </c>
-      <c r="J20" s="14" t="n">
-        <v>2.39</v>
+        <v>0.26583</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>147.05882</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>5.3707128</v>
+      </c>
+      <c r="J20" s="15" t="n">
+        <v>1.864</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>272.92</v>
+        <v>54.74</v>
       </c>
     </row>
     <row r="21">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -6710,25 +6710,25 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.15277</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>0.09748999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>0.52018</v>
       </c>
       <c r="H21" t="n">
-        <v>12.002341</v>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>1.8203113</v>
+        <v>17.985348</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>3.0619087</v>
       </c>
       <c r="J21" s="14" t="n">
-        <v>138.994</v>
+        <v>2.39</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>170.8</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22">
@@ -6761,7 +6761,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>11.267164</v>
+        <v>11.032432</v>
       </c>
       <c r="J22" s="11" t="n">
         <v>0.049</v>
@@ -6797,16 +6797,16 @@
         <v>0.53282</v>
       </c>
       <c r="H23" t="n">
-        <v>14.941839</v>
+        <v>14.619884</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>3.0483768</v>
+        <v>2.9828203</v>
       </c>
       <c r="J23" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>466.81</v>
+        <v>466.83</v>
       </c>
     </row>
     <row r="24">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>COIN.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -6827,25 +6827,25 @@
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0</v>
+        <v>0.1093</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>8.94</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>0.30952</v>
-      </c>
-      <c r="H24" s="17" t="n">
-        <v>210.27287</v>
-      </c>
-      <c r="I24" s="14" t="n">
-        <v>10.623804</v>
-      </c>
-      <c r="J24" s="11" t="n">
-        <v>0.261</v>
+        <v>0.221</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>0.08218</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>8.710463000000001</v>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>0.5943329000000001</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>56.561</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>6.23</v>
+        <v>20.55</v>
       </c>
     </row>
     <row r="25">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PBSA.JK</t>
+          <t>COIN.JK</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -6865,26 +6865,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E25" s="8" t="n">
-        <v>0.31697</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>-0.192</v>
-      </c>
-      <c r="G25" s="9" t="n">
-        <v>0.15842</v>
-      </c>
-      <c r="H25" t="n">
-        <v>15.748032</v>
-      </c>
-      <c r="I25" s="15" t="n">
-        <v>4.769388</v>
-      </c>
-      <c r="J25" s="15" t="n">
-        <v>1.461</v>
+      <c r="E25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>204.14673</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>10.38051</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>0.261</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>77.47</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="26">
@@ -6893,11 +6893,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>PBSA.JK</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6905,25 +6905,25 @@
         </is>
       </c>
       <c r="E26" s="8" t="n">
-        <v>0.33183</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>0.415</v>
+        <v>0.31697</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>-0.192</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.13921</v>
-      </c>
-      <c r="H26" s="17" t="n">
-        <v>61.12176</v>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>425000</v>
-      </c>
-      <c r="J26" s="14" t="n">
-        <v>201.586</v>
+        <v>0.15842</v>
+      </c>
+      <c r="H26" t="n">
+        <v>15.873016</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>4.8084817</v>
+      </c>
+      <c r="J26" s="15" t="n">
+        <v>1.461</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>20.86</v>
+        <v>77.48999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -6932,37 +6932,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E27" s="9" t="n">
-        <v>0.12380999</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>-0.075</v>
+      <c r="E27" s="8" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0.415</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.18375</v>
-      </c>
-      <c r="H27" t="n">
-        <v>27.64977</v>
+        <v>0.13921</v>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>62.891567</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>49411.76</v>
+        <v>435000</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>51.917</v>
+        <v>201.586</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>60.76</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="28">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.12082</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>0.008</v>
+        <v>0.12380999</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>-0.075</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.0806</v>
-      </c>
-      <c r="H28" s="10" t="n">
-        <v>9.023039000000001</v>
+        <v>0.18375</v>
+      </c>
+      <c r="H28" t="n">
+        <v>25.573338</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>17280.701</v>
+        <v>45588.234</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>32.802</v>
+        <v>51.917</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>218.33</v>
+        <v>60.61</v>
       </c>
     </row>
     <row r="29">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -7022,103 +7022,103 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
+        <v>0.12082</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>0.0806</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>8.968712999999999</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>17149.123</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>32.802</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>217.98</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>KLBF.JK</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>11</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
         <v>0.14554</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F30" s="9" t="n">
         <v>0.126</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G30" s="9" t="n">
         <v>0.10163</v>
       </c>
-      <c r="H29" t="n">
-        <v>13.051422</v>
-      </c>
-      <c r="I29" s="11" t="n">
+      <c r="H30" t="n">
+        <v>13.054831</v>
+      </c>
+      <c r="I30" s="11" t="n">
         <v>1.9723282</v>
       </c>
-      <c r="J29" s="14" t="n">
+      <c r="J30" s="14" t="n">
         <v>2.102</v>
       </c>
-      <c r="K29" s="11" t="n">
-        <v>76.62</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="K30" s="11" t="n">
+        <v>76.59999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>BRPT.JK</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C31" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E31" s="13" t="n">
         <v>0.35876</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F31" s="13" t="n">
         <v>3.509</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="G31" s="13" t="n">
         <v>0.09752</v>
       </c>
-      <c r="H30" s="12" t="n">
-        <v>13.586956</v>
-      </c>
-      <c r="I30" s="14" t="n">
-        <v>62500</v>
-      </c>
-      <c r="J30" s="14" t="n">
+      <c r="H31" s="12" t="n">
+        <v>13.333333</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>61250</v>
+      </c>
+      <c r="J31" s="14" t="n">
         <v>107.818</v>
       </c>
-      <c r="K30" s="11" t="n">
-        <v>110.4</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>IRSX.JK</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>11</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>0.11936</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>-0.5590000000000001</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>0.06455</v>
-      </c>
-      <c r="H31" s="17" t="n">
-        <v>61.793102</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>9.284974</v>
-      </c>
-      <c r="J31" s="11" t="n">
-        <v>0.216</v>
-      </c>
       <c r="K31" s="11" t="n">
-        <v>7.25</v>
+        <v>110.25</v>
       </c>
     </row>
     <row r="32">
@@ -7127,11 +7127,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PNLF.JK</t>
+          <t>IRSX.JK</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7139,25 +7139,25 @@
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.05041</v>
+        <v>0.11936</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.15737</v>
-      </c>
-      <c r="H32" s="10" t="n">
-        <v>4.6231546</v>
-      </c>
-      <c r="I32" s="11" t="n">
-        <v>0.24470064</v>
+        <v>0.06455</v>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>62.116993</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>9.243524000000001</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>51.48</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="33">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CPRO.JK</t>
+          <t>PNLF.JK</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -7178,25 +7178,25 @@
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.10436</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>0.081</v>
+        <v>0.05041</v>
+      </c>
+      <c r="F33" s="16" t="n">
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.041550003</v>
+        <v>0.15737</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>8.115942</v>
+        <v>4.5825243</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>0.8355216</v>
-      </c>
-      <c r="J33" s="14" t="n">
-        <v>43.245</v>
+        <v>0.24264432</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>6.9</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="34">
@@ -7205,37 +7205,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>CPRO.JK</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.045900002</v>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>0.329</v>
+        <v>0.10436</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>0.081</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.19652</v>
-      </c>
-      <c r="H34" s="17" t="n">
-        <v>152.95169</v>
-      </c>
-      <c r="I34" s="14" t="n">
-        <v>95000.00999999999</v>
+        <v>0.041550003</v>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v>8.115942</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>0.8355216</v>
       </c>
       <c r="J34" s="14" t="n">
-        <v>12.694</v>
+        <v>43.245</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>5.59</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="35">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -7255,26 +7255,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E35" s="9" t="n">
-        <v>0.15447</v>
-      </c>
-      <c r="F35" s="9" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="G35" s="9" t="n">
-        <v>0.091759995</v>
-      </c>
-      <c r="H35" t="n">
-        <v>37.489555</v>
+      <c r="E35" s="8" t="n">
+        <v>0.45251998</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>-0.183</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>52.911343</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>74791.664</v>
+        <v>319117.62</v>
       </c>
       <c r="J35" s="14" t="n">
-        <v>68.20699999999999</v>
+        <v>36.548</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>95.76000000000001</v>
+        <v>102.53</v>
       </c>
     </row>
     <row r="36">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RATU.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -7294,26 +7294,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E36" s="8" t="n">
-        <v>0.45251998</v>
-      </c>
-      <c r="F36" s="16" t="n">
-        <v>-0.183</v>
-      </c>
-      <c r="G36" s="8" t="n">
-        <v>0.31559</v>
-      </c>
-      <c r="H36" s="17" t="n">
-        <v>51.814735</v>
-      </c>
-      <c r="I36" s="14" t="n">
-        <v>313235.28</v>
+      <c r="E36" s="16" t="n">
+        <v>-0.29015</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>-0.21053</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>3.7229817</v>
       </c>
       <c r="J36" s="14" t="n">
-        <v>36.548</v>
-      </c>
-      <c r="K36" s="11" t="n">
-        <v>102.77</v>
+        <v>65.76600000000001</v>
+      </c>
+      <c r="K36" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -7333,26 +7333,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E37" s="16" t="n">
-        <v>-0.29015</v>
+      <c r="E37" s="9" t="n">
+        <v>0.045900002</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.671</v>
+        <v>0.329</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-0.21053</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="15" t="n">
-        <v>3.6875246</v>
+        <v>0.19652</v>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>151.62454</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>93333.336</v>
       </c>
       <c r="J37" s="14" t="n">
-        <v>65.76600000000001</v>
-      </c>
-      <c r="K37" s="15" t="n">
-        <v>0</v>
+        <v>12.694</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <v>5.54</v>
       </c>
     </row>
     <row r="38">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -7373,25 +7373,25 @@
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.05801</v>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>0.317</v>
+        <v>0.15447</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>0.034</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.01754</v>
+        <v>0.091759995</v>
       </c>
       <c r="H38" t="n">
-        <v>29.79668</v>
+        <v>37.73782</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>212500</v>
+        <v>75208.336</v>
       </c>
       <c r="J38" s="14" t="n">
-        <v>276.511</v>
+        <v>68.20699999999999</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>171.16</v>
+        <v>95.66</v>
       </c>
     </row>
     <row r="39">
@@ -7421,10 +7421,10 @@
         <v>0.24544</v>
       </c>
       <c r="H39" s="17" t="n">
-        <v>200</v>
+        <v>204.31654</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>6.840046</v>
+        <v>6.987673</v>
       </c>
       <c r="J39" s="14" t="n">
         <v>2.833</v>
@@ -7460,16 +7460,16 @@
         <v>0.14588</v>
       </c>
       <c r="H40" s="17" t="n">
-        <v>169.53763</v>
+        <v>163.97125</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>35.735443</v>
+        <v>34.8755</v>
       </c>
       <c r="J40" s="14" t="n">
         <v>38.133</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>11.03</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="41">
@@ -7499,16 +7499,16 @@
         <v>0.65328</v>
       </c>
       <c r="H41" s="17" t="n">
-        <v>70.58326</v>
+        <v>71.914894</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>104374.99</v>
+        <v>105624.99</v>
       </c>
       <c r="J41" s="14" t="n">
         <v>34.873</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>11.83</v>
+        <v>11.75</v>
       </c>
     </row>
   </sheetData>

--- a/reports/HEDGEFUND_TERMINAL.xlsx
+++ b/reports/HEDGEFUND_TERMINAL.xlsx
@@ -58,17 +58,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -94,17 +94,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -473,12 +474,12 @@
   <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="47" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,7 +513,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>RISK-OFF</t>
         </is>
       </c>
     </row>
@@ -527,7 +528,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sideways. Selektif akumulasi.</t>
+          <t>IHSG Downtrend. Defensive Positioning.</t>
         </is>
       </c>
     </row>
@@ -545,12 +546,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Total Foreign Today</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>-1.5B</t>
+          <t>Total Foreign Today (Market)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>-36.4M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -562,12 +563,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Total Foreign Accum</t>
+          <t>Total Foreign Accum (Top Institutional Picks)</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>-1.2B</t>
+          <t>39.9M</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -580,7 +581,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>991000</t>
+          <t>19.3M</t>
         </is>
       </c>
     </row>
@@ -592,7 +593,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -600,24 +601,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-12.7M</t>
+          <t>16.1M</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1. Industrials</t>
+          <t>1. Energy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26.2M</t>
+          <t>326.8M</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -625,24 +626,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.4M</t>
+          <t>4.5M</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2. Consumer Defensive</t>
+          <t>2. Industrials</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>245.5M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -650,24 +651,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6.6M</t>
+          <t>85.0M</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3. Healthcare</t>
+          <t>3. Basic Materials</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6.2M</t>
+          <t>81.9M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -675,19 +676,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>9.2M</t>
+          <t>44.9M</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4. Utilities</t>
+          <t>4. Communication Services</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3.0M</t>
+          <t>22.1M</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -695,7 +696,7 @@
           <t>Market Risk</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -704,12 +705,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5. Unknown</t>
+          <t>5. Utilities</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2.4M</t>
+          <t>10.2M</t>
         </is>
       </c>
     </row>
@@ -727,71 +728,71 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>67.7</v>
+        <v>66.7</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-108.7M</t>
+          <t>81.9M</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2. Unknown</t>
+          <t>2. Energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>65</v>
+        <v>61.8</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.4M</t>
+          <t>326.8M</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3. Energy</t>
+          <t>3. Communication Services</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>63</v>
+        <v>55.2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-738.9M</t>
+          <t>22.1M</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4. Healthcare</t>
+          <t>4. Unknown</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6.2M</t>
+          <t>2.7M</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5. Technology</t>
+          <t>5. Financial Services</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55.7</v>
+        <v>51.2</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-210.7M</t>
+          <t>-15.3M</t>
         </is>
       </c>
     </row>
@@ -818,10 +819,10 @@
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -910,20 +911,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9351-9899</t>
+          <t>9875-10475</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8802.678571428572</v>
+        <v>9300</v>
       </c>
       <c r="F2" t="n">
-        <v>10657.14285714286</v>
+        <v>11275</v>
       </c>
       <c r="G2" t="n">
-        <v>11722.85714285714</v>
+        <v>12400</v>
       </c>
       <c r="H2" t="n">
-        <v>12425.89285714286</v>
+        <v>13125</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -932,14 +933,14 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16.48%</t>
+          <t>16.94%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6262422440.65</v>
+        <v>6439026157.84</v>
       </c>
       <c r="L2" t="n">
-        <v>991000</v>
+        <v>19314300</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -953,7 +954,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -961,20 +962,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>711-789</t>
+          <t>2860-2960</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>633.2142857142857</v>
+        <v>2760</v>
       </c>
       <c r="F3" t="n">
-        <v>901.4285714285714</v>
+        <v>3100</v>
       </c>
       <c r="G3" t="n">
-        <v>1013.928571428571</v>
+        <v>3410</v>
       </c>
       <c r="H3" t="n">
-        <v>1163.928571428572</v>
+        <v>3690</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -983,18 +984,18 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.17%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11464380831.06</v>
+        <v>3395257639.74</v>
       </c>
       <c r="L3" t="n">
-        <v>-12701100</v>
+        <v>16104500</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1005,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1012,40 +1013,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6146-6704</t>
+          <t>725-785</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5589.285714285715</v>
+        <v>670</v>
       </c>
       <c r="F4" t="n">
-        <v>7483.035714285714</v>
+        <v>865</v>
       </c>
       <c r="G4" t="n">
-        <v>8231.339285714286</v>
+        <v>955</v>
       </c>
       <c r="H4" t="n">
-        <v>9301.785714285714</v>
+        <v>1055</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20.38%</t>
+          <t>4.59%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>70.12</v>
+        <v>2.81</v>
       </c>
       <c r="L4" t="n">
-        <v>-2404400</v>
+        <v>4524600</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1056,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1063,36 +1064,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2823-2917</t>
+          <t>2440-2500</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2728.571428571428</v>
+        <v>2340</v>
       </c>
       <c r="F5" t="n">
-        <v>3050</v>
+        <v>2700</v>
       </c>
       <c r="G5" t="n">
-        <v>3355</v>
+        <v>2840</v>
       </c>
       <c r="H5" t="n">
-        <v>3360</v>
+        <v>3030</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.81%</t>
+          <t>13.51%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3346996680.7</v>
+        <v>49.21</v>
       </c>
       <c r="L5" t="n">
-        <v>6558700</v>
+        <v>84990300</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1106,7 +1107,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1114,36 +1115,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1276-1374</t>
+          <t>1660-1800</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1178.214285714286</v>
+        <v>1520</v>
       </c>
       <c r="F6" t="n">
-        <v>1508.392857142857</v>
+        <v>2000</v>
       </c>
       <c r="G6" t="n">
-        <v>1659.232142857143</v>
+        <v>2200</v>
       </c>
       <c r="H6" t="n">
-        <v>1822.142857142857</v>
+        <v>2460</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13.98%</t>
+          <t>12.88%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>40.41</v>
+        <v>63.69</v>
       </c>
       <c r="L6" t="n">
-        <v>9168500</v>
+        <v>44947300</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1157,7 +1158,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1165,36 +1166,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1595-1735</t>
+          <t>11275-11825</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1456.071428571429</v>
+        <v>10725</v>
       </c>
       <c r="F7" t="n">
-        <v>1939.285714285714</v>
+        <v>12650</v>
       </c>
       <c r="G7" t="n">
-        <v>2133.214285714286</v>
+        <v>13900</v>
       </c>
       <c r="H7" t="n">
-        <v>2416.785714285714</v>
+        <v>14550</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13.11%</t>
+          <t>15.35%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>64.81</v>
+        <v>5832318378.22</v>
       </c>
       <c r="L7" t="n">
-        <v>5531200</v>
+        <v>381000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1208,7 +1209,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1216,36 +1217,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>693-747</t>
+          <t>1345-1585</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>638.0357142857142</v>
+        <v>1115</v>
       </c>
       <c r="F8" t="n">
-        <v>826.0714285714286</v>
+        <v>1920</v>
       </c>
       <c r="G8" t="n">
-        <v>908.6785714285714</v>
+        <v>2260</v>
       </c>
       <c r="H8" t="n">
-        <v>1009.821428571429</v>
+        <v>2700</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.38%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2.73</v>
+        <v>2.11</v>
       </c>
       <c r="L8" t="n">
-        <v>-4144300</v>
+        <v>-11980700</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1259,7 +1260,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1267,36 +1268,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2569-2791</t>
+          <t>705-785</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2346.785714285714</v>
+        <v>625</v>
       </c>
       <c r="F9" t="n">
-        <v>3098.571428571428</v>
+        <v>900</v>
       </c>
       <c r="G9" t="n">
-        <v>3408.428571428572</v>
+        <v>1010</v>
       </c>
       <c r="H9" t="n">
-        <v>3816.071428571428</v>
+        <v>1160</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20.70%</t>
+          <t>29.84%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>21.64</v>
+        <v>293.91</v>
       </c>
       <c r="L9" t="n">
-        <v>-3687900</v>
+        <v>-2426700</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1310,7 +1311,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1318,40 +1319,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11245-11805</t>
+          <t>5725-6325</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10683.92857142857</v>
+        <v>5150</v>
       </c>
       <c r="F10" t="n">
-        <v>12643.75</v>
+        <v>7100</v>
       </c>
       <c r="G10" t="n">
-        <v>13908.125</v>
+        <v>7900</v>
       </c>
       <c r="H10" t="n">
-        <v>14600</v>
+        <v>8950</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16.08%</t>
+          <t>18.51%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6108929941.24</v>
+        <v>44.1</v>
       </c>
       <c r="L10" t="n">
-        <v>165900</v>
+        <v>-10343700</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1362,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1369,36 +1370,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1433-1667</t>
+          <t>2510-2750</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1200.178571428572</v>
+        <v>2290</v>
       </c>
       <c r="F11" t="n">
-        <v>2003.035714285714</v>
+        <v>3050</v>
       </c>
       <c r="G11" t="n">
-        <v>2339.464285714286</v>
+        <v>3360</v>
       </c>
       <c r="H11" t="n">
-        <v>2788.035714285714</v>
+        <v>3770</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.38%</t>
+          <t>18.77%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2.04</v>
+        <v>19.71</v>
       </c>
       <c r="L11" t="n">
-        <v>12210500</v>
+        <v>709400</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1412,7 +1413,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1420,40 +1421,40 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2304-2396</t>
+          <t>1815-1945</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2210.714285714286</v>
+        <v>1690</v>
       </c>
       <c r="F12" t="n">
-        <v>2530.357142857143</v>
+        <v>2130</v>
       </c>
       <c r="G12" t="n">
-        <v>2783.392857142858</v>
+        <v>2340</v>
       </c>
       <c r="H12" t="n">
-        <v>2842.857142857143</v>
+        <v>2560</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.04%</t>
+          <t>15.03%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>51.1</v>
+        <v>13.23</v>
       </c>
       <c r="L12" t="n">
-        <v>-4536100</v>
+        <v>3244900</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1464,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1471,40 +1472,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3858-4082</t>
+          <t>3250-3490</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3632.5</v>
+        <v>3010</v>
       </c>
       <c r="F13" t="n">
-        <v>4363.214285714285</v>
+        <v>3810</v>
       </c>
       <c r="G13" t="n">
-        <v>4799.535714285715</v>
+        <v>4190</v>
       </c>
       <c r="H13" t="n">
-        <v>5018.214285714285</v>
+        <v>4560</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14.60%</t>
+          <t>21.58%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>35.32</v>
+        <v>8199146885.76</v>
       </c>
       <c r="L13" t="n">
-        <v>-4224700</v>
+        <v>8605000</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1514,44 +1515,44 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>EMAS.JK</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1798-1922</t>
+          <t>7675-8175</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1674.642857142857</v>
+        <v>7200</v>
       </c>
       <c r="F14" t="n">
-        <v>2102.857142857143</v>
+        <v>8800</v>
       </c>
       <c r="G14" t="n">
-        <v>2313.142857142857</v>
+        <v>9675</v>
       </c>
       <c r="H14" t="n">
-        <v>2525.357142857143</v>
+        <v>10250</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16.23%</t>
+          <t>22.68%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>14.36</v>
+        <v>8618293137.690001</v>
       </c>
       <c r="L14" t="n">
-        <v>-1695600</v>
+        <v>-43100</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1565,44 +1566,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3252-3488</t>
+          <t>3440-3780</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3017.5</v>
+        <v>3110</v>
       </c>
       <c r="F15" t="n">
-        <v>3806.785714285714</v>
+        <v>4270</v>
       </c>
       <c r="G15" t="n">
-        <v>4187.464285714286</v>
+        <v>4700</v>
       </c>
       <c r="H15" t="n">
-        <v>4551.785714285714</v>
+        <v>5425</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>22.37%</t>
+          <t>28.05%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>8499441089.94</v>
+        <v>264.71</v>
       </c>
       <c r="L15" t="n">
-        <v>4635800</v>
+        <v>232900</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1616,48 +1617,48 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EMAS.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7762-8238</t>
+          <t>3530-3610</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7287.5</v>
+        <v>3450</v>
       </c>
       <c r="F16" t="n">
-        <v>8875</v>
+        <v>3700</v>
       </c>
       <c r="G16" t="n">
-        <v>9762.5</v>
+        <v>3920</v>
       </c>
       <c r="H16" t="n">
-        <v>10362.5</v>
+        <v>4070</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>23.21%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>8821565588.219999</v>
+        <v>2.73</v>
       </c>
       <c r="L16" t="n">
-        <v>184400</v>
+        <v>-42911100</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1667,48 +1668,48 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3523-3857</t>
+          <t>197-236</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3188.571428571428</v>
+        <v>161</v>
       </c>
       <c r="F17" t="n">
-        <v>4347.857142857143</v>
+        <v>288</v>
       </c>
       <c r="G17" t="n">
-        <v>4782.642857142858</v>
+        <v>340</v>
       </c>
       <c r="H17" t="n">
-        <v>5492.857142857143</v>
+        <v>410</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30.12%</t>
+          <t>59.25%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>476.65</v>
+        <v>13.53</v>
       </c>
       <c r="L17" t="n">
-        <v>-551700</v>
+        <v>248594500</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1719,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1726,40 +1727,40 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8807-9643</t>
+          <t>3770-4010</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7971.428571428572</v>
+        <v>3550</v>
       </c>
       <c r="F18" t="n">
-        <v>10824.10714285714</v>
+        <v>4280</v>
       </c>
       <c r="G18" t="n">
-        <v>12005.35714285714</v>
+        <v>4710</v>
       </c>
       <c r="H18" t="n">
-        <v>13580.35714285714</v>
+        <v>4920</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9.24%</t>
+          <t>13.51%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>5.97</v>
+        <v>32.75</v>
       </c>
       <c r="L18" t="n">
-        <v>-3950500</v>
+        <v>3334100</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1770,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1777,36 +1778,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>216-252</t>
+          <t>104-110</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>179.3571428571429</v>
+        <v>98</v>
       </c>
       <c r="F19" t="n">
-        <v>304.5</v>
+        <v>112</v>
       </c>
       <c r="G19" t="n">
-        <v>342</v>
+        <v>115</v>
       </c>
       <c r="H19" t="n">
-        <v>426.5</v>
+        <v>123</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>61.69%</t>
+          <t>54.29%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>14.04</v>
+        <v>20631296533.55</v>
       </c>
       <c r="L19" t="n">
-        <v>69119800</v>
+        <v>204200</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1820,7 +1821,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1828,40 +1829,40 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3532-3848</t>
+          <t>1190-1290</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3217.5</v>
+        <v>1090</v>
       </c>
       <c r="F20" t="n">
-        <v>4245</v>
+        <v>1425</v>
       </c>
       <c r="G20" t="n">
-        <v>4669.5</v>
+        <v>1570</v>
       </c>
       <c r="H20" t="n">
-        <v>5172.5</v>
+        <v>1745</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>10.47%</t>
+          <t>12.59%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>10.44</v>
+        <v>24.63</v>
       </c>
       <c r="L20" t="n">
-        <v>-15972500</v>
+        <v>13420900</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1871,48 +1872,48 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>UNTR.JK</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>114-122</t>
+          <t>29450-30525</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106.5357142857143</v>
+        <v>28400</v>
       </c>
       <c r="F21" t="n">
-        <v>127.7142857142857</v>
+        <v>32000</v>
       </c>
       <c r="G21" t="n">
-        <v>140.4857142857143</v>
+        <v>35200</v>
       </c>
       <c r="H21" t="n">
-        <v>141.4642857142857</v>
+        <v>35500</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>53.56%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>195.79</v>
+        <v>1.02</v>
       </c>
       <c r="L21" t="n">
-        <v>-1342400</v>
+        <v>1078900</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1933,7 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1958,11 +1959,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>GOTO.JK</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>69119800</v>
+        <v>-611078500</v>
       </c>
     </row>
     <row r="3">
@@ -1971,11 +1972,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>53796800</v>
+        <v>248594500</v>
       </c>
     </row>
     <row r="4">
@@ -1984,11 +1985,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>BUMI.JK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13474500</v>
+        <v>122986100</v>
       </c>
     </row>
     <row r="5">
@@ -1997,11 +1998,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12210500</v>
+        <v>84990300</v>
       </c>
     </row>
     <row r="6">
@@ -2010,11 +2011,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>DEWA.JK</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10894900</v>
+        <v>55692600</v>
       </c>
     </row>
     <row r="7">
@@ -2023,11 +2024,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9168500</v>
+        <v>44947300</v>
       </c>
     </row>
     <row r="8">
@@ -2036,11 +2037,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8526300</v>
+        <v>-42911100</v>
       </c>
     </row>
     <row r="9">
@@ -2053,7 +2054,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8111900</v>
+        <v>39476500</v>
       </c>
     </row>
     <row r="10">
@@ -2062,11 +2063,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMRT.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7833500</v>
+        <v>36164200</v>
       </c>
     </row>
     <row r="11">
@@ -2075,11 +2076,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6640500</v>
+        <v>-29395000</v>
       </c>
     </row>
     <row r="12">
@@ -2088,11 +2089,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>PNLF.JK</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6558700</v>
+        <v>-20566600</v>
       </c>
     </row>
     <row r="13">
@@ -2101,11 +2102,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5531200</v>
+        <v>19724300</v>
       </c>
     </row>
     <row r="14">
@@ -2114,11 +2115,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BBKP.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5269000</v>
+        <v>19314300</v>
       </c>
     </row>
     <row r="15">
@@ -2127,11 +2128,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>BRIS.JK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4853200</v>
+        <v>16329800</v>
       </c>
     </row>
     <row r="16">
@@ -2140,11 +2141,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4635800</v>
+        <v>16104500</v>
       </c>
     </row>
     <row r="17">
@@ -2157,7 +2158,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4228100</v>
+        <v>-14947200</v>
       </c>
     </row>
     <row r="18">
@@ -2166,11 +2167,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LPKR.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4122600</v>
+        <v>-14652300</v>
       </c>
     </row>
     <row r="19">
@@ -2179,11 +2180,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HUMI.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4037800</v>
+        <v>13801700</v>
       </c>
     </row>
     <row r="20">
@@ -2192,11 +2193,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GTSI.JK</t>
+          <t>BBCA.JK</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3447700</v>
+        <v>13696800</v>
       </c>
     </row>
     <row r="21">
@@ -2205,11 +2206,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3303200</v>
+        <v>13420900</v>
       </c>
     </row>
     <row r="22">
@@ -2218,11 +2219,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BRIS.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3000000</v>
+        <v>-11980700</v>
       </c>
     </row>
     <row r="23">
@@ -2231,11 +2232,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PNLF.JK</t>
+          <t>ARCI.JK</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2908800</v>
+        <v>10448100</v>
       </c>
     </row>
     <row r="24">
@@ -2244,11 +2245,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2435900</v>
+        <v>-10343700</v>
       </c>
     </row>
     <row r="25">
@@ -2257,11 +2258,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2385000</v>
+        <v>9794800</v>
       </c>
     </row>
     <row r="26">
@@ -2270,11 +2271,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2076200</v>
+        <v>9571200</v>
       </c>
     </row>
     <row r="27">
@@ -2283,11 +2284,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>TRUE.JK</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1522500</v>
+        <v>8930900</v>
       </c>
     </row>
     <row r="28">
@@ -2296,11 +2297,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>995800</v>
+        <v>8605000</v>
       </c>
     </row>
     <row r="29">
@@ -2309,11 +2310,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>BKSL.JK</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>991000</v>
+        <v>-8292700</v>
       </c>
     </row>
     <row r="30">
@@ -2322,11 +2323,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>835300</v>
+        <v>8212600</v>
       </c>
     </row>
     <row r="31">
@@ -2335,11 +2336,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UNTR.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>676200</v>
+        <v>7888400</v>
       </c>
     </row>
   </sheetData>
@@ -2398,489 +2399,489 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>98</v>
       </c>
       <c r="C3" t="n">
-        <v>79.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-2.3%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>97</v>
       </c>
       <c r="C4" t="n">
-        <v>78.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-3.8%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>96</v>
       </c>
       <c r="C5" t="n">
-        <v>74.8</v>
+        <v>73</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>95</v>
       </c>
       <c r="C6" t="n">
-        <v>69.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-14.2%</t>
+          <t>-13.3%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-6.5%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>66</v>
+        <v>61.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-33.4%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>92</v>
       </c>
       <c r="C9" t="n">
-        <v>65.2</v>
+        <v>59.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-25.5%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>91</v>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>58.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-23.7%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>90</v>
       </c>
       <c r="C11" t="n">
-        <v>61.6</v>
+        <v>58.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-19.1%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>89</v>
       </c>
       <c r="C12" t="n">
-        <v>58</v>
+        <v>52.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-17.5%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>88</v>
       </c>
       <c r="C13" t="n">
-        <v>55.6</v>
+        <v>52</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-14.5%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>EMAS.JK</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" t="n">
-        <v>52.8</v>
+        <v>52</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-8.9%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C15" t="n">
         <v>52</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-14.9%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMAS.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>50.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-10.1%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C17" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-32.1%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>82</v>
       </c>
       <c r="C18" t="n">
-        <v>51</v>
+        <v>48.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-18.3%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>81</v>
       </c>
       <c r="C19" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-34.4%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>47.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.7%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>UNTR.JK</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21" t="n">
-        <v>48</v>
+        <v>44.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-6.3%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ARCI.JK</t>
+          <t>INKP.JK</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>78</v>
       </c>
       <c r="C22" t="n">
-        <v>47.6</v>
+        <v>43</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-23.5%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UNTR.JK</t>
+          <t>MBMA.JK</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>77</v>
       </c>
       <c r="C23" t="n">
-        <v>44.8</v>
+        <v>42</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-19.9%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MBMA.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>76</v>
       </c>
       <c r="C24" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-22.8%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DADA.JK</t>
+          <t>ARCI.JK</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>75</v>
       </c>
       <c r="C25" t="n">
-        <v>38.6</v>
+        <v>39.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-18.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C26" t="n">
-        <v>37.4</v>
+        <v>39.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-16.7%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HRUM.JK</t>
+          <t>DADA.JK</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>73</v>
       </c>
       <c r="C27" t="n">
-        <v>37</v>
+        <v>38.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-20.6%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WIFI.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>72</v>
       </c>
       <c r="C28" t="n">
-        <v>34.8</v>
+        <v>37.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-46.4%</t>
+          <t>-7.7%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>HRUM.JK</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>70</v>
       </c>
       <c r="C29" t="n">
-        <v>31.6</v>
+        <v>37</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2891,738 +2892,738 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>69</v>
       </c>
       <c r="C30" t="n">
-        <v>28.2</v>
+        <v>34</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-7.6%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>68</v>
       </c>
       <c r="C31" t="n">
-        <v>25.6</v>
+        <v>33.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-13.4%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TPIA.JK</t>
+          <t>GOTO.JK</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>24.6</v>
+        <v>26.8</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-18.8%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>TPIA.JK</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>66</v>
       </c>
       <c r="C33" t="n">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-21.5%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>BRIS.JK</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>65</v>
       </c>
       <c r="C34" t="n">
-        <v>22</v>
+        <v>20.8</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-9.8%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>64</v>
       </c>
       <c r="C35" t="n">
-        <v>21.6</v>
+        <v>18.2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-50.3%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>DSSA.JK</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>63</v>
       </c>
       <c r="C36" t="n">
-        <v>21.4</v>
+        <v>17.4</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-34.8%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BRIS.JK</t>
+          <t>BBYB.JK</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C37" t="n">
-        <v>20.8</v>
+        <v>17.4</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-51.2%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DSSA.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>17.4</v>
+        <v>16.8</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-23.4%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BBYB.JK</t>
+          <t>EMTK.JK</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C39" t="n">
-        <v>17.4</v>
+        <v>16.2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-50.2%</t>
+          <t>-50.7%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>ICBP.JK</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>59</v>
       </c>
       <c r="C40" t="n">
-        <v>16.8</v>
+        <v>15</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-11.7%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GOTO.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>59</v>
       </c>
       <c r="C41" t="n">
-        <v>16.8</v>
+        <v>15</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-37.8%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EMTK.JK</t>
+          <t>JPFA.JK</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>56</v>
       </c>
       <c r="C42" t="n">
-        <v>16.2</v>
+        <v>13.2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-22.2%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>55</v>
       </c>
       <c r="C43" t="n">
-        <v>15</v>
+        <v>12.8</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-37.3%</t>
+          <t>-59.1%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LPKR.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>54</v>
       </c>
       <c r="C44" t="n">
-        <v>13.6</v>
+        <v>12</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-32.8%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>EXCL.JK</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>53</v>
       </c>
       <c r="C45" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-37.2%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>PSAB.JK</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C46" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-55.6%</t>
+          <t>-26.4%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PSAB.JK</t>
+          <t>NICL.JK</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>51</v>
       </c>
       <c r="C47" t="n">
-        <v>11.8</v>
+        <v>10.8</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-50.8%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NICL.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>50</v>
       </c>
       <c r="C48" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-50.3%</t>
+          <t>-55.9%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RATU.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C49" t="n">
         <v>10.4</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-53.3%</t>
+          <t>-73.8%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C50" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-71.0%</t>
+          <t>-12.4%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>47</v>
       </c>
       <c r="C51" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-42.5%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>BBCA.JK</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>46</v>
       </c>
       <c r="C52" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-41.2%</t>
+          <t>-16.9%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>46</v>
       </c>
       <c r="C53" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-47.2%</t>
+          <t>-50.6%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BBCA.JK</t>
+          <t>COIN.JK</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C54" t="n">
         <v>7.8</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-70.7%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>PBSA.JK</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C55" t="n">
         <v>7.8</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-54.1%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>COIN.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C56" t="n">
-        <v>7.8</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-51.4%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PBSA.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C57" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-54.3%</t>
+          <t>-22.1%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>39</v>
       </c>
       <c r="C58" t="n">
-        <v>7.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-61.3%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TOBA.JK</t>
+          <t>IRSX.JK</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-44.7%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-18.7%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>PNLF.JK</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>36</v>
       </c>
       <c r="C61" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-60.4%</t>
+          <t>-28.7%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>CPRO.JK</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>36</v>
       </c>
       <c r="C62" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-43.2%</t>
+          <t>-36.0%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PNLF.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>34</v>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-37.8%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CPRO.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>34</v>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-34.9%</t>
+          <t>-56.8%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C65" t="n">
         <v>5.399999999999999</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-69.1%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C66" t="n">
         <v>5.399999999999999</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-55.4%</t>
+          <t>-56.5%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C67" t="n">
         <v>5.399999999999999</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-69.6%</t>
+          <t>-55.7%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C68" t="n">
         <v>5.399999999999999</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-54.9%</t>
+          <t>-32.9%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>WIFI.JK</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C69" t="n">
-        <v>5.399999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-54.3%</t>
+          <t>-42.0%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>GTSI.JK</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C70" t="n">
-        <v>5.399999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-55.0%</t>
         </is>
       </c>
     </row>
@@ -3633,14 +3634,14 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C71" t="n">
         <v>4.8</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-31.8%</t>
         </is>
       </c>
     </row>
@@ -3651,140 +3652,140 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C72" t="n">
         <v>4.8</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-27.5%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>LPKR.JK</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>23</v>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-32.8%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C74" t="n">
         <v>3</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-19.6%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C75" t="n">
         <v>3</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-48.2%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C76" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-61.2%</t>
+          <t>-16.0%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BULL.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C77" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-42.5%</t>
+          <t>-23.8%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EXCL.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C78" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-38.1%</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GTSI.JK</t>
+          <t>BULL.JK</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C79" t="n">
         <v>1.8</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-46.9%</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3803,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-49.7%</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3821,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-53.0%</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3839,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-50.7%</t>
+          <t>-53.5%</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3857,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-32.5%</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3875,14 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-63.8%</t>
+          <t>-65.4%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ICBP.JK</t>
+          <t>BBKP.JK</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -3892,14 +3893,14 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-34.0%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BBKP.JK</t>
+          <t>TRUE.JK</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -3910,133 +3911,133 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-74.5%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TRUE.JK</t>
+          <t>BKSL.JK</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-37.4%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BKSL.JK</t>
+          <t>AMMN.JK</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>7</v>
       </c>
       <c r="C88" t="n">
-        <v>-1.2</v>
+        <v>-3</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-35.2%</t>
+          <t>-32.2%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AMMN.JK</t>
+          <t>VKTR.JK</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C89" t="n">
         <v>-3</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-43.6%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>TOBA.JK</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C90" t="n">
         <v>-3</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-44.2%</t>
+          <t>-37.0%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VKTR.JK</t>
+          <t>HUMI.JK</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C91" t="n">
         <v>-3</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-39.0%</t>
+          <t>-46.9%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HUMI.JK</t>
+          <t>TRIN.JK</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C92" t="n">
         <v>-3</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-44.1%</t>
+          <t>-67.8%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TRIN.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C93" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-64.1%</t>
+          <t>-48.1%</t>
         </is>
       </c>
     </row>
@@ -4047,14 +4048,14 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94" t="n">
         <v>-6</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-36.9%</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4079,7 @@
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4137,17 +4138,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9351-9899</t>
+          <t>9875-10475</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>991000</t>
+          <t>19.3M</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4159,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -4166,17 +4167,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>711-789</t>
+          <t>2860-2960</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12701100</t>
+          <t>16.1M</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4188,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -4195,17 +4196,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2823-2917</t>
+          <t>2440-2500</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6558700</t>
+          <t>85.0M</t>
         </is>
       </c>
     </row>
@@ -4220,21 +4221,21 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1595-1735</t>
+          <t>1660-1800</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5531200</t>
+          <t>44.9M</t>
         </is>
       </c>
     </row>
@@ -4249,21 +4250,21 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1433-1667</t>
+          <t>1345-1585</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>12210500</t>
+          <t>-12.0M</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4279,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -4286,17 +4287,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6146-6704</t>
+          <t>725-785</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>955</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2404400</t>
+          <t>4.5M</t>
         </is>
       </c>
     </row>
@@ -4307,25 +4308,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1276-1374</t>
+          <t>5725-6325</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9168500</t>
+          <t>-10.3M</t>
         </is>
       </c>
     </row>
@@ -4336,25 +4337,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>693-747</t>
+          <t>1815-1945</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-4144300</t>
+          <t>3.2M</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4366,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -4373,17 +4374,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3858-4082</t>
+          <t>3250-3490</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4224700</t>
+          <t>8.6M</t>
         </is>
       </c>
     </row>
@@ -4394,32 +4395,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>EMAS.JK</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1798-1922</t>
+          <t>7675-8175</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1695600</t>
+          <t>-43100</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4427,25 +4428,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2569-2791</t>
+          <t>11275-11825</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3687900</t>
+          <t>381000</t>
         </is>
       </c>
     </row>
@@ -4456,25 +4457,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>114-122</t>
+          <t>197-236</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>340</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1342400</t>
+          <t>248.6M</t>
         </is>
       </c>
     </row>
@@ -4485,25 +4486,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>PBSA.JK</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>235-269</t>
+          <t>1180-1290</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2146100</t>
+          <t>146200</t>
         </is>
       </c>
     </row>
@@ -4514,25 +4515,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>260-304</t>
+          <t>1670-1850</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-23700600</t>
+          <t>-760900</t>
         </is>
       </c>
     </row>
@@ -4543,32 +4544,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>GTSI.JK</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>986-1154</t>
+          <t>197-236</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>338</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6086900</t>
+          <t>-3.4M</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -4576,25 +4577,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11245-11805</t>
+          <t>2510-2750</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>165900</t>
+          <t>709400</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4606,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -4613,17 +4614,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>216-252</t>
+          <t>104-110</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>69119800</t>
+          <t>204200</t>
         </is>
       </c>
     </row>
@@ -4634,25 +4635,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PBSA.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1177-1283</t>
+          <t>232-268</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>370</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>90800</t>
+          <t>-47000</t>
         </is>
       </c>
     </row>
@@ -4663,25 +4664,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1735-1915</t>
+          <t>236-284</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>410</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5616800</t>
+          <t>-14.7M</t>
         </is>
       </c>
     </row>
@@ -4692,32 +4693,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5843-6057</t>
+          <t>925-1095</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-338100</t>
+          <t>-4.1M</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -4725,25 +4726,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DADA.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>50-50</t>
+          <t>3530-3610</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-42.9M</t>
         </is>
       </c>
     </row>
@@ -4754,25 +4755,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>339-349</t>
+          <t>4880-5050</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3303200</t>
+          <t>39.5M</t>
         </is>
       </c>
     </row>
@@ -4783,25 +4784,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7807-8293</t>
+          <t>4220-4340</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-983300</t>
+          <t>-29.4M</t>
         </is>
       </c>
     </row>
@@ -4812,25 +4813,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>BRIS.JK</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4764-5056</t>
+          <t>2160-2260</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-588600</t>
+          <t>16.3M</t>
         </is>
       </c>
     </row>
@@ -4841,32 +4842,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>172-186</t>
+          <t>89-109</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>164</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8526300</t>
+          <t>-6.0M</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -4874,25 +4875,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4806-4954</t>
+          <t>1975-2110</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8111900</t>
+          <t>7.9M</t>
         </is>
       </c>
     </row>
@@ -4903,25 +4904,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>94-114</t>
+          <t>3310-3690</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-44752700</t>
+          <t>-3.5M</t>
         </is>
       </c>
     </row>
@@ -4932,25 +4933,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3541-3619</t>
+          <t>780-850</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-22448200</t>
+          <t>5.8M</t>
         </is>
       </c>
     </row>
@@ -4961,25 +4962,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4239-4341</t>
+          <t>6325-6825</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-13801800</t>
+          <t>-483200</t>
         </is>
       </c>
     </row>
@@ -4990,32 +4991,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BRIS.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2172-2248</t>
+          <t>970-1010</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>1.4M</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -5023,25 +5024,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WIFI.JK</t>
+          <t>DADA.JK</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2196-2364</t>
+          <t>50-53</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3742900</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -5052,25 +5053,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GOTO.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>56-58</t>
+          <t>334-346</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>390</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-204546500</t>
+          <t>-1.6M</t>
         </is>
       </c>
     </row>
@@ -5081,549 +5082,549 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>416-476</t>
+          <t>7625-8125</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2421000</t>
+          <t>380000</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1897-2013</t>
+          <t>167-183</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2391</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-2968600</t>
+          <t>-3.8M</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3424-3796</t>
+          <t>4670-4970</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>644600</t>
+          <t>-67500</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>811-879</t>
+          <t>2070-2210</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>6640500</t>
+          <t>9.6M</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6757-7193</t>
+          <t>2950-3090</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-977300</t>
+          <t>19.7M</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMTK.JK</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>60</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>700-750</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-5.4M</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EXCL.JK</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>53</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2720-2920</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>750400</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="n">
         <v>5</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>PGEO.JK</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>23</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>983-1017</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>1173</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2385000</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>INET.JK</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>34</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>248-280</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-2.6M</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
         <v>1</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>RLCO.JK</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>65</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>5539-6311</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>8194</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2435900</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>KLBF.JK</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>64</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>982-1018</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1171</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2076200</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="n">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>GOTO.JK</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>67</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>54-58</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-611.1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="n">
         <v>2</v>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>LPKR.JK</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>54</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>85-91</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>4122600</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>IRSX.JK</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1971-2089</t>
+          <t>404-464</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>620</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>995800</t>
+          <t>380600</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>WIFI.JK</t>
         </is>
       </c>
       <c r="D44" t="n">
+        <v>27</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2010-2190</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2670</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-5.8M</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ICBP.JK</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
         <v>59</v>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2932-3068</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>3586</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>53796800</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="n">
-        <v>3</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>EMTK.JK</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>56</v>
-      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>722-768</t>
+          <t>7450-7700</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>8825</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1970700</t>
+          <t>2.1M</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>JPFA.JK</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>269-299</t>
+          <t>2210-2350</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-91081100</t>
+          <t>2.5M</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EXCL.JK</t>
+          <t>CPRO.JK</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2677-2883</t>
+          <t>53-57</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-5941300</t>
+          <t>-4.4M</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Consumer Defensive</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2216-2344</t>
+          <t>1835-1945</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1522500</t>
+          <t>-14.9M</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CPRO.JK</t>
+          <t>AMRT.JK</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>55-57</t>
+          <t>1410-1490</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-6488800</t>
+          <t>5.7M</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1949-2051</t>
+          <t>5475-6225</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4228100</t>
+          <t>2.7M</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AMRT.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1401-1479</t>
+          <t>980-1020</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>7833500</t>
+          <t>9.8M</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>LPKR.JK</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -5631,17 +5632,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>5943-6107</t>
+          <t>82-90</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>835300</t>
+          <t>167800</t>
         </is>
       </c>
     </row>
@@ -5693,11 +5694,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BUMI.JK</t>
+          <t>GOTO.JK</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-586435100</v>
+        <v>-611078500</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5711,11 +5712,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GOTO.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-204546500</v>
+        <v>248594500</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5729,11 +5730,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEWA.JK</t>
+          <t>BUMI.JK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-161720500</v>
+        <v>122986100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -5747,11 +5748,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-91081100</v>
+        <v>84990300</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5765,11 +5766,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>DEWA.JK</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>69119800</v>
+        <v>55692600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -5783,11 +5784,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MBMA.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-61600100</v>
+        <v>44947300</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -5801,11 +5802,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>53796800</v>
+        <v>-42911100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -5819,11 +5820,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-44752700</v>
+        <v>39476500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5837,11 +5838,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BULL.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-43193300</v>
+        <v>36164200</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5855,11 +5856,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BBCA.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-38049200</v>
+        <v>-29395000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5895,57 +5896,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>FundScore</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>RevenueGrowth</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Margin</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>PBV</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>DER</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
@@ -5968,25 +5969,25 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="9" t="n">
         <v>0.19143999</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" s="10" t="n">
         <v>0.128</v>
       </c>
-      <c r="G2" s="8" t="n">
+      <c r="G2" s="9" t="n">
         <v>0.38872</v>
       </c>
-      <c r="H2" s="10" t="n">
-        <v>8.090589</v>
-      </c>
-      <c r="I2" s="11" t="n">
-        <v>1.5491217</v>
-      </c>
-      <c r="J2" s="11" t="n">
+      <c r="H2" s="11" t="n">
+        <v>8.223221000000001</v>
+      </c>
+      <c r="I2" s="12" t="n">
+        <v>1.5745171</v>
+      </c>
+      <c r="J2" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="11" t="n">
+      <c r="K2" s="12" t="n">
         <v>603.17</v>
       </c>
     </row>
@@ -6007,64 +6008,64 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="E3" s="10" t="n">
         <v>0.12336001</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="9" t="n">
         <v>0.749</v>
       </c>
-      <c r="G3" s="8" t="n">
+      <c r="G3" s="9" t="n">
         <v>0.34335998</v>
       </c>
-      <c r="H3" s="10" t="n">
-        <v>8.168936</v>
-      </c>
-      <c r="I3" s="11" t="n">
-        <v>0.9494897</v>
-      </c>
-      <c r="J3" s="11" t="n">
+      <c r="H3" s="11" t="n">
+        <v>8.002222</v>
+      </c>
+      <c r="I3" s="12" t="n">
+        <v>0.93011236</v>
+      </c>
+      <c r="J3" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K3" s="11" t="n">
+      <c r="K3" s="12" t="n">
         <v>35.99</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="A4" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>EMTK.JK</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="14" t="n">
         <v>0.20097</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="14" t="n">
         <v>0.466</v>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="14" t="n">
         <v>0.43205002</v>
       </c>
-      <c r="H4" s="12" t="n">
-        <v>6.090084</v>
-      </c>
-      <c r="I4" s="11" t="n">
-        <v>1.1638134</v>
-      </c>
-      <c r="J4" s="14" t="n">
+      <c r="H4" s="13" t="n">
+        <v>5.926592</v>
+      </c>
+      <c r="I4" s="12" t="n">
+        <v>1.13257</v>
+      </c>
+      <c r="J4" s="15" t="n">
         <v>2.444</v>
       </c>
-      <c r="K4" s="11" t="n">
+      <c r="K4" s="12" t="n">
         <v>122.33</v>
       </c>
     </row>
@@ -6085,25 +6086,25 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="10" t="n">
         <v>0.17465</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="9" t="n">
         <v>0.17</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="9" t="n">
         <v>0.40405998</v>
       </c>
-      <c r="H5" s="10" t="n">
-        <v>9.523809</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>1.6638672</v>
-      </c>
-      <c r="J5" s="11" t="n">
+      <c r="H5" s="11" t="n">
+        <v>9.497207</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>1.6592195</v>
+      </c>
+      <c r="J5" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="K5" s="12" t="n">
         <v>375.9</v>
       </c>
     </row>
@@ -6124,25 +6125,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="9" t="n">
         <v>0.25308</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <v>0.097</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="9" t="n">
         <v>0.27552</v>
       </c>
-      <c r="H6" s="10" t="n">
-        <v>10.460251</v>
-      </c>
-      <c r="I6" s="15" t="n">
-        <v>2.3364198</v>
-      </c>
-      <c r="J6" s="14" t="n">
+      <c r="H6" s="11" t="n">
+        <v>9.789216</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>2.1865363</v>
+      </c>
+      <c r="J6" s="15" t="n">
         <v>23.671</v>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="K6" s="12" t="n">
         <v>126.67</v>
       </c>
     </row>
@@ -6163,64 +6164,64 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="9" t="n">
         <v>0.24911</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="9" t="n">
         <v>4.381</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="9" t="n">
         <v>0.71615</v>
       </c>
       <c r="H7" t="n">
-        <v>27.225132</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>6.504065</v>
-      </c>
-      <c r="J7" s="14" t="n">
+        <v>25.916231</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>6.1913695</v>
+      </c>
+      <c r="J7" s="15" t="n">
         <v>5.093</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="12" t="n">
         <v>3.82</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>JPFA.JK</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <v>0.23401</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="14" t="n">
         <v>0.213</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="14" t="n">
         <v>0.06594999999999999</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="13" t="n">
         <v>6.626944</v>
       </c>
-      <c r="I8" s="11" t="n">
+      <c r="I8" s="12" t="n">
         <v>1.4204581</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J8" s="15" t="n">
         <v>59.254</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="K8" s="12" t="n">
         <v>344.05</v>
       </c>
     </row>
@@ -6241,25 +6242,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="9" t="n">
         <v>0.24216999</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="10" t="n">
         <v>0.025</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="10" t="n">
         <v>0.15481</v>
       </c>
-      <c r="H9" s="10" t="n">
-        <v>6.1311984</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>22488.318</v>
-      </c>
-      <c r="J9" s="14" t="n">
+      <c r="H9" s="11" t="n">
+        <v>6.4815526</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>23773.365</v>
+      </c>
+      <c r="J9" s="15" t="n">
         <v>22.636</v>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="K9" s="12" t="n">
         <v>1569.84</v>
       </c>
     </row>
@@ -6269,7 +6270,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6280,26 +6281,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>0.15277</v>
+      <c r="E10" s="10" t="n">
+        <v>0.096820004</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>0.09748999999999999</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>11.876207</v>
-      </c>
-      <c r="I10" s="11" t="n">
-        <v>1.8025521</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>138.994</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>170.93</v>
+        <v>0.328</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>0.13656999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23.352922</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>29038.46</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <v>32.33</v>
       </c>
     </row>
     <row r="11">
@@ -6319,25 +6320,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="10" t="n">
         <v>0.15604</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="10" t="n">
         <v>0.075</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G11" s="9" t="n">
         <v>0.31919</v>
       </c>
       <c r="H11" t="n">
         <v>13.477254</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="12" t="n">
         <v>1.9622712</v>
       </c>
-      <c r="J11" s="11" t="n">
+      <c r="J11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K11" s="12" t="n">
         <v>163.98</v>
       </c>
     </row>
@@ -6358,64 +6359,64 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="9" t="n">
         <v>0.65794</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>-0.261</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="9" t="n">
         <v>0.27632</v>
       </c>
       <c r="H12" t="n">
-        <v>18.11453</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>11.907811</v>
-      </c>
-      <c r="J12" s="11" t="n">
+        <v>17.91975</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>11.77977</v>
+      </c>
+      <c r="J12" s="12" t="n">
         <v>0.378</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="K12" s="12" t="n">
         <v>51.34</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="A13" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>HRTA.JK</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="14" t="n">
         <v>0.28483</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="14" t="n">
         <v>1.009</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="14" t="n">
         <v>0.023759998</v>
       </c>
-      <c r="H13" s="12" t="n">
-        <v>17.241379</v>
-      </c>
-      <c r="I13" s="15" t="n">
-        <v>4.3781047</v>
-      </c>
-      <c r="J13" s="14" t="n">
+      <c r="H13" s="13" t="n">
+        <v>16.919712</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>4.2964234</v>
+      </c>
+      <c r="J13" s="15" t="n">
         <v>139.825</v>
       </c>
-      <c r="K13" s="11" t="n">
+      <c r="K13" s="12" t="n">
         <v>155.44</v>
       </c>
     </row>
@@ -6436,25 +6437,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="10" t="n">
         <v>0.14062001</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="10" t="n">
         <v>0.075</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="10" t="n">
         <v>0.04955</v>
       </c>
-      <c r="H14" s="10" t="n">
-        <v>7.9423914</v>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>1.0303642</v>
-      </c>
-      <c r="J14" s="14" t="n">
+      <c r="H14" s="11" t="n">
+        <v>7.889442</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>1.0234951</v>
+      </c>
+      <c r="J14" s="15" t="n">
         <v>12.229</v>
       </c>
-      <c r="K14" s="11" t="n">
+      <c r="K14" s="12" t="n">
         <v>94.43000000000001</v>
       </c>
     </row>
@@ -6475,64 +6476,64 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="9" t="n">
         <v>0.28336</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="9" t="n">
         <v>0.879</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G15" s="9" t="n">
         <v>0.21154</v>
       </c>
       <c r="H15" t="n">
-        <v>29.672817</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>121785.71</v>
-      </c>
-      <c r="J15" s="14" t="n">
+        <v>28.97668</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>118928.57</v>
+      </c>
+      <c r="J15" s="15" t="n">
         <v>118.6</v>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="K15" s="12" t="n">
         <v>57.46</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>TPIA.JK</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="14" t="n">
         <v>0.42018002</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="14" t="n">
         <v>4.295</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G16" s="14" t="n">
         <v>0.2208</v>
       </c>
-      <c r="H16" s="12" t="n">
-        <v>18.621975</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>126666.664</v>
-      </c>
-      <c r="J16" s="14" t="n">
+      <c r="H16" s="13" t="n">
+        <v>18.785324</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>127777.77</v>
+      </c>
+      <c r="J16" s="15" t="n">
         <v>82.7</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="K16" s="12" t="n">
         <v>306.09</v>
       </c>
     </row>
@@ -6553,25 +6554,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="10" t="n">
         <v>0.1173</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <v>0.028</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G17" s="9" t="n">
         <v>0.40232</v>
       </c>
-      <c r="H17" s="10" t="n">
-        <v>7.9871907</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>0.93071413</v>
-      </c>
-      <c r="J17" s="11" t="n">
+      <c r="H17" s="11" t="n">
+        <v>7.9685726</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>0.92854464</v>
+      </c>
+      <c r="J17" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="K17" s="12" t="n">
         <v>537.11</v>
       </c>
     </row>
@@ -6592,25 +6593,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="10" t="n">
         <v>0.102419995</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="10" t="n">
         <v>0.144</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G18" s="9" t="n">
         <v>0.30543</v>
       </c>
-      <c r="H18" s="10" t="n">
-        <v>7.746003</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>0.7586417</v>
-      </c>
-      <c r="J18" s="14" t="n">
+      <c r="H18" s="11" t="n">
+        <v>7.6559334</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>0.7498203</v>
+      </c>
+      <c r="J18" s="15" t="n">
         <v>21.136</v>
       </c>
-      <c r="K18" s="11" t="n">
+      <c r="K18" s="12" t="n">
         <v>44.41</v>
       </c>
     </row>
@@ -6631,25 +6632,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="10" t="n">
         <v>0.02158</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="9" t="n">
         <v>0.212</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="10" t="n">
         <v>0.06239</v>
       </c>
-      <c r="H19" s="17" t="n">
-        <v>64.10256</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>24616.857</v>
-      </c>
-      <c r="J19" s="11" t="n">
+      <c r="H19" s="18" t="n">
+        <v>60.11174</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>23084.291</v>
+      </c>
+      <c r="J19" s="12" t="n">
         <v>0.173</v>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="K19" s="12" t="n">
         <v>100.23</v>
       </c>
     </row>
@@ -6659,7 +6660,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -6670,26 +6671,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E20" s="9" t="n">
-        <v>0.07034</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>0.26583</v>
-      </c>
-      <c r="H20" s="17" t="n">
-        <v>147.05882</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>5.3707128</v>
+      <c r="E20" s="10" t="n">
+        <v>0.15277</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>0.09748999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12.519746</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>1.9002273</v>
       </c>
       <c r="J20" s="15" t="n">
-        <v>1.864</v>
-      </c>
-      <c r="K20" s="11" t="n">
-        <v>54.74</v>
+        <v>138.994</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>170.93</v>
       </c>
     </row>
     <row r="21">
@@ -6698,7 +6699,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -6709,26 +6710,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>0.52018</v>
-      </c>
-      <c r="H21" t="n">
-        <v>17.985348</v>
+      <c r="E21" s="10" t="n">
+        <v>0.07034</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>0.26583</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>143.8619</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>3.0619087</v>
-      </c>
-      <c r="J21" s="14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="K21" s="11" t="n">
-        <v>273</v>
+        <v>5.253958</v>
+      </c>
+      <c r="J21" s="16" t="n">
+        <v>1.864</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>54.74</v>
       </c>
     </row>
     <row r="22">
@@ -6748,25 +6749,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>-0.04084</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="9" t="n">
         <v>0.368</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="10" t="n">
         <v>-0.69613</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="14" t="n">
-        <v>11.032432</v>
-      </c>
-      <c r="J22" s="11" t="n">
+      <c r="I22" s="15" t="n">
+        <v>10.171745</v>
+      </c>
+      <c r="J22" s="12" t="n">
         <v>0.049</v>
       </c>
-      <c r="K22" s="15" t="n">
+      <c r="K22" s="16" t="n">
         <v>-0.71</v>
       </c>
     </row>
@@ -6787,25 +6788,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="9" t="n">
         <v>0.21143</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="17" t="n">
         <v>-0.027</v>
       </c>
-      <c r="G23" s="8" t="n">
+      <c r="G23" s="9" t="n">
         <v>0.53282</v>
       </c>
       <c r="H23" t="n">
-        <v>14.619884</v>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v>2.9828203</v>
-      </c>
-      <c r="J23" s="11" t="n">
+        <v>14.780541</v>
+      </c>
+      <c r="I23" s="16" t="n">
+        <v>3.0155985</v>
+      </c>
+      <c r="J23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="11" t="n">
+      <c r="K23" s="12" t="n">
         <v>466.83</v>
       </c>
     </row>
@@ -6826,25 +6827,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="10" t="n">
         <v>0.1093</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="9" t="n">
         <v>0.221</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="10" t="n">
         <v>0.08218</v>
       </c>
-      <c r="H24" s="10" t="n">
-        <v>8.710463000000001</v>
-      </c>
-      <c r="I24" s="11" t="n">
-        <v>0.5943329000000001</v>
-      </c>
-      <c r="J24" s="14" t="n">
+      <c r="H24" s="11" t="n">
+        <v>8.515815999999999</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>0.5810516999999999</v>
+      </c>
+      <c r="J24" s="15" t="n">
         <v>56.561</v>
       </c>
-      <c r="K24" s="11" t="n">
+      <c r="K24" s="12" t="n">
         <v>20.55</v>
       </c>
     </row>
@@ -6865,25 +6866,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="9" t="n">
         <v>8.94</v>
       </c>
-      <c r="G25" s="8" t="n">
+      <c r="G25" s="9" t="n">
         <v>0.30952</v>
       </c>
-      <c r="H25" s="17" t="n">
-        <v>204.14673</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>10.38051</v>
-      </c>
-      <c r="J25" s="11" t="n">
+      <c r="H25" s="18" t="n">
+        <v>194.57735</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>9.893924999999999</v>
+      </c>
+      <c r="J25" s="12" t="n">
         <v>0.261</v>
       </c>
-      <c r="K25" s="11" t="n">
+      <c r="K25" s="12" t="n">
         <v>6.27</v>
       </c>
     </row>
@@ -6904,25 +6905,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E26" s="9" t="n">
         <v>0.31697</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F26" s="17" t="n">
         <v>-0.192</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="10" t="n">
         <v>0.15842</v>
       </c>
       <c r="H26" t="n">
-        <v>15.873016</v>
-      </c>
-      <c r="I26" s="15" t="n">
-        <v>4.8084817</v>
-      </c>
-      <c r="J26" s="15" t="n">
+        <v>15.937541</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <v>4.828028</v>
+      </c>
+      <c r="J26" s="16" t="n">
         <v>1.461</v>
       </c>
-      <c r="K26" s="11" t="n">
+      <c r="K26" s="12" t="n">
         <v>77.48999999999999</v>
       </c>
     </row>
@@ -6943,25 +6944,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="9" t="n">
         <v>0.33183</v>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F27" s="9" t="n">
         <v>0.415</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" s="10" t="n">
         <v>0.13921</v>
       </c>
-      <c r="H27" s="17" t="n">
-        <v>62.891567</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>435000</v>
-      </c>
-      <c r="J27" s="14" t="n">
+      <c r="H27" s="18" t="n">
+        <v>59.277107</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>410000</v>
+      </c>
+      <c r="J27" s="15" t="n">
         <v>201.586</v>
       </c>
-      <c r="K27" s="11" t="n">
+      <c r="K27" s="12" t="n">
         <v>20.75</v>
       </c>
     </row>
@@ -6982,25 +6983,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="10" t="n">
         <v>0.12380999</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="17" t="n">
         <v>-0.075</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="10" t="n">
         <v>0.18375</v>
       </c>
       <c r="H28" t="n">
-        <v>25.573338</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>45588.234</v>
-      </c>
-      <c r="J28" s="14" t="n">
+        <v>24.170929</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>43088.234</v>
+      </c>
+      <c r="J28" s="15" t="n">
         <v>51.917</v>
       </c>
-      <c r="K28" s="11" t="n">
+      <c r="K28" s="12" t="n">
         <v>60.61</v>
       </c>
     </row>
@@ -7021,104 +7022,104 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="10" t="n">
         <v>0.12082</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="10" t="n">
         <v>0.008</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G29" s="10" t="n">
         <v>0.0806</v>
       </c>
-      <c r="H29" s="10" t="n">
-        <v>8.968712999999999</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>17149.123</v>
-      </c>
-      <c r="J29" s="14" t="n">
+      <c r="H29" s="11" t="n">
+        <v>9.358656999999999</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>17894.736</v>
+      </c>
+      <c r="J29" s="15" t="n">
         <v>32.802</v>
       </c>
-      <c r="K29" s="11" t="n">
+      <c r="K29" s="12" t="n">
         <v>217.98</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>KLBF.JK</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>BRPT.JK</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E30" s="9" t="n">
-        <v>0.14554</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="G30" s="9" t="n">
-        <v>0.10163</v>
-      </c>
-      <c r="H30" t="n">
-        <v>13.054831</v>
-      </c>
-      <c r="I30" s="11" t="n">
-        <v>1.9723282</v>
-      </c>
-      <c r="J30" s="14" t="n">
-        <v>2.102</v>
-      </c>
-      <c r="K30" s="11" t="n">
-        <v>76.59999999999999</v>
+      <c r="E30" s="14" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>3.509</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>0.09752</v>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>13.015873</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>59791.668</v>
+      </c>
+      <c r="J30" s="15" t="n">
+        <v>107.818</v>
+      </c>
+      <c r="K30" s="12" t="n">
+        <v>110.25</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>BRPT.JK</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>IRSX.JK</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>11</v>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E31" s="13" t="n">
-        <v>0.35876</v>
-      </c>
-      <c r="F31" s="13" t="n">
-        <v>3.509</v>
-      </c>
-      <c r="G31" s="13" t="n">
-        <v>0.09752</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>13.333333</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>61250</v>
-      </c>
-      <c r="J31" s="14" t="n">
-        <v>107.818</v>
-      </c>
-      <c r="K31" s="11" t="n">
-        <v>110.25</v>
+      <c r="E31" s="10" t="n">
+        <v>0.11936</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>-0.5590000000000001</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>0.06455</v>
+      </c>
+      <c r="H31" s="18" t="n">
+        <v>60.445683</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>8.994819</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="K31" s="12" t="n">
+        <v>7.18</v>
       </c>
     </row>
     <row r="32">
@@ -7127,7 +7128,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -7138,26 +7139,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E32" s="9" t="n">
-        <v>0.11936</v>
-      </c>
-      <c r="F32" s="16" t="n">
-        <v>-0.5590000000000001</v>
-      </c>
-      <c r="G32" s="9" t="n">
-        <v>0.06455</v>
-      </c>
-      <c r="H32" s="17" t="n">
-        <v>62.116993</v>
-      </c>
-      <c r="I32" s="14" t="n">
-        <v>9.243524000000001</v>
-      </c>
-      <c r="J32" s="11" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="K32" s="11" t="n">
-        <v>7.18</v>
+      <c r="E32" s="10" t="n">
+        <v>0.14554</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>0.10163</v>
+      </c>
+      <c r="H32" t="n">
+        <v>13.054831</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>1.9723282</v>
+      </c>
+      <c r="J32" s="15" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="K32" s="12" t="n">
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -7177,25 +7178,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="10" t="n">
         <v>0.05041</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="17" t="n">
         <v>-0.07199999999999999</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" s="10" t="n">
         <v>0.15737</v>
       </c>
-      <c r="H33" s="10" t="n">
-        <v>4.5825243</v>
-      </c>
-      <c r="I33" s="11" t="n">
-        <v>0.24264432</v>
-      </c>
-      <c r="J33" s="11" t="n">
+      <c r="H33" s="11" t="n">
+        <v>4.6213593</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>0.24470064</v>
+      </c>
+      <c r="J33" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="11" t="n">
+      <c r="K33" s="12" t="n">
         <v>51.5</v>
       </c>
     </row>
@@ -7216,25 +7217,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="10" t="n">
         <v>0.10436</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="10" t="n">
         <v>0.081</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="10" t="n">
         <v>0.041550003</v>
       </c>
-      <c r="H34" s="10" t="n">
-        <v>8.115942</v>
-      </c>
-      <c r="I34" s="11" t="n">
-        <v>0.8355216</v>
-      </c>
-      <c r="J34" s="14" t="n">
+      <c r="H34" s="11" t="n">
+        <v>7.9710145</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>0.8206015</v>
+      </c>
+      <c r="J34" s="15" t="n">
         <v>43.245</v>
       </c>
-      <c r="K34" s="11" t="n">
+      <c r="K34" s="12" t="n">
         <v>6.9</v>
       </c>
     </row>
@@ -7255,25 +7256,25 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="9" t="n">
         <v>0.45251998</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="F35" s="17" t="n">
         <v>-0.183</v>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="G35" s="9" t="n">
         <v>0.31559</v>
       </c>
-      <c r="H35" s="17" t="n">
-        <v>52.911343</v>
-      </c>
-      <c r="I35" s="14" t="n">
-        <v>319117.62</v>
-      </c>
-      <c r="J35" s="14" t="n">
+      <c r="H35" s="18" t="n">
+        <v>49.98537</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>301470.56</v>
+      </c>
+      <c r="J35" s="15" t="n">
         <v>36.548</v>
       </c>
-      <c r="K35" s="11" t="n">
+      <c r="K35" s="12" t="n">
         <v>102.53</v>
       </c>
     </row>
@@ -7294,25 +7295,25 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>-0.29015</v>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F36" s="9" t="n">
         <v>0.671</v>
       </c>
-      <c r="G36" s="9" t="n">
+      <c r="G36" s="10" t="n">
         <v>-0.21053</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="15" t="n">
-        <v>3.7229817</v>
-      </c>
-      <c r="J36" s="14" t="n">
+      <c r="I36" s="16" t="n">
+        <v>3.3613205</v>
+      </c>
+      <c r="J36" s="15" t="n">
         <v>65.76600000000001</v>
       </c>
-      <c r="K36" s="15" t="n">
+      <c r="K36" s="16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7333,25 +7334,25 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="10" t="n">
         <v>0.045900002</v>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="F37" s="9" t="n">
         <v>0.329</v>
       </c>
-      <c r="G37" s="9" t="n">
+      <c r="G37" s="10" t="n">
         <v>0.19652</v>
       </c>
-      <c r="H37" s="17" t="n">
-        <v>151.62454</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>93333.336</v>
-      </c>
-      <c r="J37" s="14" t="n">
+      <c r="H37" s="18" t="n">
+        <v>147.11191</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>90555.56</v>
+      </c>
+      <c r="J37" s="15" t="n">
         <v>12.694</v>
       </c>
-      <c r="K37" s="11" t="n">
+      <c r="K37" s="12" t="n">
         <v>5.54</v>
       </c>
     </row>
@@ -7372,25 +7373,25 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="10" t="n">
         <v>0.15447</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="10" t="n">
         <v>0.034</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="10" t="n">
         <v>0.091759995</v>
       </c>
       <c r="H38" t="n">
-        <v>37.73782</v>
-      </c>
-      <c r="I38" s="14" t="n">
-        <v>75208.336</v>
-      </c>
-      <c r="J38" s="14" t="n">
+        <v>36.587914</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>72916.664</v>
+      </c>
+      <c r="J38" s="15" t="n">
         <v>68.20699999999999</v>
       </c>
-      <c r="K38" s="11" t="n">
+      <c r="K38" s="12" t="n">
         <v>95.66</v>
       </c>
     </row>
@@ -7411,25 +7412,25 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="10" t="n">
         <v>0.06432</v>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="9" t="n">
         <v>1.905</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G39" s="9" t="n">
         <v>0.24544</v>
       </c>
-      <c r="H39" s="17" t="n">
-        <v>204.31654</v>
-      </c>
-      <c r="I39" s="14" t="n">
-        <v>6.987673</v>
-      </c>
-      <c r="J39" s="14" t="n">
+      <c r="H39" s="18" t="n">
+        <v>189.92805</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>6.495583</v>
+      </c>
+      <c r="J39" s="15" t="n">
         <v>2.833</v>
       </c>
-      <c r="K39" s="11" t="n">
+      <c r="K39" s="12" t="n">
         <v>1.39</v>
       </c>
     </row>
@@ -7450,25 +7451,25 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E40" s="8" t="n">
+      <c r="E40" s="9" t="n">
         <v>0.23723</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="10" t="n">
         <v>0.145</v>
       </c>
-      <c r="G40" s="9" t="n">
+      <c r="G40" s="10" t="n">
         <v>0.14588</v>
       </c>
-      <c r="H40" s="17" t="n">
-        <v>163.97125</v>
-      </c>
-      <c r="I40" s="14" t="n">
-        <v>34.8755</v>
-      </c>
-      <c r="J40" s="14" t="n">
+      <c r="H40" s="18" t="n">
+        <v>158.13118</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>33.633358</v>
+      </c>
+      <c r="J40" s="15" t="n">
         <v>38.133</v>
       </c>
-      <c r="K40" s="11" t="n">
+      <c r="K40" s="12" t="n">
         <v>11.13</v>
       </c>
     </row>
@@ -7489,25 +7490,25 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="9" t="n">
         <v>0.421</v>
       </c>
-      <c r="G41" s="8" t="n">
+      <c r="G41" s="9" t="n">
         <v>0.65328</v>
       </c>
-      <c r="H41" s="17" t="n">
-        <v>71.914894</v>
-      </c>
-      <c r="I41" s="14" t="n">
-        <v>105624.99</v>
-      </c>
-      <c r="J41" s="14" t="n">
+      <c r="H41" s="18" t="n">
+        <v>69.3617</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>101874.99</v>
+      </c>
+      <c r="J41" s="15" t="n">
         <v>34.873</v>
       </c>
-      <c r="K41" s="11" t="n">
+      <c r="K41" s="12" t="n">
         <v>11.75</v>
       </c>
     </row>

--- a/reports/HEDGEFUND_TERMINAL.xlsx
+++ b/reports/HEDGEFUND_TERMINAL.xlsx
@@ -63,12 +63,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -94,17 +94,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -475,11 +474,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,7 +491,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12 March 2026</t>
+          <t>16 March 2026</t>
         </is>
       </c>
     </row>
@@ -504,7 +503,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -539,7 +538,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7"/>
@@ -551,7 +550,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>-36.4M</t>
+          <t>-433.8M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -566,9 +565,9 @@
           <t>Total Foreign Accum (Top Institutional Picks)</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>39.9M</t>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>-889.0M</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -581,7 +580,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.3M</t>
+          <t>15.5M</t>
         </is>
       </c>
     </row>
@@ -593,7 +592,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -601,7 +600,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16.1M</t>
+          <t>989600</t>
         </is>
       </c>
     </row>
@@ -613,12 +612,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>326.8M</t>
+          <t>406.5M</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -626,7 +625,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4.5M</t>
+          <t>300600</t>
         </is>
       </c>
     </row>
@@ -638,12 +637,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>245.5M</t>
+          <t>272.2M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -651,24 +650,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>85.0M</t>
+          <t>14.2M</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3. Basic Materials</t>
+          <t>3. Utilities</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>81.9M</t>
+          <t>47.6M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -676,7 +675,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>44.9M</t>
+          <t>16.3M</t>
         </is>
       </c>
     </row>
@@ -688,7 +687,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22.1M</t>
+          <t>45.3M</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -696,7 +695,7 @@
           <t>Market Risk</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -705,12 +704,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5. Utilities</t>
+          <t>5. Healthcare</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10.2M</t>
+          <t>43.6M</t>
         </is>
       </c>
     </row>
@@ -728,71 +727,71 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>81.9M</t>
+          <t>-36.0M</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2. Energy</t>
+          <t>2. Financial Services</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>61.8</v>
+        <v>58.8</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>326.8M</t>
+          <t>-103.4M</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3. Communication Services</t>
+          <t>3. Healthcare</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>55.2</v>
+        <v>53</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>22.1M</t>
+          <t>43.6M</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4. Unknown</t>
+          <t>4. Communication Services</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.7M</t>
+          <t>45.3M</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5. Financial Services</t>
+          <t>5. Energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-15.3M</t>
+          <t>406.5M</t>
         </is>
       </c>
     </row>
@@ -825,7 +824,7 @@
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
   </cols>
@@ -911,20 +910,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9875-10475</t>
+          <t>10050-10650</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9300</v>
+        <v>9475</v>
       </c>
       <c r="F2" t="n">
-        <v>11275</v>
+        <v>11450</v>
       </c>
       <c r="G2" t="n">
-        <v>12400</v>
+        <v>12600</v>
       </c>
       <c r="H2" t="n">
-        <v>13125</v>
+        <v>13300</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -933,14 +932,14 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16.94%</t>
+          <t>17.75%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6439026157.84</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>19314300</v>
+        <v>15516700</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -954,7 +953,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -962,36 +961,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2860-2960</t>
+          <t>2480-2720</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2760</v>
+        <v>2250</v>
       </c>
       <c r="F3" t="n">
-        <v>3100</v>
+        <v>3040</v>
       </c>
       <c r="G3" t="n">
-        <v>3410</v>
+        <v>3360</v>
       </c>
       <c r="H3" t="n">
-        <v>3690</v>
+        <v>3790</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>16.42%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3395257639.74</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>16104500</v>
+        <v>989600</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1005,7 +1004,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1013,36 +1012,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>725-785</t>
+          <t>11050-11650</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>670</v>
+        <v>10475</v>
       </c>
       <c r="F4" t="n">
-        <v>865</v>
+        <v>12500</v>
       </c>
       <c r="G4" t="n">
-        <v>955</v>
+        <v>13750</v>
       </c>
       <c r="H4" t="n">
-        <v>1055</v>
+        <v>14475</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>14.03%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2.81</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>4524600</v>
+        <v>300600</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1056,7 +1055,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1064,36 +1063,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2440-2500</t>
+          <t>2870-2970</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2340</v>
+        <v>2770</v>
       </c>
       <c r="F5" t="n">
-        <v>2700</v>
+        <v>3120</v>
       </c>
       <c r="G5" t="n">
-        <v>2840</v>
+        <v>3430</v>
       </c>
       <c r="H5" t="n">
-        <v>3030</v>
+        <v>3440</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13.51%</t>
+          <t>9.23%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>49.21</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>84990300</v>
+        <v>14235600</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1107,7 +1106,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1115,36 +1114,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1660-1800</t>
+          <t>715-775</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1520</v>
+        <v>660</v>
       </c>
       <c r="F6" t="n">
-        <v>2000</v>
+        <v>855</v>
       </c>
       <c r="G6" t="n">
-        <v>2200</v>
+        <v>940</v>
       </c>
       <c r="H6" t="n">
-        <v>2460</v>
+        <v>1040</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12.88%</t>
+          <t>5.33%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>63.69</v>
+        <v>3.1</v>
       </c>
       <c r="L6" t="n">
-        <v>44947300</v>
+        <v>16337800</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1158,7 +1157,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1166,36 +1165,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11275-11825</t>
+          <t>2380-2500</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10725</v>
+        <v>2280</v>
       </c>
       <c r="F7" t="n">
-        <v>12650</v>
+        <v>2650</v>
       </c>
       <c r="G7" t="n">
-        <v>13900</v>
+        <v>2910</v>
       </c>
       <c r="H7" t="n">
-        <v>14550</v>
+        <v>3010</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.35%</t>
+          <t>12.40%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>5832318378.22</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>381000</v>
+        <v>4812100</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1209,7 +1208,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1217,40 +1216,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1345-1585</t>
+          <t>665-745</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1115</v>
+        <v>585</v>
       </c>
       <c r="F8" t="n">
-        <v>1920</v>
+        <v>860</v>
       </c>
       <c r="G8" t="n">
-        <v>2260</v>
+        <v>975</v>
       </c>
       <c r="H8" t="n">
-        <v>2700</v>
+        <v>1125</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>29.04%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2.11</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>-11980700</v>
+        <v>20676500</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1259,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1268,36 +1267,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>705-785</t>
+          <t>4620-4780</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>625</v>
+        <v>4470</v>
       </c>
       <c r="F9" t="n">
-        <v>900</v>
+        <v>4970</v>
       </c>
       <c r="G9" t="n">
-        <v>1010</v>
+        <v>5400</v>
       </c>
       <c r="H9" t="n">
-        <v>1160</v>
+        <v>5475</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>29.84%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>293.91</v>
+        <v>2.11</v>
       </c>
       <c r="L9" t="n">
-        <v>-2426700</v>
+        <v>-23067200</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1311,7 +1310,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1319,36 +1318,36 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5725-6325</t>
+          <t>4260-4380</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5150</v>
+        <v>4150</v>
       </c>
       <c r="F10" t="n">
-        <v>7100</v>
+        <v>4530</v>
       </c>
       <c r="G10" t="n">
-        <v>7900</v>
+        <v>4880</v>
       </c>
       <c r="H10" t="n">
-        <v>8950</v>
+        <v>4980</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18.51%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>44.1</v>
+        <v>1.29</v>
       </c>
       <c r="L10" t="n">
-        <v>-10343700</v>
+        <v>-46813700</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1362,7 +1361,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1370,40 +1369,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2510-2750</t>
+          <t>1805-1945</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2290</v>
+        <v>1675</v>
       </c>
       <c r="F11" t="n">
-        <v>3050</v>
+        <v>2140</v>
       </c>
       <c r="G11" t="n">
-        <v>3360</v>
+        <v>2350</v>
       </c>
       <c r="H11" t="n">
-        <v>3770</v>
+        <v>2580</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18.77%</t>
+          <t>12.85%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>19.71</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>709400</v>
+        <v>-9111700</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1413,44 +1412,44 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1815-1945</t>
+          <t>3230-3570</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1690</v>
+        <v>2890</v>
       </c>
       <c r="F12" t="n">
-        <v>2130</v>
+        <v>4070</v>
       </c>
       <c r="G12" t="n">
-        <v>2340</v>
+        <v>4480</v>
       </c>
       <c r="H12" t="n">
-        <v>2560</v>
+        <v>5250</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15.03%</t>
+          <t>24.37%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>13.23</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>3244900</v>
+        <v>1383900</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1464,7 +1463,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1472,36 +1471,36 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3250-3490</t>
+          <t>1680-1820</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3010</v>
+        <v>1540</v>
       </c>
       <c r="F13" t="n">
-        <v>3810</v>
+        <v>2020</v>
       </c>
       <c r="G13" t="n">
-        <v>4190</v>
+        <v>2230</v>
       </c>
       <c r="H13" t="n">
-        <v>4560</v>
+        <v>2490</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>21.58%</t>
+          <t>12.67%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>8199146885.76</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>8605000</v>
+        <v>9672200</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1515,48 +1514,48 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EMAS.JK</t>
+          <t>PSAB.JK</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7675-8175</t>
+          <t>530-580</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7200</v>
+        <v>494</v>
       </c>
       <c r="F14" t="n">
-        <v>8800</v>
+        <v>635</v>
       </c>
       <c r="G14" t="n">
-        <v>9675</v>
+        <v>695</v>
       </c>
       <c r="H14" t="n">
-        <v>10250</v>
+        <v>760</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>22.68%</t>
+          <t>-3.77%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>8618293137.690001</v>
+        <v>0.45</v>
       </c>
       <c r="L14" t="n">
-        <v>-43100</v>
+        <v>37104900</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1566,48 +1565,48 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>BRIS.JK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3440-3780</t>
+          <t>2060-2160</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3110</v>
+        <v>1980</v>
       </c>
       <c r="F15" t="n">
-        <v>4270</v>
+        <v>2270</v>
       </c>
       <c r="G15" t="n">
-        <v>4700</v>
+        <v>2500</v>
       </c>
       <c r="H15" t="n">
-        <v>5425</v>
+        <v>2530</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>28.05%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>264.71</v>
+        <v>1.75</v>
       </c>
       <c r="L15" t="n">
-        <v>232900</v>
+        <v>-835400</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1616,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1625,40 +1624,40 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3530-3610</t>
+          <t>2930-3190</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3450</v>
+        <v>2690</v>
       </c>
       <c r="F16" t="n">
-        <v>3700</v>
+        <v>3510</v>
       </c>
       <c r="G16" t="n">
-        <v>3920</v>
+        <v>3860</v>
       </c>
       <c r="H16" t="n">
-        <v>4070</v>
+        <v>4270</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>19.83%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2.73</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>-42911100</v>
+        <v>18794200</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>DISTRIB</t>
+          <t>ACCUM</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1667,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>UNTR.JK</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1676,36 +1675,36 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>197-236</t>
+          <t>28900-30050</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>161</v>
+        <v>27800</v>
       </c>
       <c r="F17" t="n">
-        <v>288</v>
+        <v>31625</v>
       </c>
       <c r="G17" t="n">
-        <v>340</v>
+        <v>34800</v>
       </c>
       <c r="H17" t="n">
-        <v>410</v>
+        <v>35350</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>59.25%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>13.53</v>
+        <v>0.96</v>
       </c>
       <c r="L17" t="n">
-        <v>248594500</v>
+        <v>58500</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1719,7 +1718,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>INKP.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1727,36 +1726,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3770-4010</t>
+          <t>8550-9400</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3550</v>
+        <v>7750</v>
       </c>
       <c r="F18" t="n">
-        <v>4280</v>
+        <v>10525</v>
       </c>
       <c r="G18" t="n">
-        <v>4710</v>
+        <v>11675</v>
       </c>
       <c r="H18" t="n">
-        <v>4920</v>
+        <v>13200</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13.51%</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>32.75</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>3334100</v>
+        <v>350400</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1770,7 +1769,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>MBMA.JK</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1778,40 +1777,40 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>104-110</t>
+          <t>650-720</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>98</v>
+        <v>580</v>
       </c>
       <c r="F19" t="n">
-        <v>112</v>
+        <v>815</v>
       </c>
       <c r="G19" t="n">
-        <v>115</v>
+        <v>905</v>
       </c>
       <c r="H19" t="n">
-        <v>123</v>
+        <v>1025</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>54.29%</t>
+          <t>13.43%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>20631296533.55</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
-        <v>204200</v>
+        <v>-45966700</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIB</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1820,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>ARCI.JK</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1829,36 +1828,36 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1190-1290</t>
+          <t>1625-1755</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1090</v>
+        <v>1500</v>
       </c>
       <c r="F20" t="n">
-        <v>1425</v>
+        <v>1920</v>
       </c>
       <c r="G20" t="n">
-        <v>1570</v>
+        <v>2120</v>
       </c>
       <c r="H20" t="n">
-        <v>1745</v>
+        <v>2310</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12.59%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>24.63</v>
+        <v>1.7</v>
       </c>
       <c r="L20" t="n">
-        <v>13420900</v>
+        <v>48995500</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1872,48 +1871,48 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UNTR.JK</t>
+          <t>DADA.JK</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29450-30525</t>
+          <t>50-53</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>28400</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>32000</v>
+        <v>52</v>
       </c>
       <c r="G21" t="n">
-        <v>35200</v>
+        <v>54</v>
       </c>
       <c r="H21" t="n">
-        <v>35500</v>
+        <v>56</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1078900</v>
+        <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1932,7 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1963,7 +1962,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-611078500</v>
+        <v>-1608064600</v>
       </c>
     </row>
     <row r="3">
@@ -1972,11 +1971,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>BUMI.JK</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>248594500</v>
+        <v>258923000</v>
       </c>
     </row>
     <row r="4">
@@ -1985,11 +1984,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BUMI.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>122986100</v>
+        <v>204694700</v>
       </c>
     </row>
     <row r="5">
@@ -1998,11 +1997,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>84990300</v>
+        <v>-105977600</v>
       </c>
     </row>
     <row r="6">
@@ -2011,11 +2010,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DEWA.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55692600</v>
+        <v>-76632500</v>
       </c>
     </row>
     <row r="7">
@@ -2024,11 +2023,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>BBCA.JK</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>44947300</v>
+        <v>-59129700</v>
       </c>
     </row>
     <row r="8">
@@ -2037,11 +2036,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>DEWA.JK</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-42911100</v>
+        <v>54591400</v>
       </c>
     </row>
     <row r="9">
@@ -2050,11 +2049,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>ARCI.JK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>39476500</v>
+        <v>48995500</v>
       </c>
     </row>
     <row r="10">
@@ -2063,11 +2062,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>36164200</v>
+        <v>-46813700</v>
       </c>
     </row>
     <row r="11">
@@ -2076,11 +2075,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>MBMA.JK</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-29395000</v>
+        <v>-45966700</v>
       </c>
     </row>
     <row r="12">
@@ -2089,11 +2088,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PNLF.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-20566600</v>
+        <v>45147600</v>
       </c>
     </row>
     <row r="13">
@@ -2102,11 +2101,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>LPKR.JK</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19724300</v>
+        <v>45092900</v>
       </c>
     </row>
     <row r="14">
@@ -2115,11 +2114,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>BULL.JK</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19314300</v>
+        <v>38602000</v>
       </c>
     </row>
     <row r="15">
@@ -2128,11 +2127,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BRIS.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16329800</v>
+        <v>37937900</v>
       </c>
     </row>
     <row r="16">
@@ -2141,11 +2140,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16104500</v>
+        <v>-37777000</v>
       </c>
     </row>
     <row r="17">
@@ -2154,11 +2153,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>PSAB.JK</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-14947200</v>
+        <v>37104900</v>
       </c>
     </row>
     <row r="18">
@@ -2167,11 +2166,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-14652300</v>
+        <v>33670200</v>
       </c>
     </row>
     <row r="19">
@@ -2180,11 +2179,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13801700</v>
+        <v>-32022700</v>
       </c>
     </row>
     <row r="20">
@@ -2193,11 +2192,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BBCA.JK</t>
+          <t>BKSL.JK</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13696800</v>
+        <v>28025900</v>
       </c>
     </row>
     <row r="21">
@@ -2206,11 +2205,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13420900</v>
+        <v>-23067200</v>
       </c>
     </row>
     <row r="22">
@@ -2219,11 +2218,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-11980700</v>
+        <v>22945100</v>
       </c>
     </row>
     <row r="23">
@@ -2232,11 +2231,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ARCI.JK</t>
+          <t>HUMI.JK</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10448100</v>
+        <v>21398900</v>
       </c>
     </row>
     <row r="24">
@@ -2245,11 +2244,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-10343700</v>
+        <v>20676500</v>
       </c>
     </row>
     <row r="25">
@@ -2258,11 +2257,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9794800</v>
+        <v>18794200</v>
       </c>
     </row>
     <row r="26">
@@ -2271,11 +2270,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9571200</v>
+        <v>18587000</v>
       </c>
     </row>
     <row r="27">
@@ -2284,11 +2283,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TRUE.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8930900</v>
+        <v>16337800</v>
       </c>
     </row>
     <row r="28">
@@ -2297,11 +2296,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8605000</v>
+        <v>15516700</v>
       </c>
     </row>
     <row r="29">
@@ -2310,11 +2309,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BKSL.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-8292700</v>
+        <v>14872000</v>
       </c>
     </row>
     <row r="30">
@@ -2323,11 +2322,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8212600</v>
+        <v>14626700</v>
       </c>
     </row>
     <row r="31">
@@ -2336,11 +2335,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>SUPA.JK</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7888400</v>
+        <v>14277100</v>
       </c>
     </row>
   </sheetData>
@@ -2354,7 +2353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2399,194 +2398,194 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-2.1%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PTBA.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>98</v>
       </c>
       <c r="C3" t="n">
-        <v>74.8</v>
+        <v>65.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-20.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>97</v>
       </c>
       <c r="C4" t="n">
-        <v>74.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-8.1%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>PTBA.JK</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>96</v>
       </c>
       <c r="C5" t="n">
-        <v>73</v>
+        <v>59.8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-2.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>95</v>
       </c>
       <c r="C6" t="n">
-        <v>67</v>
+        <v>59.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-5.1%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>61.6</v>
+        <v>57.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-29.5%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>92</v>
       </c>
       <c r="C9" t="n">
-        <v>59.6</v>
+        <v>57.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-12.6%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>91</v>
       </c>
       <c r="C10" t="n">
-        <v>58.4</v>
+        <v>54</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-6.7%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>90</v>
       </c>
       <c r="C11" t="n">
-        <v>58.2</v>
+        <v>52.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-17.8%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" t="n">
-        <v>52.8</v>
+        <v>52</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-19.8%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>MEDC.JK</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2597,1465 +2596,1411 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-12.3%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMAS.JK</t>
+          <t>PSAB.JK</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>46.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-15.3%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>BRIS.JK</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>45.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-13.9%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>84</v>
       </c>
       <c r="C16" t="n">
-        <v>50.6</v>
+        <v>45</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-22.3%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>UNTR.JK</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>83</v>
       </c>
       <c r="C17" t="n">
-        <v>49</v>
+        <v>44.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-7.8%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>INKP.JK</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>82</v>
       </c>
       <c r="C18" t="n">
-        <v>48.6</v>
+        <v>43</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-25.2%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>MBMA.JK</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>81</v>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-24.3%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>ARCI.JK</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>47.4</v>
+        <v>39.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-16.7%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UNTR.JK</t>
+          <t>DADA.JK</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C21" t="n">
-        <v>44.8</v>
+        <v>38.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-20.6%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INKP.JK</t>
+          <t>BBCA.JK</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C22" t="n">
-        <v>43</v>
+        <v>37.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-17.4%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MBMA.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C23" t="n">
-        <v>42</v>
+        <v>36.4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-18.2%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C24" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-38.7%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ARCI.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C25" t="n">
-        <v>39.6</v>
+        <v>31.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-23.5%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C26" t="n">
-        <v>39.6</v>
+        <v>31.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-36.4%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DADA.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C27" t="n">
-        <v>38.6</v>
+        <v>28</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-21.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C28" t="n">
-        <v>37.4</v>
+        <v>27</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-20.1%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HRUM.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>70</v>
       </c>
       <c r="C29" t="n">
-        <v>37</v>
+        <v>26.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-32.3%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>BBRI.JK</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C30" t="n">
-        <v>34</v>
+        <v>25.6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-12.3%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C31" t="n">
-        <v>33.4</v>
+        <v>24.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-27.2%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GOTO.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C32" t="n">
-        <v>26.8</v>
+        <v>19</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-14.4%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TPIA.JK</t>
+          <t>BBYB.JK</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C33" t="n">
-        <v>24.6</v>
+        <v>17.4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-53.2%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BRIS.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C34" t="n">
-        <v>20.8</v>
+        <v>16.8</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-24.9%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C35" t="n">
-        <v>18.2</v>
+        <v>16.6</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-50.3%</t>
+          <t>-21.1%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DSSA.JK</t>
+          <t>EMTK.JK</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C36" t="n">
-        <v>17.4</v>
+        <v>16.2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-51.7%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BBYB.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C37" t="n">
-        <v>17.4</v>
+        <v>15.4</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-48.5%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C38" t="n">
-        <v>16.8</v>
+        <v>15</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-40.3%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EMTK.JK</t>
+          <t>JPFA.JK</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C39" t="n">
-        <v>16.2</v>
+        <v>13.2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-50.7%</t>
+          <t>-25.3%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ICBP.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C40" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-17.0%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C41" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-49.1%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>NICL.JK</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C42" t="n">
-        <v>13.2</v>
+        <v>10.8</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-55.1%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C43" t="n">
-        <v>12.8</v>
+        <v>10</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-59.1%</t>
+          <t>-29.8%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-65.7%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EXCL.JK</t>
+          <t>TPIA.JK</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>53</v>
       </c>
       <c r="C45" t="n">
-        <v>11.8</v>
+        <v>9.6</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>-29.7%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PSAB.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C46" t="n">
-        <v>11.8</v>
+        <v>8.4</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-43.8%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NICL.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47" t="n">
-        <v>10.8</v>
+        <v>7.8</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-63.1%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RATU.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>50</v>
       </c>
       <c r="C48" t="n">
-        <v>10.4</v>
+        <v>7.8</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-55.9%</t>
+          <t>-51.4%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>COIN.JK</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>50</v>
       </c>
       <c r="C49" t="n">
-        <v>10.4</v>
+        <v>7.8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-72.7%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>PBSA.JK</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-55.2%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C51" t="n">
-        <v>8.4</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-42.5%</t>
+          <t>-54.8%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BBCA.JK</t>
+          <t>AMMN.JK</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C52" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-44.7%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>LPKR.JK</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C53" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-50.6%</t>
+          <t>-43.0%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>COIN.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C54" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-26.9%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PBSA.JK</t>
+          <t>IRSX.JK</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C55" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-54.1%</t>
+          <t>-47.5%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>PNLF.JK</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C56" t="n">
-        <v>7.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-51.4%</t>
+          <t>-30.5%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>CPRO.JK</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>40</v>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-38.4%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C58" t="n">
-        <v>6.6</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-61.3%</t>
+          <t>-58.0%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C59" t="n">
-        <v>6.6</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-44.7%</t>
+          <t>-71.0%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C60" t="n">
-        <v>6.6</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-55.7%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PNLF.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-57.3%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CPRO.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-54.6%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C63" t="n">
         <v>5.399999999999999</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-39.0%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>SUPA.JK</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C64" t="n">
-        <v>5.399999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-56.8%</t>
+          <t>-32.9%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>WIFI.JK</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C65" t="n">
-        <v>5.399999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-69.1%</t>
+          <t>-43.6%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>GTSI.JK</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C66" t="n">
-        <v>5.399999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-56.5%</t>
+          <t>-60.6%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C67" t="n">
-        <v>5.399999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-55.7%</t>
+          <t>-33.0%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>AMRT.JK</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C68" t="n">
-        <v>5.399999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-29.0%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>WIFI.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C69" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-42.0%</t>
+          <t>-20.9%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GTSI.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C70" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-55.0%</t>
+          <t>-50.2%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C71" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-67.0%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AMRT.JK</t>
+          <t>DSSA.JK</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C72" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-46.9%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LPKR.JK</t>
+          <t>GOTO.JK</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C73" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-24.6%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>BULL.JK</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-53.0%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>EXCL.JK</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-43.0%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-54.3%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-75.2%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>DEWA.JK</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C78" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>-51.7%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BULL.JK</t>
+          <t>BUMI.JK</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C79" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-56.0%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DEWA.JK</t>
+          <t>RMKE.JK</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-66.9%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BUMI.JK</t>
+          <t>ICBP.JK</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-53.0%</t>
+          <t>-17.5%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>BBKP.JK</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-53.5%</t>
+          <t>-36.2%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SUPA.JK</t>
+          <t>BKSL.JK</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-43.0%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>RMKE.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-65.4%</t>
+          <t>-56.2%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BBKP.JK</t>
+          <t>VKTR.JK</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-48.3%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TRUE.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-40.8%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BKSL.JK</t>
+          <t>TOBA.JK</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>8</v>
       </c>
       <c r="C87" t="n">
-        <v>-1.2</v>
+        <v>-3</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-45.8%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AMMN.JK</t>
+          <t>HRUM.JK</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C88" t="n">
         <v>-3</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-24.5%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VKTR.JK</t>
+          <t>HUMI.JK</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C89" t="n">
         <v>-3</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-43.6%</t>
+          <t>-55.1%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TOBA.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C90" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-37.0%</t>
+          <t>-52.3%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HUMI.JK</t>
+          <t>SSIA.JK</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C91" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-46.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>TRIN.JK</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>7</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-3</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>-67.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>OASA.JK</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>2</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-6</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>-48.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>SSIA.JK</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>2</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-6</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>-36.9%</t>
+          <t>-37.2%</t>
         </is>
       </c>
     </row>
@@ -4138,17 +4083,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9875-10475</t>
+          <t>10050-10650</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19.3M</t>
+          <t>15.5M</t>
         </is>
       </c>
     </row>
@@ -4163,21 +4108,21 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2860-2960</t>
+          <t>2870-2970</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>16.1M</t>
+          <t>14.2M</t>
         </is>
       </c>
     </row>
@@ -4192,21 +4137,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2440-2500</t>
+          <t>2380-2500</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>85.0M</t>
+          <t>4.8M</t>
         </is>
       </c>
     </row>
@@ -4217,25 +4162,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1660-1800</t>
+          <t>665-745</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>975</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>44.9M</t>
+          <t>20.7M</t>
         </is>
       </c>
     </row>
@@ -4246,32 +4191,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1345-1585</t>
+          <t>3230-3570</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.0M</t>
+          <t>1.4M</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4279,25 +4224,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>HRTA.JK</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>725-785</t>
+          <t>2480-2720</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.5M</t>
+          <t>989600</t>
         </is>
       </c>
     </row>
@@ -4308,25 +4253,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5725-6325</t>
+          <t>224-256</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>344</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-10.3M</t>
+          <t>2.4M</t>
         </is>
       </c>
     </row>
@@ -4337,25 +4282,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1815-1945</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-76.6M</t>
         </is>
       </c>
     </row>
@@ -4366,25 +4311,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3250-3490</t>
+          <t>212-256</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>370</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.6M</t>
+          <t>22.9M</t>
         </is>
       </c>
     </row>
@@ -4395,25 +4340,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EMAS.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7675-8175</t>
+          <t>865-1035</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-43100</t>
+          <t>18.6M</t>
         </is>
       </c>
     </row>
@@ -4432,21 +4377,21 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11275-11825</t>
+          <t>11050-11650</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>381000</t>
+          <t>300600</t>
         </is>
       </c>
     </row>
@@ -4461,21 +4406,21 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>197-236</t>
+          <t>178-212</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>308</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>248.6M</t>
+          <t>204.7M</t>
         </is>
       </c>
     </row>
@@ -4490,21 +4435,21 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1180-1290</t>
+          <t>1150-1260</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>146200</t>
+          <t>-111600</t>
         </is>
       </c>
     </row>
@@ -4519,11 +4464,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1670-1850</t>
+          <t>1710-1880</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4533,7 +4478,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-760900</t>
+          <t>-1.7M</t>
         </is>
       </c>
     </row>
@@ -4548,28 +4493,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>197-236</t>
+          <t>171-208</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>308</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.4M</t>
+          <t>12.1M</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -4577,25 +4522,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HRTA.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2510-2750</t>
+          <t>715-775</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>940</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>709400</t>
+          <t>16.3M</t>
         </is>
       </c>
     </row>
@@ -4606,25 +4551,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>ADMR.JK</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>104-110</t>
+          <t>1805-1945</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>204200</t>
+          <t>-9.1M</t>
         </is>
       </c>
     </row>
@@ -4635,25 +4580,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>PSAB.JK</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>232-268</t>
+          <t>530-580</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>695</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-47000</t>
+          <t>37.1M</t>
         </is>
       </c>
     </row>
@@ -4664,25 +4609,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>236-284</t>
+          <t>2930-3190</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-14.7M</t>
+          <t>18.8M</t>
         </is>
       </c>
     </row>
@@ -4693,25 +4638,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>UNTR.JK</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>925-1095</t>
+          <t>28900-30050</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>34800</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-4.1M</t>
+          <t>58500</t>
         </is>
       </c>
     </row>
@@ -4726,25 +4671,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>BMRI.JK</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3530-3610</t>
+          <t>4620-4780</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-42.9M</t>
+          <t>-23.1M</t>
         </is>
       </c>
     </row>
@@ -4755,25 +4700,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4880-5050</t>
+          <t>4260-4380</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>39.5M</t>
+          <t>-46.8M</t>
         </is>
       </c>
     </row>
@@ -4784,25 +4729,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>BRIS.JK</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4220-4340</t>
+          <t>2060-2160</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-29.4M</t>
+          <t>-835400</t>
         </is>
       </c>
     </row>
@@ -4813,25 +4758,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BRIS.JK</t>
+          <t>BBCA.JK</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2160-2260</t>
+          <t>6650-6850</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>-59.1M</t>
         </is>
       </c>
     </row>
@@ -4842,32 +4787,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>89-109</t>
+          <t>1560-1650</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-6.0M</t>
+          <t>-1.4M</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -4875,25 +4820,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>DADA.JK</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1975-2110</t>
+          <t>50-53</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>7.9M</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4904,25 +4849,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3310-3690</t>
+          <t>326-338</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>380</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.5M</t>
+          <t>5.7M</t>
         </is>
       </c>
     </row>
@@ -4933,25 +4878,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>780-850</t>
+          <t>7425-7925</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5.8M</t>
+          <t>697200</t>
         </is>
       </c>
     </row>
@@ -4962,25 +4907,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6325-6825</t>
+          <t>165-180</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-483200</t>
+          <t>1.9M</t>
         </is>
       </c>
     </row>
@@ -4991,32 +4936,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>970-1010</t>
+          <t>4480-4780</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.4M</t>
+          <t>-60400</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -5024,25 +4969,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DADA.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>50-53</t>
+          <t>1955-2090</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.5M</t>
         </is>
       </c>
     </row>
@@ -5053,25 +4998,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>334-346</t>
+          <t>2880-3040</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>-4.5M</t>
         </is>
       </c>
     </row>
@@ -5082,25 +5027,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PANI.JK</t>
+          <t>EMTK.JK</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>7625-8125</t>
+          <t>685-735</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>880</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>380000</t>
+          <t>3.1M</t>
         </is>
       </c>
     </row>
@@ -5111,25 +5056,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>167-183</t>
+          <t>232-264</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>346</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-3.8M</t>
+          <t>45.1M</t>
         </is>
       </c>
     </row>
@@ -5140,32 +5085,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>EXCL.JK</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4670-4970</t>
+          <t>2460-2660</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-67500</t>
+          <t>160700</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -5173,25 +5118,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2070-2210</t>
+          <t>1870-2000</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9.6M</t>
+          <t>11.2M</t>
         </is>
       </c>
     </row>
@@ -5202,25 +5147,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2950-3090</t>
+          <t>930-970</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19.7M</t>
+          <t>4.3M</t>
         </is>
       </c>
     </row>
@@ -5231,25 +5176,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EMTK.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>700-750</t>
+          <t>3210-3590</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-5.4M</t>
+          <t>5.0M</t>
         </is>
       </c>
     </row>
@@ -5260,25 +5205,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EXCL.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2720-2920</t>
+          <t>750-820</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>750400</t>
+          <t>12.0M</t>
         </is>
       </c>
     </row>
@@ -5289,32 +5234,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>248-280</t>
+          <t>5725-6225</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-2.6M</t>
+          <t>249600</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -5322,25 +5267,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GOTO.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>54-58</t>
+          <t>950-990</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-611.1M</t>
+          <t>-1.5M</t>
         </is>
       </c>
     </row>
@@ -5351,44 +5296,48 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>LPKR.JK</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>404-464</t>
+          <t>69-77</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>96</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>380600</t>
+          <t>45.1M</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WIFI.JK</t>
+          <t>JPFA.JK</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2010-2190</t>
+          <t>2120-2260</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5398,251 +5347,247 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-5.8M</t>
+          <t>1.4M</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Consumer Defensive</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ICBP.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7450-7700</t>
+          <t>5875-6075</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2.1M</t>
+          <t>-660200</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>CPRO.JK</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2210-2350</t>
+          <t>51-55</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.5M</t>
+          <t>11.0M</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CPRO.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>53-57</t>
+          <t>1800-1910</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-4.4M</t>
+          <t>377900</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>AMRT.JK</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1835-1945</t>
+          <t>1380-1460</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-14.9M</t>
+          <t>437000</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
       <c r="B49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AMRT.JK</t>
+          <t>IRSX.JK</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1410-1490</t>
+          <t>378-446</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>590</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>5.7M</t>
+          <t>11.1M</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>WIFI.JK</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>31</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1905-2090</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-396600</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>GOTO.JK</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>21</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>50-54</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-1.6B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B52" t="n">
         <v>1</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>RLCO.JK</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>54</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>5475-6225</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>8050</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2.7M</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>KLBF.JK</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>39</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>980-1020</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1175</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>9.8M</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="n">
-        <v>2</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>LPKR.JK</t>
-        </is>
-      </c>
       <c r="D52" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>82-90</t>
+          <t>4810-5500</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>7475</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>167800</t>
+          <t>2.8M</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5607,7 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -5698,7 +5643,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-611078500</v>
+        <v>-1608064600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5712,11 +5657,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>BUMI.JK</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>248594500</v>
+        <v>258923000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5730,11 +5675,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BUMI.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>122986100</v>
+        <v>204694700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -5748,11 +5693,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>84990300</v>
+        <v>-105977600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5766,11 +5711,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DEWA.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55692600</v>
+        <v>-76632500</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -5784,11 +5729,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MEDC.JK</t>
+          <t>BBCA.JK</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>44947300</v>
+        <v>-59129700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -5802,11 +5747,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BBRI.JK</t>
+          <t>DEWA.JK</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-42911100</v>
+        <v>54591400</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -5820,11 +5765,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>ARCI.JK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>39476500</v>
+        <v>48995500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5838,11 +5783,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>36164200</v>
+        <v>-46813700</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5856,11 +5801,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BBNI.JK</t>
+          <t>MBMA.JK</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-29395000</v>
+        <v>-45966700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5889,64 +5834,64 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>FundScore</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>RevenueGrowth</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Margin</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>PBV</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>DER</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
@@ -5969,26 +5914,26 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E2" s="8" t="n">
         <v>0.19143999</v>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="F2" s="9" t="n">
         <v>0.128</v>
       </c>
-      <c r="G2" s="9" t="n">
+      <c r="G2" s="8" t="n">
         <v>0.38872</v>
       </c>
-      <c r="H2" s="11" t="n">
-        <v>8.223221000000001</v>
-      </c>
-      <c r="I2" s="12" t="n">
-        <v>1.5745171</v>
-      </c>
-      <c r="J2" s="12" t="n">
+      <c r="H2" s="10" t="n">
+        <v>7.7911315</v>
+      </c>
+      <c r="I2" s="11" t="n">
+        <v>1.491982</v>
+      </c>
+      <c r="J2" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="12" t="n">
-        <v>603.17</v>
+      <c r="K2" s="11" t="n">
+        <v>603.25</v>
       </c>
     </row>
     <row r="3">
@@ -6008,65 +5953,65 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="E3" s="10" t="n">
+      <c r="E3" s="9" t="n">
         <v>0.12336001</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" s="8" t="n">
         <v>0.749</v>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="G3" s="8" t="n">
         <v>0.34335998</v>
       </c>
-      <c r="H3" s="11" t="n">
-        <v>8.002222</v>
-      </c>
-      <c r="I3" s="12" t="n">
-        <v>0.93011236</v>
-      </c>
-      <c r="J3" s="12" t="n">
+      <c r="H3" s="10" t="n">
+        <v>7.664538</v>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>0.8913576600000001</v>
+      </c>
+      <c r="J3" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K3" s="12" t="n">
-        <v>35.99</v>
+      <c r="K3" s="11" t="n">
+        <v>36.01</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>EMTK.JK</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="13" t="n">
         <v>0.20097</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="13" t="n">
         <v>0.466</v>
       </c>
-      <c r="G4" s="14" t="n">
+      <c r="G4" s="13" t="n">
         <v>0.43205002</v>
       </c>
-      <c r="H4" s="13" t="n">
-        <v>5.926592</v>
-      </c>
-      <c r="I4" s="12" t="n">
-        <v>1.13257</v>
-      </c>
-      <c r="J4" s="15" t="n">
+      <c r="H4" s="12" t="n">
+        <v>5.804447</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>1.1091375</v>
+      </c>
+      <c r="J4" s="14" t="n">
         <v>2.444</v>
       </c>
-      <c r="K4" s="12" t="n">
-        <v>122.33</v>
+      <c r="K4" s="11" t="n">
+        <v>122.32</v>
       </c>
     </row>
     <row r="5">
@@ -6086,26 +6031,26 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="9" t="n">
         <v>0.17465</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>0.17</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>0.40405998</v>
       </c>
-      <c r="H5" s="11" t="n">
-        <v>9.497207</v>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>1.6592195</v>
-      </c>
-      <c r="J5" s="12" t="n">
+      <c r="H5" s="10" t="n">
+        <v>9.257288000000001</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>1.6173905</v>
+      </c>
+      <c r="J5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="12" t="n">
-        <v>375.9</v>
+      <c r="K5" s="11" t="n">
+        <v>375.92</v>
       </c>
     </row>
     <row r="6">
@@ -6125,104 +6070,104 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>0.25308</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="9" t="n">
         <v>0.097</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="8" t="n">
         <v>0.27552</v>
       </c>
-      <c r="H6" s="11" t="n">
-        <v>9.789216</v>
-      </c>
-      <c r="I6" s="16" t="n">
-        <v>2.1865363</v>
-      </c>
-      <c r="J6" s="15" t="n">
+      <c r="H6" s="10" t="n">
+        <v>8.881346000000001</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>1.9837526</v>
+      </c>
+      <c r="J6" s="14" t="n">
         <v>23.671</v>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" s="11" t="n">
         <v>126.67</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PADI.JK</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>JPFA.JK</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n">
-        <v>0.24911</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>4.381</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>0.71615</v>
-      </c>
-      <c r="H7" t="n">
-        <v>25.916231</v>
-      </c>
-      <c r="I7" s="15" t="n">
-        <v>6.1913695</v>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>5.093</v>
-      </c>
-      <c r="K7" s="12" t="n">
-        <v>3.82</v>
+      <c r="E7" s="13" t="n">
+        <v>0.23401</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0.06594999999999999</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>6.365724</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>1.3643874</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>59.254</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>344.03</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>JPFA.JK</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AADI.JK</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E8" s="14" t="n">
-        <v>0.23401</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="G8" s="14" t="n">
-        <v>0.06594999999999999</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>6.626944</v>
-      </c>
-      <c r="I8" s="12" t="n">
-        <v>1.4204581</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>59.254</v>
-      </c>
-      <c r="K8" s="12" t="n">
-        <v>344.05</v>
+      <c r="E8" s="8" t="n">
+        <v>0.24216999</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>0.15481</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>6.5934486</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>24182.242</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>22.636</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <v>1569.74</v>
       </c>
     </row>
     <row r="9">
@@ -6231,7 +6176,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>ESSA.JK</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6243,25 +6188,25 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.24216999</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>0.15481</v>
-      </c>
-      <c r="H9" s="11" t="n">
-        <v>6.4815526</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>23773.365</v>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>22.636</v>
-      </c>
-      <c r="K9" s="12" t="n">
-        <v>1569.84</v>
+        <v>0.096820004</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>0.13656999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>18.841679</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>28653.846</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>39.54</v>
       </c>
     </row>
     <row r="10">
@@ -6270,7 +6215,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ESSA.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6281,26 +6226,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E10" s="10" t="n">
-        <v>0.096820004</v>
+      <c r="E10" s="9" t="n">
+        <v>0.15277</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>0.13656999</v>
-      </c>
-      <c r="H10" t="n">
-        <v>23.352922</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>29038.46</v>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="K10" s="12" t="n">
-        <v>32.33</v>
+        <v>0.091</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>0.09748999999999999</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>11.826697</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>1.7936726</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>138.994</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>170.8</v>
       </c>
     </row>
     <row r="11">
@@ -6320,26 +6265,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="9" t="n">
         <v>0.15604</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="9" t="n">
         <v>0.075</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="8" t="n">
         <v>0.31919</v>
       </c>
       <c r="H11" t="n">
-        <v>13.477254</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>1.9622712</v>
-      </c>
-      <c r="J11" s="12" t="n">
+        <v>12.865069</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>1.8734807</v>
+      </c>
+      <c r="J11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="12" t="n">
-        <v>163.98</v>
+      <c r="K11" s="11" t="n">
+        <v>164.01</v>
       </c>
     </row>
     <row r="12">
@@ -6359,65 +6304,65 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <v>0.65794</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="15" t="n">
         <v>-0.261</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="8" t="n">
         <v>0.27632</v>
       </c>
       <c r="H12" t="n">
-        <v>17.91975</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>11.77977</v>
-      </c>
-      <c r="J12" s="12" t="n">
+        <v>16.37427</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>10.755442</v>
+      </c>
+      <c r="J12" s="11" t="n">
         <v>0.378</v>
       </c>
-      <c r="K12" s="12" t="n">
-        <v>51.34</v>
+      <c r="K12" s="11" t="n">
+        <v>51.3</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="n">
+      <c r="A13" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>HRTA.JK</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="13" t="n">
         <v>0.28483</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="13" t="n">
         <v>1.009</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="13" t="n">
         <v>0.023759998</v>
       </c>
-      <c r="H13" s="13" t="n">
-        <v>16.919712</v>
+      <c r="H13" s="12" t="n">
+        <v>16.73317</v>
       </c>
       <c r="I13" s="16" t="n">
-        <v>4.2964234</v>
-      </c>
-      <c r="J13" s="15" t="n">
+        <v>4.247415</v>
+      </c>
+      <c r="J13" s="14" t="n">
         <v>139.825</v>
       </c>
-      <c r="K13" s="12" t="n">
-        <v>155.44</v>
+      <c r="K13" s="11" t="n">
+        <v>155.38</v>
       </c>
     </row>
     <row r="14">
@@ -6437,25 +6382,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="9" t="n">
         <v>0.14062001</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="9" t="n">
         <v>0.075</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="9" t="n">
         <v>0.04955</v>
       </c>
-      <c r="H14" s="11" t="n">
-        <v>7.889442</v>
-      </c>
-      <c r="I14" s="12" t="n">
-        <v>1.0234951</v>
-      </c>
-      <c r="J14" s="15" t="n">
+      <c r="H14" s="10" t="n">
+        <v>7.4658475</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>0.9685423</v>
+      </c>
+      <c r="J14" s="14" t="n">
         <v>12.229</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="K14" s="11" t="n">
         <v>94.43000000000001</v>
       </c>
     </row>
@@ -6476,104 +6421,104 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>0.28336</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <v>0.879</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="8" t="n">
         <v>0.21154</v>
       </c>
       <c r="H15" t="n">
-        <v>28.97668</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>118928.57</v>
-      </c>
-      <c r="J15" s="15" t="n">
+        <v>29.411766</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>120714.28</v>
+      </c>
+      <c r="J15" s="14" t="n">
         <v>118.6</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="K15" s="11" t="n">
         <v>57.46</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="n">
+      <c r="A16" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>BRPT.JK</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>3.509</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>0.09752</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>11.348162</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>52083.332</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>107.818</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>110.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>TPIA.JK</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C17" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E17" s="13" t="n">
         <v>0.42018002</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F17" s="13" t="n">
         <v>4.295</v>
       </c>
-      <c r="G16" s="14" t="n">
+      <c r="G17" s="13" t="n">
         <v>0.2208</v>
       </c>
-      <c r="H16" s="13" t="n">
-        <v>18.785324</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>127777.77</v>
-      </c>
-      <c r="J16" s="15" t="n">
+      <c r="H17" s="12" t="n">
+        <v>16.843826</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>114444.44</v>
+      </c>
+      <c r="J17" s="14" t="n">
         <v>82.7</v>
       </c>
-      <c r="K16" s="12" t="n">
-        <v>306.09</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>BBNI.JK</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>15</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0.1173</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>0.40232</v>
-      </c>
-      <c r="H17" s="11" t="n">
-        <v>7.9685726</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>0.92854464</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>537.11</v>
+      <c r="K17" s="11" t="n">
+        <v>305.75</v>
       </c>
     </row>
     <row r="18">
@@ -6582,7 +6527,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>BBNI.JK</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -6593,26 +6538,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E18" s="10" t="n">
-        <v>0.102419995</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>0.30543</v>
-      </c>
-      <c r="H18" s="11" t="n">
-        <v>7.6559334</v>
-      </c>
-      <c r="I18" s="12" t="n">
-        <v>0.7498203</v>
-      </c>
-      <c r="J18" s="15" t="n">
-        <v>21.136</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>44.41</v>
+      <c r="E18" s="9" t="n">
+        <v>0.1173</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>8.041548000000001</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>0.9372226</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>537.21</v>
       </c>
     </row>
     <row r="19">
@@ -6621,37 +6566,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E19" s="10" t="n">
-        <v>0.02158</v>
+      <c r="E19" s="9" t="n">
+        <v>0.102419995</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>0.06239</v>
-      </c>
-      <c r="H19" s="18" t="n">
-        <v>60.11174</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>23084.291</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>100.23</v>
+        <v>0.144</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>7.474111</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>0.73217744</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>21.136</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>44.42</v>
       </c>
     </row>
     <row r="20">
@@ -6660,7 +6605,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -6671,26 +6616,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E20" s="10" t="n">
-        <v>0.15277</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="G20" s="10" t="n">
-        <v>0.09748999999999999</v>
-      </c>
-      <c r="H20" t="n">
-        <v>12.519746</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>1.9002273</v>
-      </c>
-      <c r="J20" s="15" t="n">
-        <v>138.994</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>170.93</v>
+      <c r="E20" s="9" t="n">
+        <v>0.02158</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>0.06239</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>53.196777</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>20498.084</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>100.57</v>
       </c>
     </row>
     <row r="21">
@@ -6710,26 +6655,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" s="9" t="n">
         <v>0.07034</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="8" t="n">
         <v>0.647</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>0.26583</v>
       </c>
-      <c r="H21" s="18" t="n">
-        <v>143.8619</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>5.253958</v>
+      <c r="H21" s="17" t="n">
+        <v>139.46939</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>5.120524</v>
       </c>
       <c r="J21" s="16" t="n">
         <v>1.864</v>
       </c>
-      <c r="K21" s="12" t="n">
-        <v>54.74</v>
+      <c r="K21" s="11" t="n">
+        <v>55.03</v>
       </c>
     </row>
     <row r="22">
@@ -6738,7 +6683,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>BBCA.JK</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -6749,26 +6694,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E22" s="17" t="n">
-        <v>-0.04084</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="G22" s="10" t="n">
-        <v>-0.69613</v>
+      <c r="E22" s="8" t="n">
+        <v>0.21143</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>0.53282</v>
       </c>
       <c r="H22" t="n">
+        <v>14.459845</v>
+      </c>
+      <c r="I22" s="16" t="n">
+        <v>2.950042</v>
+      </c>
+      <c r="J22" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="15" t="n">
-        <v>10.171745</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="K22" s="16" t="n">
-        <v>-0.71</v>
+      <c r="K22" s="11" t="n">
+        <v>466.81</v>
       </c>
     </row>
     <row r="23">
@@ -6777,7 +6722,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BBCA.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -6788,26 +6733,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E23" s="9" t="n">
-        <v>0.21143</v>
-      </c>
-      <c r="F23" s="17" t="n">
-        <v>-0.027</v>
+      <c r="E23" s="15" t="n">
+        <v>-0.04084</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0.368</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.53282</v>
+        <v>-0.69613</v>
       </c>
       <c r="H23" t="n">
-        <v>14.780541</v>
-      </c>
-      <c r="I23" s="16" t="n">
-        <v>3.0155985</v>
-      </c>
-      <c r="J23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="12" t="n">
-        <v>466.83</v>
+      <c r="I23" s="14" t="n">
+        <v>9.154572</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="K23" s="16" t="n">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="24">
@@ -6827,25 +6772,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="9" t="n">
         <v>0.1093</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>0.221</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="G24" s="9" t="n">
         <v>0.08218</v>
       </c>
-      <c r="H24" s="11" t="n">
-        <v>8.515815999999999</v>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>0.5810516999999999</v>
-      </c>
-      <c r="J24" s="15" t="n">
+      <c r="H24" s="10" t="n">
+        <v>8.36983</v>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>0.5710908</v>
+      </c>
+      <c r="J24" s="14" t="n">
         <v>56.561</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="K24" s="11" t="n">
         <v>20.55</v>
       </c>
     </row>
@@ -6866,26 +6811,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="8" t="n">
         <v>8.94</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="8" t="n">
         <v>0.30952</v>
       </c>
-      <c r="H25" s="18" t="n">
-        <v>194.57735</v>
-      </c>
-      <c r="I25" s="15" t="n">
-        <v>9.893924999999999</v>
-      </c>
-      <c r="J25" s="12" t="n">
+      <c r="H25" s="17" t="n">
+        <v>183.95462</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>9.204594</v>
+      </c>
+      <c r="J25" s="11" t="n">
         <v>0.261</v>
       </c>
-      <c r="K25" s="12" t="n">
-        <v>6.27</v>
+      <c r="K25" s="11" t="n">
+        <v>6.17</v>
       </c>
     </row>
     <row r="26">
@@ -6905,26 +6850,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>0.31697</v>
       </c>
-      <c r="F26" s="17" t="n">
+      <c r="F26" s="15" t="n">
         <v>-0.192</v>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="G26" s="9" t="n">
         <v>0.15842</v>
       </c>
       <c r="H26" t="n">
-        <v>15.937541</v>
+        <v>15.562444</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>4.828028</v>
+        <v>4.710748</v>
       </c>
       <c r="J26" s="16" t="n">
         <v>1.461</v>
       </c>
-      <c r="K26" s="12" t="n">
-        <v>77.48999999999999</v>
+      <c r="K26" s="11" t="n">
+        <v>77.43000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -6944,26 +6889,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>0.33183</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="8" t="n">
         <v>0.415</v>
       </c>
-      <c r="G27" s="10" t="n">
+      <c r="G27" s="9" t="n">
         <v>0.13921</v>
       </c>
-      <c r="H27" s="18" t="n">
-        <v>59.277107</v>
-      </c>
-      <c r="I27" s="15" t="n">
-        <v>410000</v>
-      </c>
-      <c r="J27" s="15" t="n">
+      <c r="H27" s="17" t="n">
+        <v>52.66955</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>365000</v>
+      </c>
+      <c r="J27" s="14" t="n">
         <v>201.586</v>
       </c>
-      <c r="K27" s="12" t="n">
-        <v>20.75</v>
+      <c r="K27" s="11" t="n">
+        <v>20.79</v>
       </c>
     </row>
     <row r="28">
@@ -6983,26 +6928,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E28" s="10" t="n">
+      <c r="E28" s="9" t="n">
         <v>0.12380999</v>
       </c>
-      <c r="F28" s="17" t="n">
+      <c r="F28" s="15" t="n">
         <v>-0.075</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G28" s="9" t="n">
         <v>0.18375</v>
       </c>
       <c r="H28" t="n">
-        <v>24.170929</v>
-      </c>
-      <c r="I28" s="15" t="n">
-        <v>43088.234</v>
-      </c>
-      <c r="J28" s="15" t="n">
+        <v>23.09088</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>41176.47</v>
+      </c>
+      <c r="J28" s="14" t="n">
         <v>51.917</v>
       </c>
-      <c r="K28" s="12" t="n">
-        <v>60.61</v>
+      <c r="K28" s="11" t="n">
+        <v>60.63</v>
       </c>
     </row>
     <row r="29">
@@ -7011,7 +6956,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PGAS.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -7022,65 +6967,65 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E29" s="10" t="n">
-        <v>0.12082</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="G29" s="10" t="n">
-        <v>0.0806</v>
-      </c>
-      <c r="H29" s="11" t="n">
-        <v>9.358656999999999</v>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v>17894.736</v>
-      </c>
-      <c r="J29" s="15" t="n">
-        <v>32.802</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>217.98</v>
+      <c r="E29" s="9" t="n">
+        <v>0.14554</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>0.10163</v>
+      </c>
+      <c r="H29" t="n">
+        <v>12.65988</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>1.9131583</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>76.62</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="n">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>BRPT.JK</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LPKR.JK</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>11</v>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="E30" s="14" t="n">
-        <v>0.35876</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>3.509</v>
-      </c>
-      <c r="G30" s="14" t="n">
-        <v>0.09752</v>
-      </c>
-      <c r="H30" s="13" t="n">
-        <v>13.015873</v>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v>59791.668</v>
-      </c>
-      <c r="J30" s="15" t="n">
-        <v>107.818</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>110.25</v>
+      <c r="E30" s="9" t="n">
+        <v>0.01847</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>0.05309</v>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>11.02719</v>
+      </c>
+      <c r="I30" s="11" t="n">
+        <v>0.17173682</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>31.043</v>
+      </c>
+      <c r="K30" s="11" t="n">
+        <v>6.62</v>
       </c>
     </row>
     <row r="31">
@@ -7089,7 +7034,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IRSX.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -7100,26 +7045,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E31" s="10" t="n">
-        <v>0.11936</v>
-      </c>
-      <c r="F31" s="17" t="n">
-        <v>-0.5590000000000001</v>
-      </c>
-      <c r="G31" s="10" t="n">
-        <v>0.06455</v>
-      </c>
-      <c r="H31" s="18" t="n">
-        <v>60.445683</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>8.994819</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>7.18</v>
+      <c r="E31" s="9" t="n">
+        <v>0.06791</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="H31" t="n">
+        <v>18.119398</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>19387.756</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>36.805</v>
+      </c>
+      <c r="K31" s="11" t="n">
+        <v>52.43</v>
       </c>
     </row>
     <row r="32">
@@ -7128,7 +7073,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>IRSX.JK</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -7139,26 +7084,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E32" s="10" t="n">
-        <v>0.14554</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="G32" s="10" t="n">
-        <v>0.10163</v>
-      </c>
-      <c r="H32" t="n">
-        <v>13.054831</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>1.9723282</v>
-      </c>
-      <c r="J32" s="15" t="n">
-        <v>2.102</v>
-      </c>
-      <c r="K32" s="12" t="n">
-        <v>76.59999999999999</v>
+      <c r="E32" s="9" t="n">
+        <v>0.11936</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <v>-0.5590000000000001</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>0.06455</v>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>60.946743</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>8.53886</v>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="K32" s="11" t="n">
+        <v>6.76</v>
       </c>
     </row>
     <row r="33">
@@ -7178,26 +7123,26 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E33" s="10" t="n">
+      <c r="E33" s="9" t="n">
         <v>0.05041</v>
       </c>
-      <c r="F33" s="17" t="n">
+      <c r="F33" s="15" t="n">
         <v>-0.07199999999999999</v>
       </c>
-      <c r="G33" s="10" t="n">
+      <c r="G33" s="9" t="n">
         <v>0.15737</v>
       </c>
-      <c r="H33" s="11" t="n">
-        <v>4.6213593</v>
-      </c>
-      <c r="I33" s="12" t="n">
-        <v>0.24470064</v>
-      </c>
-      <c r="J33" s="12" t="n">
+      <c r="H33" s="10" t="n">
+        <v>4.5066047</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>0.23853171</v>
+      </c>
+      <c r="J33" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="12" t="n">
-        <v>51.5</v>
+      <c r="K33" s="11" t="n">
+        <v>51.48</v>
       </c>
     </row>
     <row r="34">
@@ -7217,25 +7162,25 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="E34" s="10" t="n">
+      <c r="E34" s="9" t="n">
         <v>0.10436</v>
       </c>
-      <c r="F34" s="10" t="n">
+      <c r="F34" s="9" t="n">
         <v>0.081</v>
       </c>
-      <c r="G34" s="10" t="n">
+      <c r="G34" s="9" t="n">
         <v>0.041550003</v>
       </c>
-      <c r="H34" s="11" t="n">
-        <v>7.9710145</v>
-      </c>
-      <c r="I34" s="12" t="n">
-        <v>0.8206015</v>
-      </c>
-      <c r="J34" s="15" t="n">
+      <c r="H34" s="10" t="n">
+        <v>7.6811595</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>0.7907615</v>
+      </c>
+      <c r="J34" s="14" t="n">
         <v>43.245</v>
       </c>
-      <c r="K34" s="12" t="n">
+      <c r="K34" s="11" t="n">
         <v>6.9</v>
       </c>
     </row>
@@ -7245,7 +7190,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RATU.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -7257,25 +7202,25 @@
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.45251998</v>
-      </c>
-      <c r="F35" s="17" t="n">
-        <v>-0.183</v>
+        <v>0.045900002</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>0.329</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.31559</v>
-      </c>
-      <c r="H35" s="18" t="n">
-        <v>49.98537</v>
-      </c>
-      <c r="I35" s="15" t="n">
-        <v>301470.56</v>
-      </c>
-      <c r="J35" s="15" t="n">
-        <v>36.548</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>102.53</v>
+        <v>0.19652</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>120.320854</v>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>75000</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>12.694</v>
+      </c>
+      <c r="K35" s="11" t="n">
+        <v>5.61</v>
       </c>
     </row>
     <row r="36">
@@ -7284,7 +7229,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -7295,26 +7240,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E36" s="17" t="n">
-        <v>-0.29015</v>
+      <c r="E36" s="9" t="n">
+        <v>0.15447</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>0.671</v>
-      </c>
-      <c r="G36" s="10" t="n">
-        <v>-0.21053</v>
+        <v>0.034</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>0.091759995</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="16" t="n">
-        <v>3.3613205</v>
-      </c>
-      <c r="J36" s="15" t="n">
-        <v>65.76600000000001</v>
-      </c>
-      <c r="K36" s="16" t="n">
-        <v>0</v>
+        <v>35.557415</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>70833.336</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>68.20699999999999</v>
+      </c>
+      <c r="K36" s="11" t="n">
+        <v>95.62</v>
       </c>
     </row>
     <row r="37">
@@ -7323,7 +7268,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -7334,26 +7279,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E37" s="10" t="n">
-        <v>0.045900002</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="G37" s="10" t="n">
-        <v>0.19652</v>
-      </c>
-      <c r="H37" s="18" t="n">
-        <v>147.11191</v>
-      </c>
-      <c r="I37" s="15" t="n">
-        <v>90555.56</v>
-      </c>
-      <c r="J37" s="15" t="n">
-        <v>12.694</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>5.54</v>
+      <c r="E37" s="9" t="n">
+        <v>0.06432</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>1.905</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>0.24544</v>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>178.41727</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>6.1019115</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <v>1.39</v>
       </c>
     </row>
     <row r="38">
@@ -7362,7 +7307,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -7373,26 +7318,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E38" s="10" t="n">
-        <v>0.15447</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="G38" s="10" t="n">
-        <v>0.091759995</v>
-      </c>
-      <c r="H38" t="n">
-        <v>36.587914</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>72916.664</v>
-      </c>
-      <c r="J38" s="15" t="n">
-        <v>68.20699999999999</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>95.66</v>
+      <c r="E38" s="8" t="n">
+        <v>0.23723</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>0.14588</v>
+      </c>
+      <c r="H38" s="17" t="n">
+        <v>160.98656</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>34.302204</v>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>38.133</v>
+      </c>
+      <c r="K38" s="11" t="n">
+        <v>11.15</v>
       </c>
     </row>
     <row r="39">
@@ -7401,7 +7346,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>CDIA.JK</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -7412,26 +7357,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E39" s="10" t="n">
-        <v>0.06432</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>1.905</v>
-      </c>
-      <c r="G39" s="9" t="n">
-        <v>0.24544</v>
-      </c>
-      <c r="H39" s="18" t="n">
-        <v>189.92805</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>6.495583</v>
-      </c>
-      <c r="J39" s="15" t="n">
-        <v>2.833</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>1.39</v>
+      <c r="E39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>0.65328</v>
+      </c>
+      <c r="H39" s="17" t="n">
+        <v>66.69498400000001</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>98124.99000000001</v>
+      </c>
+      <c r="J39" s="14" t="n">
+        <v>34.873</v>
+      </c>
+      <c r="K39" s="11" t="n">
+        <v>11.77</v>
       </c>
     </row>
     <row r="40">
@@ -7440,7 +7385,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -7451,26 +7396,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E40" s="9" t="n">
-        <v>0.23723</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="G40" s="10" t="n">
-        <v>0.14588</v>
-      </c>
-      <c r="H40" s="18" t="n">
-        <v>158.13118</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <v>33.633358</v>
-      </c>
-      <c r="J40" s="15" t="n">
-        <v>38.133</v>
-      </c>
-      <c r="K40" s="12" t="n">
-        <v>11.13</v>
+      <c r="E40" s="8" t="n">
+        <v>0.45251998</v>
+      </c>
+      <c r="F40" s="15" t="n">
+        <v>-0.183</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="H40" s="17" t="n">
+        <v>47.29334</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <v>284705.88</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>36.548</v>
+      </c>
+      <c r="K40" s="11" t="n">
+        <v>102.34</v>
       </c>
     </row>
     <row r="41">
@@ -7479,7 +7424,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CDIA.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -7490,26 +7435,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="E41" s="10" t="n">
-        <v>0</v>
+      <c r="E41" s="8" t="n">
+        <v>0.22038001</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="G41" s="9" t="n">
-        <v>0.65328</v>
-      </c>
-      <c r="H41" s="18" t="n">
-        <v>69.3617</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>101874.99</v>
-      </c>
-      <c r="J41" s="15" t="n">
-        <v>34.873</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>11.75</v>
+        <v>0.04</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>0.23266001</v>
+      </c>
+      <c r="H41" s="17" t="n">
+        <v>327.03885</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>1195000</v>
+      </c>
+      <c r="J41" s="14" t="n">
+        <v>239.827</v>
+      </c>
+      <c r="K41" s="11" t="n">
+        <v>18.27</v>
       </c>
     </row>
   </sheetData>
